--- a/build/ショートステイ管理台帳.xlsx
+++ b/build/ショートステイ管理台帳.xlsx
@@ -31,12 +31,13 @@
     <definedName name="区分一覧">OFFSET('M_区分'!$A$4,0,0,MAX(1,COUNTA('M_区分'!$A$4:$A$20)),1)</definedName>
     <definedName name="送迎一覧">OFFSET('M_送迎'!$A$4,0,0,MAX(1,COUNTA('M_送迎'!$A$4:$A$15)),1)</definedName>
     <definedName name="状態一覧">'M_状態'!$A$4:$A$8</definedName>
+    <definedName name="送付先一覧">OFFSET('M_FAX送付先'!$A$4,0,0,MAX(1,COUNTA('M_FAX送付先'!$A$4:$A$24)),1)</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_予約入力'!$A$4:$AA$204</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02_カレンダー'!$A$1:$H$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'03_帯表'!$A$1:$AG$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'04_月間表'!$A$1:$K$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'06_食数表'!$A$1:$F$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'09_FAX空き表'!$A$1:$AF$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'09_FAX空き表'!$A$1:$H$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +50,7 @@
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="d"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -179,8 +180,57 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="001F3B52"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="00555555"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00A93226"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00222222"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="001F618D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -271,8 +321,14 @@
         <bgColor rgb="00FBF8F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+        <bgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -365,6 +421,185 @@
       </bottom>
     </border>
     <border>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -408,11 +643,221 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -554,19 +999,124 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -590,8 +1140,35 @@
     <xf numFmtId="166" fontId="17" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -927,6 +1504,27 @@
     <author>設計メモ</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>M_FAX送付先 に登録した事業所を選ぶと、御中・ご担当・FAX番号が自動で入ります。
+空欄のままにすると、手書き用の下線が印刷されます。</t>
+      </text>
+    </comment>
+    <comment ref="A39" authorId="0" shapeId="0">
+      <text>
+        <t>送付先へのひとこと（任意）。空欄のままでも印刷できます。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>設計メモ</author>
+  </authors>
+  <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>氏名を書き換えると 01_予約入力 のプルダウンにも反映されます。
@@ -1227,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1348,7 +1946,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>外部へFAXする空き状況。利用者名は載りません。</t>
+          <t>★このまま印刷してFAX送信できる1枚ものの用紙です。送信票と空き状況カレンダーが一体になっており、送信先・送信元・挨拶文・凡例・注意書き・連絡事項欄まで入っています。利用者名は載りません。A4縦1枚に収まるよう設定済みです。</t>
         </is>
       </c>
     </row>
@@ -1515,506 +2113,530 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>⑤ M_FAX送付先</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>相談支援事業所などFAXの送り先を登録します。09_FAX空き表 の宛先が一覧から選べるようになり、番号の打ち間違いによる誤送信を防げます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>④ M_区分・M_送迎</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>区分（SS・無料・契約など）と、その区分を支給量に数えるかどうか。★区分名はカレンダーの色分けに使います。M_区分 の上から4つまでが色に対応します。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>★ 部屋数が施設ごとに違う場合（1室の施設と2室の施設）</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>同じファイルで使えます</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>1室の施設は M_部屋 に1行だけ、2室の施設は2行だけ登録してください。定員・空室数・空き記号（○△×）は全て M_部屋 の行数から計算しているので、シートも数式も一切変えずに両方に対応します。最大4室まで。</t>
-        </is>
-      </c>
+      <c r="B29" s="4" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>使わない部屋の行を隠す</t>
+          <t>同じファイルで使えます</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>02_カレンダー は各週に「部屋1〜部屋4」の4行があります。1〜2室の施設では、使わない部屋の行（部屋名が空欄の行）をまとめて選択し、右クリック→非表示 にしてください。6週ぶんまとめて選べます。03_帯表・04_月間表 も同様に列を非表示にできます。</t>
+          <t>1室の施設は M_部屋 に1行だけ、2室の施設は2行だけ登録してください。定員・空室数・空き記号（○△×）は全て M_部屋 の行数から計算しているので、シートも数式も一切変えずに両方に対応します。最大4室まで。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>部屋を減らしたとき</t>
+          <t>使わない部屋の行を隠す</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>2室から1室に変更したのに古い予約が「部屋2」のまま残っていると、01_予約入力 のS列に「⚠部屋が未登録」と赤で出ます。その予約の部屋を選び直してください。</t>
+          <t>02_カレンダー は各週に「部屋1〜部屋4」の4行があります。1〜2室の施設では、使わない部屋の行（部屋名が空欄の行）をまとめて選択し、右クリック→非表示 にしてください。6週ぶんまとめて選べます。03_帯表・04_月間表 も同様に列を非表示にできます。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>1室のときの表示</t>
+          <t>部屋を減らしたとき</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>1室の施設では「△（残りわずか）」は構造上発生せず、必ず ○ か × になります。</t>
+          <t>2室から1室に変更したのに古い予約が「部屋2」のまま残っていると、01_予約入力 のS列に「⚠部屋が未登録」と赤で出ます。その予約の部屋を選び直してください。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>1室のときの表示</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>1室の施設では「△（残りわずか）」は構造上発生せず、必ず ○ か × になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>★ファイルは施設ごとに分ける</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>このファイルを施設の数だけコピーして「施設A_管理台帳.xlsx」「施設B_管理台帳.xlsx」のように分けてください。1つのファイルに複数施設を混ぜると、定員が施設ごとに違うため空き判定が成立せず、全ての集計に施設の絞り込みが必要になって必ず崩れます。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>★ 食事の決め方（3段階）</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>① 標準（何もしない）</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>日帰り=昼のみ ／ 初日=夕 ／ 中日=朝昼夕 ／ 最終日=朝。ほとんどの予約はこれで足ります。</t>
-        </is>
-      </c>
+      <c r="B35" s="4" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>② 予約ごとに決める</t>
+          <t>① 標準（何もしない）</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>01_予約入力 の「朝食」「昼食」「夕食」列で選びます。空欄=標準、○=その滞在の全ての利用日で出す、×=その滞在では出さない。「この方は毎日昼食もつける」「この方は朝食なし」といった決め方に使います。</t>
+          <t>日帰り=昼のみ ／ 初日=夕 ／ 中日=朝昼夕 ／ 最終日=朝。ほとんどの予約はこれで足ります。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>③ 特定の日だけ直す</t>
+          <t>② 予約ごとに決める</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>02_カレンダー 下部の「食事の個別調整」に日付と食数を入れます。★①②より優先されます。「この日だけ来客で1食多い」といった例外に使います。</t>
+          <t>01_予約入力 の「朝食」「昼食」「夕食」列で選びます。空欄=標準、○=その滞在の全ての利用日で出す、×=その滞在では出さない。「この方は毎日昼食もつける」「この方は朝食なし」といった決め方に使います。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>③ 特定の日だけ直す</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>02_カレンダー 下部の「食事の個別調整」に日付と食数を入れます。★①②より優先されます。「この日だけ来客で1食多い」といった例外に使います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>反映先</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>どれで決めても、02_カレンダー の食事行と 06_食数表 に自動で反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>★ 食事をカレンダーで見る・直す</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>いつもは自動</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>各週のいちばん下の「食事」行に、その日の 朝○ 昼○ 夕○ が自動で出ます。予約ごとの指定（01_予約入力 の朝食・昼食・夕食）もここに反映されます。</t>
-        </is>
-      </c>
+      <c r="B40" s="4" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>違う日だけ入れる</t>
+          <t>いつもは自動</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>02_カレンダー のカレンダーの下に「食事の個別調整」表があります。日付と、その日の実際の食数（朝・昼・夕）を入れてください。空欄の欄は自動のままです。0 を入れれば「その食事なし」になります。</t>
+          <t>各週のいちばん下の「食事」行に、その日の 朝○ 昼○ 夕○ が自動で出ます。予約ごとの指定（01_予約入力 の朝食・昼食・夕食）もここに反映されます。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>入れたらどうなる</t>
+          <t>違う日だけ入れる</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>カレンダーの食事行に「※調整」と付き、06_食数表 の食数もその値に変わります。厨房へ渡す数字も自動で合います。</t>
+          <t>02_カレンダー のカレンダーの下に「食事の個別調整」表があります。日付と、その日の実際の食数（朝・昼・夕）を入れてください。空欄の欄は自動のままです。0 を入れれば「その食事なし」になります。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>★月をまたいでも安全</t>
+          <t>入れたらどうなる</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>調整は日付で結び付けているので、対象月を切り替えても他の月に影響しません。同じ日付を2回入れると「⚠日付が重複」と赤く出ます。</t>
+          <t>カレンダーの食事行に「※調整」と付き、06_食数表 の食数もその値に変わります。厨房へ渡す数字も自動で合います。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>★月をまたいでも安全</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>調整は日付で結び付けているので、対象月を切り替えても他の月に影響しません。同じ日付を2回入れると「⚠日付が重複」と赤く出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>表示を消したいとき</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>02_カレンダー の「食事を表示」を空欄にすると、食事行が非表示になります。</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>カレンダーの記号の読み方</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>▶16:00 利用者A</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>その日が入所日。数字は入室時刻です（01_予約入力 に 16 と入れたもの）。</t>
-        </is>
-      </c>
+      <c r="B46" s="4" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>利用者A</t>
+          <t>▶16:00 利用者A</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>記号なしは連泊の中日。前の日から続いています。</t>
+          <t>その日が入所日。数字は入室時刻です（01_予約入力 に 16 と入れたもの）。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>利用者A ◀09:00</t>
+          <t>利用者A</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>その日が退所日。数字は退室時刻です。朝に退所するので、★その日の夜はもう次の方が入れます。</t>
+          <t>記号なしは連泊の中日。前の日から続いています。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>◆ 利用者A 10:00-16:00</t>
+          <t>利用者A ◀09:00</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>日帰り（体験利用）。宿泊しません。</t>
+          <t>その日が退所日。数字は退室時刻です。朝に退所するので、★その日の夜はもう次の方が入れます。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2人並ぶとき</t>
+          <t>◆ 利用者A 10:00-16:00</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>「利用者A ◀09:00　▶16:30 利用者B」のように、退所と入所が同じ日に重なると1つのマスに並びます。</t>
+          <t>日帰り（体験利用）。宿泊しません。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>空き ○ △ × 仮</t>
+          <t>2人並ぶとき</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>○=空室あり／△=残りわずか／×=満室／仮=仮予約で調整中。これは「その日の夜」の空き状況です。</t>
+          <t>「利用者A ◀09:00　▶16:30 利用者B」のように、退所と入所が同じ日に重なると1つのマスに並びます。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>空き ○ △ × 仮</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>○=空室あり／△=残りわずか／×=満室／仮=仮予約で調整中。これは「その日の夜」の空き状況です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>色分け</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>名前のマスは区分ごとに色が付きます（M_区分 の上から4つ＝青・緑・紫・橙）。仮予約・調整中はグレーの斜体になります。</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>数え方の定義（全シート共通のルール）</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>利用日数</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>入所日から退所日までの暦日数。両端を含みます（4/1入所・4/3退所 = 3日）。</t>
-        </is>
-      </c>
+      <c r="B54" s="4" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>宿泊数</t>
+          <t>利用日数</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>退所日 − 入所日（4/1入所・4/3退所 = 2泊）。</t>
+          <t>入所日から退所日までの暦日数。両端を含みます（4/1入所・4/3退所 = 3日）。</t>
         </is>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>日帰り（体験利用）</t>
+          <t>宿泊数</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>入所日 = 退所日。1利用日・0泊。食事は昼のみが既定です。</t>
+          <t>退所日 − 入所日（4/1入所・4/3退所 = 2泊）。</t>
         </is>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>空室の判定</t>
+          <t>日帰り（体験利用）</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>「その日の夜に泊まるか」で見ます。★退所日の当日の夜は空き扱いです（次の方が入れます）。カレンダーで退所日に名前が出ていても、その夜は空いています。</t>
+          <t>入所日 = 退所日。1利用日・0泊。食事は昼のみが既定です。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>集計に入る予約</t>
+          <t>空室の判定</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>確定・利用済み・仮予約・調整中は集計に入り、キャンセルだけが除外されます。キャンセルは行を削除せず、状態を「キャンセル」に変えて記録として残してください。</t>
+          <t>「その日の夜に泊まるか」で見ます。★退所日の当日の夜は空き扱いです（次の方が入れます）。カレンダーで退所日に名前が出ていても、その夜は空いています。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
+          <t>集計に入る予約</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>確定・利用済み・仮予約・調整中は集計に入り、キャンセルだけが除外されます。キャンセルは行を削除せず、状態を「キャンセル」に変えて記録として残してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
           <t>食事の既定</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>日帰り=昼のみ ／ 初日=夕 ／ 中日=朝昼夕 ／ 最終日=朝。例外だけ 06_食数表 の「調整」列に実数を入れると、そちらが優先されます。</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>セルの色の意味</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>うすい黄色</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>手で入力するセルです。</t>
-        </is>
-      </c>
+      <c r="B61" s="4" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>うすい灰色（斜体）</t>
+          <t>うすい黄色</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>自動計算です。上書きすると壊れます。触らないでください。</t>
+          <t>手で入力するセルです。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>うすい灰色（斜体）</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>自動計算です。上書きすると壊れます。触らないでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
           <t>赤・オレンジ</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>警告です。ダブルブッキング（⚠重複）・支給量オーバー・未登録の部屋を知らせます。</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>毎日の使い方</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n"/>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>予約が入ったら</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>01_予約入力 の空いている行に、1滞在=1行で入れます。日にちも時刻も数字だけ。食事が標準と違うときだけ 朝食・昼食・夕食 列で ○/× を選びます。Y列・Z列が赤くならないことだけ確認してください。</t>
-        </is>
-      </c>
+      <c r="B65" s="4" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>★部屋は必ず選ぶ</t>
+          <t>予約が入ったら</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>部屋が空欄のままだと、その予約はカレンダーの部屋の行に出ません（「空き」の判定には数えるので×にはなります）。V列に「⚠部屋が未選択」と赤で出るので直してください。</t>
+          <t>01_予約入力 の空いている行に、1滞在=1行で入れます。日にちも時刻も数字だけ。食事が標準と違うときだけ 朝食・昼食・夕食 列で ○/× を選びます。Y列・Z列が赤くならないことだけ確認してください。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>入れたあと確認</t>
+          <t>★部屋は必ず選ぶ</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>02_カレンダー を見て、意図した期間に帯が出ているかを目で確かめます。</t>
+          <t>部屋が空欄のままだと、その予約はカレンダーの部屋の行に出ません（「空き」の判定には数えるので×にはなります）。V列に「⚠部屋が未選択」と赤で出るので直してください。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>「空いてますか」</t>
+          <t>入れたあと確認</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>05_空室照会 に日付を2つ入れるだけです。</t>
+          <t>02_カレンダー を見て、意図した期間に帯が出ているかを目で確かめます。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
+          <t>「空いてますか」</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>05_空室照会 に日付を2つ入れるだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
           <t>月を切り替える</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>★02_カレンダー の「対象月」を変えると、03_帯表・06_食数表・09_FAX空き表 の月も一緒に変わります。</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>バックアップ</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
+          <t>FAXで空き状況を送る</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>09_FAX空き表 の「送信先」を選び、必要なら連絡事項を書いて印刷するだけです。送信先は M_FAX送付先 に登録しておくと一覧から選べます（番号の打ち間違いによる誤送信を防げます）。未登録・未入力の欄は手書き用の下線が印刷されるので、そのままでも使えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>バックアップ</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
           <t>月に一度はコピーを</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>このファイル自体が台帳です。月初に「YYYYMM_管理台帳.xlsx」の名前でコピーを別フォルダに残してください。</t>
         </is>
@@ -2031,596 +2653,796 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF18"/>
+  <dimension ref="A2:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10.4" customWidth="1" min="2" max="2"/>
+    <col width="10.4" customWidth="1" min="3" max="3"/>
+    <col width="10.4" customWidth="1" min="4" max="4"/>
+    <col width="10.4" customWidth="1" min="5" max="5"/>
+    <col width="10.4" customWidth="1" min="6" max="6"/>
+    <col width="10.4" customWidth="1" min="7" max="7"/>
+    <col width="10.4" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>Ｆ Ａ Ｘ　送　信　票</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="56">
+        <f>YEAR('02_カレンダー'!$B$4)&amp;"年"&amp;MONTH('02_カレンダー'!$B$4)&amp;"月"&amp;"　短期入所（ショートステイ）空き状況のご案内"</f>
+        <v/>
+      </c>
+      <c r="B3" s="116" t="n"/>
+      <c r="C3" s="116" t="n"/>
+      <c r="D3" s="116" t="n"/>
+      <c r="E3" s="116" t="n"/>
+      <c r="F3" s="116" t="n"/>
+      <c r="G3" s="116" t="n"/>
+      <c r="H3" s="116" t="n"/>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t>送 信 先</t>
+        </is>
+      </c>
+      <c r="B5" s="59" t="n"/>
+      <c r="C5" s="117" t="n"/>
+      <c r="D5" s="117" t="n"/>
+      <c r="E5" s="118" t="n"/>
+      <c r="F5" s="61" t="inlineStr">
+        <is>
+          <t>送信日</t>
+        </is>
+      </c>
+      <c r="G5" s="62">
+        <f>YEAR(TODAY())&amp;"年"&amp;MONTH(TODAY())&amp;"月"&amp;DAY(TODAY())&amp;"日"</f>
+        <v/>
+      </c>
+      <c r="H5" s="118" t="n"/>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="119" t="n"/>
+      <c r="B6" s="65">
+        <f>IF($B$5="","＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿　御中",$B$5&amp;"　御中")</f>
+        <v/>
+      </c>
+      <c r="C6" s="120" t="n"/>
+      <c r="D6" s="120" t="n"/>
+      <c r="E6" s="121" t="n"/>
+      <c r="F6" s="67" t="inlineStr">
+        <is>
+          <t>枚　数</t>
+        </is>
+      </c>
+      <c r="G6" s="68" t="inlineStr">
+        <is>
+          <t>本票を含め　1 枚</t>
+        </is>
+      </c>
+      <c r="H6" s="121" t="n"/>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="119" t="n"/>
+      <c r="B7" s="70">
+        <f>IF($B$5="","ご担当　＿＿＿＿＿＿＿＿　様",IF(IFERROR(INDEX('M_FAX送付先'!$B$4:$B$24,IFERROR(MATCH($B$5,'M_FAX送付先'!$A$4:$A$24,0),0)),"")="","","ご担当　"&amp;INDEX('M_FAX送付先'!$B$4:$B$24,IFERROR(MATCH($B$5,'M_FAX送付先'!$A$4:$A$24,0),0))&amp;"　様"))</f>
+        <v/>
+      </c>
+      <c r="C7" s="120" t="n"/>
+      <c r="D7" s="120" t="n"/>
+      <c r="E7" s="121" t="n"/>
+      <c r="F7" s="71">
+        <f>"全"&amp;'M_施設設定'!$B$6&amp;"室の施設です"</f>
+        <v/>
+      </c>
+      <c r="G7" s="120" t="n"/>
+      <c r="H7" s="121" t="n"/>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="122" t="n"/>
+      <c r="B8" s="73">
+        <f>IF($B$5="","ＦＡＸ　＿＿＿＿＿＿＿＿＿＿","ＦＡＸ　"&amp;IFERROR(INDEX('M_FAX送付先'!$C$4:$C$24,IFERROR(MATCH($B$5,'M_FAX送付先'!$A$4:$A$24,0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="C8" s="123" t="n"/>
+      <c r="D8" s="123" t="n"/>
+      <c r="E8" s="124" t="n"/>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>利用者名は記載しておりません</t>
+        </is>
+      </c>
+      <c r="G8" s="123" t="n"/>
+      <c r="H8" s="124" t="n"/>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="58" t="inlineStr">
+        <is>
+          <t>送 信 元</t>
+        </is>
+      </c>
+      <c r="B10" s="77">
         <f>'M_施設設定'!$B$4&amp;"　"&amp;'M_施設設定'!$B$5</f>
         <v/>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="55">
-        <f>TEXT('02_カレンダー'!$B$4,"yyyy年m月")&amp;"　短期入所 空き状況"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <f>'M_施設設定'!$B$11&amp;"　TEL "&amp;'M_施設設定'!$B$12&amp;"　FAX "&amp;'M_施設設定'!$B$13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <f>"作成日："&amp;TEXT(TODAY(),"yyyy年m月d日")&amp;"　／　対象月は 02_カレンダー で変更します"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="C10" s="117" t="n"/>
+      <c r="D10" s="117" t="n"/>
+      <c r="E10" s="117" t="n"/>
+      <c r="F10" s="117" t="n"/>
+      <c r="G10" s="117" t="n"/>
+      <c r="H10" s="118" t="n"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="119" t="n"/>
+      <c r="B11" s="70">
+        <f>IF('M_施設設定'!$B$11="","＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿",IF('M_施設設定'!$B$10="","","〒"&amp;'M_施設設定'!$B$10&amp;"　")&amp;'M_施設設定'!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="120" t="n"/>
+      <c r="D11" s="120" t="n"/>
+      <c r="E11" s="120" t="n"/>
+      <c r="F11" s="120" t="n"/>
+      <c r="G11" s="120" t="n"/>
+      <c r="H11" s="121" t="n"/>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="119" t="n"/>
+      <c r="B12" s="70">
+        <f>"ＴＥＬ　"&amp;IF('M_施設設定'!$B$12="","＿＿＿＿＿＿＿＿＿＿",'M_施設設定'!$B$12)&amp;"　　ＦＡＸ　"&amp;IF('M_施設設定'!$B$13="","＿＿＿＿＿＿＿＿＿＿",'M_施設設定'!$B$13)</f>
+        <v/>
+      </c>
+      <c r="C12" s="120" t="n"/>
+      <c r="D12" s="120" t="n"/>
+      <c r="E12" s="120" t="n"/>
+      <c r="F12" s="120" t="n"/>
+      <c r="G12" s="120" t="n"/>
+      <c r="H12" s="121" t="n"/>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="122" t="n"/>
+      <c r="B13" s="73">
+        <f>"担当　"&amp;IF('M_施設設定'!$B$14="","＿＿＿＿＿＿＿＿＿＿",'M_施設設定'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="C13" s="123" t="n"/>
+      <c r="D13" s="123" t="n"/>
+      <c r="E13" s="123" t="n"/>
+      <c r="F13" s="123" t="n"/>
+      <c r="G13" s="123" t="n"/>
+      <c r="H13" s="124" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="78" t="inlineStr">
+        <is>
+          <t>平素より大変お世話になっております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="78">
+        <f>YEAR('02_カレンダー'!$B$4)&amp;"年"&amp;MONTH('02_カレンダー'!$B$4)&amp;"月"&amp;"の短期入所の空き状況は下記のとおりです。ご確認のほど、よろしくお願いいたします。"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="79">
+        <f>"■　"&amp;YEAR('02_カレンダー'!$B$4)&amp;"年"&amp;MONTH('02_カレンダー'!$B$4)&amp;"月"&amp;"　空き状況"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="80" t="inlineStr"/>
+      <c r="B19" s="81" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="B6" s="56">
-        <f>IF('04_月間表'!$A7="","",DAY('04_月間表'!$A7))</f>
-        <v/>
-      </c>
-      <c r="C6" s="56">
-        <f>IF('04_月間表'!$A8="","",DAY('04_月間表'!$A8))</f>
-        <v/>
-      </c>
-      <c r="D6" s="56">
-        <f>IF('04_月間表'!$A9="","",DAY('04_月間表'!$A9))</f>
-        <v/>
-      </c>
-      <c r="E6" s="56">
-        <f>IF('04_月間表'!$A10="","",DAY('04_月間表'!$A10))</f>
-        <v/>
-      </c>
-      <c r="F6" s="56">
-        <f>IF('04_月間表'!$A11="","",DAY('04_月間表'!$A11))</f>
-        <v/>
-      </c>
-      <c r="G6" s="56">
-        <f>IF('04_月間表'!$A12="","",DAY('04_月間表'!$A12))</f>
-        <v/>
-      </c>
-      <c r="H6" s="56">
-        <f>IF('04_月間表'!$A13="","",DAY('04_月間表'!$A13))</f>
-        <v/>
-      </c>
-      <c r="I6" s="56">
-        <f>IF('04_月間表'!$A14="","",DAY('04_月間表'!$A14))</f>
-        <v/>
-      </c>
-      <c r="J6" s="56">
-        <f>IF('04_月間表'!$A15="","",DAY('04_月間表'!$A15))</f>
-        <v/>
-      </c>
-      <c r="K6" s="56">
-        <f>IF('04_月間表'!$A16="","",DAY('04_月間表'!$A16))</f>
-        <v/>
-      </c>
-      <c r="L6" s="56">
-        <f>IF('04_月間表'!$A17="","",DAY('04_月間表'!$A17))</f>
-        <v/>
-      </c>
-      <c r="M6" s="56">
-        <f>IF('04_月間表'!$A18="","",DAY('04_月間表'!$A18))</f>
-        <v/>
-      </c>
-      <c r="N6" s="56">
-        <f>IF('04_月間表'!$A19="","",DAY('04_月間表'!$A19))</f>
-        <v/>
-      </c>
-      <c r="O6" s="56">
-        <f>IF('04_月間表'!$A20="","",DAY('04_月間表'!$A20))</f>
-        <v/>
-      </c>
-      <c r="P6" s="56">
-        <f>IF('04_月間表'!$A21="","",DAY('04_月間表'!$A21))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="56">
-        <f>IF('04_月間表'!$A22="","",DAY('04_月間表'!$A22))</f>
-        <v/>
-      </c>
-      <c r="R6" s="56">
-        <f>IF('04_月間表'!$A23="","",DAY('04_月間表'!$A23))</f>
-        <v/>
-      </c>
-      <c r="S6" s="56">
-        <f>IF('04_月間表'!$A24="","",DAY('04_月間表'!$A24))</f>
-        <v/>
-      </c>
-      <c r="T6" s="56">
-        <f>IF('04_月間表'!$A25="","",DAY('04_月間表'!$A25))</f>
-        <v/>
-      </c>
-      <c r="U6" s="56">
-        <f>IF('04_月間表'!$A26="","",DAY('04_月間表'!$A26))</f>
-        <v/>
-      </c>
-      <c r="V6" s="56">
-        <f>IF('04_月間表'!$A27="","",DAY('04_月間表'!$A27))</f>
-        <v/>
-      </c>
-      <c r="W6" s="56">
-        <f>IF('04_月間表'!$A28="","",DAY('04_月間表'!$A28))</f>
-        <v/>
-      </c>
-      <c r="X6" s="56">
-        <f>IF('04_月間表'!$A29="","",DAY('04_月間表'!$A29))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="56">
-        <f>IF('04_月間表'!$A30="","",DAY('04_月間表'!$A30))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="56">
-        <f>IF('04_月間表'!$A31="","",DAY('04_月間表'!$A31))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="56">
-        <f>IF('04_月間表'!$A32="","",DAY('04_月間表'!$A32))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="56">
-        <f>IF('04_月間表'!$A33="","",DAY('04_月間表'!$A33))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="56">
-        <f>IF('04_月間表'!$A34="","",DAY('04_月間表'!$A34))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="56">
-        <f>IF('04_月間表'!$A35="","",DAY('04_月間表'!$A35))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="56">
-        <f>IF('04_月間表'!$A36="","",DAY('04_月間表'!$A36))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="56">
-        <f>IF('04_月間表'!$A37="","",DAY('04_月間表'!$A37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>曜日</t>
-        </is>
-      </c>
-      <c r="B7" s="56">
-        <f>IF('04_月間表'!$A7="","",'04_月間表'!$B7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="56">
-        <f>IF('04_月間表'!$A8="","",'04_月間表'!$B8)</f>
-        <v/>
-      </c>
-      <c r="D7" s="56">
-        <f>IF('04_月間表'!$A9="","",'04_月間表'!$B9)</f>
-        <v/>
-      </c>
-      <c r="E7" s="56">
-        <f>IF('04_月間表'!$A10="","",'04_月間表'!$B10)</f>
-        <v/>
-      </c>
-      <c r="F7" s="56">
-        <f>IF('04_月間表'!$A11="","",'04_月間表'!$B11)</f>
-        <v/>
-      </c>
-      <c r="G7" s="56">
-        <f>IF('04_月間表'!$A12="","",'04_月間表'!$B12)</f>
-        <v/>
-      </c>
-      <c r="H7" s="56">
-        <f>IF('04_月間表'!$A13="","",'04_月間表'!$B13)</f>
-        <v/>
-      </c>
-      <c r="I7" s="56">
-        <f>IF('04_月間表'!$A14="","",'04_月間表'!$B14)</f>
-        <v/>
-      </c>
-      <c r="J7" s="56">
-        <f>IF('04_月間表'!$A15="","",'04_月間表'!$B15)</f>
-        <v/>
-      </c>
-      <c r="K7" s="56">
-        <f>IF('04_月間表'!$A16="","",'04_月間表'!$B16)</f>
-        <v/>
-      </c>
-      <c r="L7" s="56">
-        <f>IF('04_月間表'!$A17="","",'04_月間表'!$B17)</f>
-        <v/>
-      </c>
-      <c r="M7" s="56">
-        <f>IF('04_月間表'!$A18="","",'04_月間表'!$B18)</f>
-        <v/>
-      </c>
-      <c r="N7" s="56">
-        <f>IF('04_月間表'!$A19="","",'04_月間表'!$B19)</f>
-        <v/>
-      </c>
-      <c r="O7" s="56">
-        <f>IF('04_月間表'!$A20="","",'04_月間表'!$B20)</f>
-        <v/>
-      </c>
-      <c r="P7" s="56">
-        <f>IF('04_月間表'!$A21="","",'04_月間表'!$B21)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="56">
-        <f>IF('04_月間表'!$A22="","",'04_月間表'!$B22)</f>
-        <v/>
-      </c>
-      <c r="R7" s="56">
-        <f>IF('04_月間表'!$A23="","",'04_月間表'!$B23)</f>
-        <v/>
-      </c>
-      <c r="S7" s="56">
-        <f>IF('04_月間表'!$A24="","",'04_月間表'!$B24)</f>
-        <v/>
-      </c>
-      <c r="T7" s="56">
-        <f>IF('04_月間表'!$A25="","",'04_月間表'!$B25)</f>
-        <v/>
-      </c>
-      <c r="U7" s="56">
-        <f>IF('04_月間表'!$A26="","",'04_月間表'!$B26)</f>
-        <v/>
-      </c>
-      <c r="V7" s="56">
-        <f>IF('04_月間表'!$A27="","",'04_月間表'!$B27)</f>
-        <v/>
-      </c>
-      <c r="W7" s="56">
-        <f>IF('04_月間表'!$A28="","",'04_月間表'!$B28)</f>
-        <v/>
-      </c>
-      <c r="X7" s="56">
-        <f>IF('04_月間表'!$A29="","",'04_月間表'!$B29)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="56">
-        <f>IF('04_月間表'!$A30="","",'04_月間表'!$B30)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="56">
-        <f>IF('04_月間表'!$A31="","",'04_月間表'!$B31)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="56">
-        <f>IF('04_月間表'!$A32="","",'04_月間表'!$B32)</f>
-        <v/>
-      </c>
-      <c r="AB7" s="56">
-        <f>IF('04_月間表'!$A33="","",'04_月間表'!$B33)</f>
-        <v/>
-      </c>
-      <c r="AC7" s="56">
-        <f>IF('04_月間表'!$A34="","",'04_月間表'!$B34)</f>
-        <v/>
-      </c>
-      <c r="AD7" s="56">
-        <f>IF('04_月間表'!$A35="","",'04_月間表'!$B35)</f>
-        <v/>
-      </c>
-      <c r="AE7" s="56">
-        <f>IF('04_月間表'!$A36="","",'04_月間表'!$B36)</f>
-        <v/>
-      </c>
-      <c r="AF7" s="56">
-        <f>IF('04_月間表'!$A37="","",'04_月間表'!$B37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>空き状況</t>
-        </is>
-      </c>
-      <c r="B8" s="57">
-        <f>IF('04_月間表'!$A7="","",'04_月間表'!$J7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="57">
-        <f>IF('04_月間表'!$A8="","",'04_月間表'!$J8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="57">
-        <f>IF('04_月間表'!$A9="","",'04_月間表'!$J9)</f>
-        <v/>
-      </c>
-      <c r="E8" s="57">
-        <f>IF('04_月間表'!$A10="","",'04_月間表'!$J10)</f>
-        <v/>
-      </c>
-      <c r="F8" s="57">
-        <f>IF('04_月間表'!$A11="","",'04_月間表'!$J11)</f>
-        <v/>
-      </c>
-      <c r="G8" s="57">
-        <f>IF('04_月間表'!$A12="","",'04_月間表'!$J12)</f>
-        <v/>
-      </c>
-      <c r="H8" s="57">
-        <f>IF('04_月間表'!$A13="","",'04_月間表'!$J13)</f>
-        <v/>
-      </c>
-      <c r="I8" s="57">
-        <f>IF('04_月間表'!$A14="","",'04_月間表'!$J14)</f>
-        <v/>
-      </c>
-      <c r="J8" s="57">
-        <f>IF('04_月間表'!$A15="","",'04_月間表'!$J15)</f>
-        <v/>
-      </c>
-      <c r="K8" s="57">
-        <f>IF('04_月間表'!$A16="","",'04_月間表'!$J16)</f>
-        <v/>
-      </c>
-      <c r="L8" s="57">
-        <f>IF('04_月間表'!$A17="","",'04_月間表'!$J17)</f>
-        <v/>
-      </c>
-      <c r="M8" s="57">
-        <f>IF('04_月間表'!$A18="","",'04_月間表'!$J18)</f>
-        <v/>
-      </c>
-      <c r="N8" s="57">
-        <f>IF('04_月間表'!$A19="","",'04_月間表'!$J19)</f>
-        <v/>
-      </c>
-      <c r="O8" s="57">
-        <f>IF('04_月間表'!$A20="","",'04_月間表'!$J20)</f>
-        <v/>
-      </c>
-      <c r="P8" s="57">
-        <f>IF('04_月間表'!$A21="","",'04_月間表'!$J21)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="57">
-        <f>IF('04_月間表'!$A22="","",'04_月間表'!$J22)</f>
-        <v/>
-      </c>
-      <c r="R8" s="57">
-        <f>IF('04_月間表'!$A23="","",'04_月間表'!$J23)</f>
-        <v/>
-      </c>
-      <c r="S8" s="57">
-        <f>IF('04_月間表'!$A24="","",'04_月間表'!$J24)</f>
-        <v/>
-      </c>
-      <c r="T8" s="57">
-        <f>IF('04_月間表'!$A25="","",'04_月間表'!$J25)</f>
-        <v/>
-      </c>
-      <c r="U8" s="57">
-        <f>IF('04_月間表'!$A26="","",'04_月間表'!$J26)</f>
-        <v/>
-      </c>
-      <c r="V8" s="57">
-        <f>IF('04_月間表'!$A27="","",'04_月間表'!$J27)</f>
-        <v/>
-      </c>
-      <c r="W8" s="57">
-        <f>IF('04_月間表'!$A28="","",'04_月間表'!$J28)</f>
-        <v/>
-      </c>
-      <c r="X8" s="57">
-        <f>IF('04_月間表'!$A29="","",'04_月間表'!$J29)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="57">
-        <f>IF('04_月間表'!$A30="","",'04_月間表'!$J30)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="57">
-        <f>IF('04_月間表'!$A31="","",'04_月間表'!$J31)</f>
-        <v/>
-      </c>
-      <c r="AA8" s="57">
-        <f>IF('04_月間表'!$A32="","",'04_月間表'!$J32)</f>
-        <v/>
-      </c>
-      <c r="AB8" s="57">
-        <f>IF('04_月間表'!$A33="","",'04_月間表'!$J33)</f>
-        <v/>
-      </c>
-      <c r="AC8" s="57">
-        <f>IF('04_月間表'!$A34="","",'04_月間表'!$J34)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="57">
-        <f>IF('04_月間表'!$A35="","",'04_月間表'!$J35)</f>
-        <v/>
-      </c>
-      <c r="AE8" s="57">
-        <f>IF('04_月間表'!$A36="","",'04_月間表'!$J36)</f>
-        <v/>
-      </c>
-      <c r="AF8" s="57">
-        <f>IF('04_月間表'!$A37="","",'04_月間表'!$J37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>凡例</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="58" t="inlineStr">
+      <c r="C19" s="82" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D19" s="82" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="E19" s="82" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="F19" s="82" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="G19" s="82" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="H19" s="83" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="84" t="inlineStr">
+        <is>
+          <t>第1週</t>
+        </is>
+      </c>
+      <c r="B20" s="125">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+0)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+1)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+1)</f>
+        <v/>
+      </c>
+      <c r="D20" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+2)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+2)</f>
+        <v/>
+      </c>
+      <c r="E20" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+3)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+3)</f>
+        <v/>
+      </c>
+      <c r="F20" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+4)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+4)</f>
+        <v/>
+      </c>
+      <c r="G20" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+5)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+5)</f>
+        <v/>
+      </c>
+      <c r="H20" s="127">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+6)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="122" t="n"/>
+      <c r="B21" s="88">
+        <f>IF(B20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(B20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C21" s="88">
+        <f>IF(C20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(C20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D21" s="88">
+        <f>IF(D20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(D20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="88">
+        <f>IF(E20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(E20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F21" s="88">
+        <f>IF(F20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(F20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G21" s="88">
+        <f>IF(G20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(G20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H21" s="89">
+        <f>IF(H20="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(H20,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="84" t="inlineStr">
+        <is>
+          <t>第2週</t>
+        </is>
+      </c>
+      <c r="B22" s="125">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+7)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+7)</f>
+        <v/>
+      </c>
+      <c r="C22" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+8)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+8)</f>
+        <v/>
+      </c>
+      <c r="D22" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+9)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+9)</f>
+        <v/>
+      </c>
+      <c r="E22" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+10)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+10)</f>
+        <v/>
+      </c>
+      <c r="F22" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+11)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+11)</f>
+        <v/>
+      </c>
+      <c r="G22" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+12)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+12)</f>
+        <v/>
+      </c>
+      <c r="H22" s="127">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+13)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="122" t="n"/>
+      <c r="B23" s="88">
+        <f>IF(B22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(B22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C23" s="88">
+        <f>IF(C22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(C22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D23" s="88">
+        <f>IF(D22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(D22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="88">
+        <f>IF(E22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(E22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F23" s="88">
+        <f>IF(F22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(F22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G23" s="88">
+        <f>IF(G22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(G22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H23" s="89">
+        <f>IF(H22="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(H22,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="84" t="inlineStr">
+        <is>
+          <t>第3週</t>
+        </is>
+      </c>
+      <c r="B24" s="125">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+14)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+14)</f>
+        <v/>
+      </c>
+      <c r="C24" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+15)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+15)</f>
+        <v/>
+      </c>
+      <c r="D24" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+16)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+16)</f>
+        <v/>
+      </c>
+      <c r="E24" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+17)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+17)</f>
+        <v/>
+      </c>
+      <c r="F24" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+18)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+18)</f>
+        <v/>
+      </c>
+      <c r="G24" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+19)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+19)</f>
+        <v/>
+      </c>
+      <c r="H24" s="127">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+20)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="122" t="n"/>
+      <c r="B25" s="88">
+        <f>IF(B24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(B24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C25" s="88">
+        <f>IF(C24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(C24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D25" s="88">
+        <f>IF(D24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(D24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="88">
+        <f>IF(E24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(E24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" s="88">
+        <f>IF(F24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(F24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G25" s="88">
+        <f>IF(G24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(G24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H25" s="89">
+        <f>IF(H24="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(H24,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="84" t="inlineStr">
+        <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="B26" s="125">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+21)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+21)</f>
+        <v/>
+      </c>
+      <c r="C26" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+22)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+22)</f>
+        <v/>
+      </c>
+      <c r="D26" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+23)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+23)</f>
+        <v/>
+      </c>
+      <c r="E26" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+24)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+24)</f>
+        <v/>
+      </c>
+      <c r="F26" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+25)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+26)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="127">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+27)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="122" t="n"/>
+      <c r="B27" s="88">
+        <f>IF(B26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(B26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C27" s="88">
+        <f>IF(C26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(C26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D27" s="88">
+        <f>IF(D26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(D26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="88">
+        <f>IF(E26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(E26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F27" s="88">
+        <f>IF(F26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(F26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G27" s="88">
+        <f>IF(G26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(G26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H27" s="89">
+        <f>IF(H26="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(H26,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="84" t="inlineStr">
+        <is>
+          <t>第5週</t>
+        </is>
+      </c>
+      <c r="B28" s="125">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+28)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+29)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+29)</f>
+        <v/>
+      </c>
+      <c r="D28" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+30)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+30)</f>
+        <v/>
+      </c>
+      <c r="E28" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+31)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+31)</f>
+        <v/>
+      </c>
+      <c r="F28" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+32)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+32)</f>
+        <v/>
+      </c>
+      <c r="G28" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+33)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+33)</f>
+        <v/>
+      </c>
+      <c r="H28" s="127">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+34)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="122" t="n"/>
+      <c r="B29" s="88">
+        <f>IF(B28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(B28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C29" s="88">
+        <f>IF(C28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(C28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D29" s="88">
+        <f>IF(D28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(D28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="88">
+        <f>IF(E28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(E28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F29" s="88">
+        <f>IF(F28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(F28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G29" s="88">
+        <f>IF(G28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(G28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H29" s="89">
+        <f>IF(H28="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(H28,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="84" t="inlineStr">
+        <is>
+          <t>第6週</t>
+        </is>
+      </c>
+      <c r="B30" s="125">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+35)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+35)</f>
+        <v/>
+      </c>
+      <c r="C30" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+36)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+36)</f>
+        <v/>
+      </c>
+      <c r="D30" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+37)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+37)</f>
+        <v/>
+      </c>
+      <c r="E30" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+38)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+38)</f>
+        <v/>
+      </c>
+      <c r="F30" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+39)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+39)</f>
+        <v/>
+      </c>
+      <c r="G30" s="126">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+40)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+40)</f>
+        <v/>
+      </c>
+      <c r="H30" s="127">
+        <f>IF(MONTH('02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+41)&lt;&gt;MONTH('02_カレンダー'!$B$4),"",'02_カレンダー'!$B$4-WEEKDAY('02_カレンダー'!$B$4)+1+41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="122" t="n"/>
+      <c r="B31" s="90">
+        <f>IF(B30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(B30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C31" s="90">
+        <f>IF(C30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(C30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D31" s="90">
+        <f>IF(D30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(D30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E31" s="90">
+        <f>IF(E30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(E30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F31" s="90">
+        <f>IF(F30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(F30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G31" s="90">
+        <f>IF(G30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(G30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H31" s="91">
+        <f>IF(H30="","",IFERROR(INDEX('04_月間表'!$J$7:$J$37,MATCH(H30,'04_月間表'!$A$7:$A$37,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="92" t="inlineStr">
+        <is>
+          <t>凡　例</t>
+        </is>
+      </c>
+      <c r="B32" s="93" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C32" s="94" t="inlineStr">
         <is>
           <t>空室あり</t>
         </is>
       </c>
-      <c r="F11" s="58" t="inlineStr">
+      <c r="D32" s="93" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E32" s="94" t="inlineStr">
         <is>
           <t>残りわずか</t>
         </is>
       </c>
-      <c r="J11" s="58" t="inlineStr">
+      <c r="F32" s="93" t="inlineStr">
         <is>
           <t>仮</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="G32" s="94" t="inlineStr">
         <is>
           <t>仮予約で調整中</t>
         </is>
       </c>
-      <c r="N11" s="58" t="inlineStr">
+      <c r="H32" s="93" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="I32" s="95" t="inlineStr">
         <is>
           <t>満室</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="95" t="inlineStr">
         <is>
           <t>・各日の欄は「その日の夜（宿泊）」の空き状況です。退所日の当日は、次の方がご利用いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>・空き状況は日々変動します。ご予約前に必ずお電話でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <f>"・全"&amp;'M_施設設定'!$B$6&amp;"室。この用紙に利用者様のお名前は記載しておりません。"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>月内集計</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="59">
-        <f>COUNTIF($B$8:$AF$8,"○")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>空室あり</t>
-        </is>
-      </c>
-      <c r="F18" s="59">
-        <f>COUNTIF($B$8:$AF$8,"△")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>残りわずか</t>
-        </is>
-      </c>
-      <c r="J18" s="59">
-        <f>COUNTIF($B$8:$AF$8,"仮")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>仮予約</t>
-        </is>
-      </c>
-      <c r="N18" s="59">
-        <f>COUNTIF($B$8:$AF$8,"×")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>満室</t>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="95" t="inlineStr">
+        <is>
+          <t>・空き状況は日々変動いたします。ご予約の前に、必ずお電話でご確認くださいますようお願いいたします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="95">
+        <f>"・全"&amp;'M_施設設定'!$B$6&amp;"室の施設です。本用紙に利用者様のお名前は記載しておりません。"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="96">
+        <f>"【月内の集計】　空室あり "&amp;COUNTIF($B$21:$H$31,"○")&amp;" 日　／　残りわずか "&amp;COUNTIF($B$21:$H$31,"△")&amp;" 日　／　仮予約 "&amp;COUNTIF($B$21:$H$31,"仮")&amp;" 日　／　満室 "&amp;COUNTIF($B$21:$H$31,"×")&amp;" 日"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="79" t="inlineStr">
+        <is>
+          <t>■　連絡事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="128" t="n"/>
+      <c r="B39" s="129" t="n"/>
+      <c r="C39" s="129" t="n"/>
+      <c r="D39" s="129" t="n"/>
+      <c r="E39" s="129" t="n"/>
+      <c r="F39" s="129" t="n"/>
+      <c r="G39" s="129" t="n"/>
+      <c r="H39" s="130" t="n"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="131" t="n"/>
+      <c r="H40" s="132" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="131" t="n"/>
+      <c r="H41" s="132" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="133" t="n"/>
+      <c r="B42" s="116" t="n"/>
+      <c r="C42" s="116" t="n"/>
+      <c r="D42" s="116" t="n"/>
+      <c r="E42" s="116" t="n"/>
+      <c r="F42" s="116" t="n"/>
+      <c r="G42" s="116" t="n"/>
+      <c r="H42" s="134" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="95" t="inlineStr">
+        <is>
+          <t>※ 本状が誤って届いた場合は、お手数ですが上記の連絡先までご一報のうえ、ご破棄くださいますようお願いいたします。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:AF8">
+  <mergeCells count="32">
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A39:H42"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B21:H31">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>B8="×"</formula>
+      <formula>B21="×"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
-      <formula>B8="△"</formula>
+      <formula>B21="△"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
-      <formula>B8="仮"</formula>
+      <formula>B21="仮"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="9">
-      <formula>B8="○"</formula>
+      <formula>B21="○"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:AF7">
-    <cfRule type="expression" priority="5" dxfId="12">
-      <formula>OR(B$7="土",B$7="日")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="送信先" prompt="M_FAX送付先 から選びます。空欄なら手書き用の下線が出ます。" type="list">
+      <formula1>=送付先一覧</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2834,71 +3656,71 @@
           <t>１Ｆ</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n"/>
+      <c r="B4" s="105" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="n"/>
-      <c r="B5" s="61" t="n"/>
+      <c r="B5" s="106" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n"/>
-      <c r="B6" s="60" t="n"/>
+      <c r="B6" s="105" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n"/>
-      <c r="B7" s="60" t="n"/>
+      <c r="B7" s="105" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n"/>
-      <c r="B8" s="60" t="n"/>
+      <c r="B8" s="105" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
-      <c r="B9" s="60" t="n"/>
+      <c r="B9" s="105" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
-      <c r="B10" s="60" t="n"/>
+      <c r="B10" s="105" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n"/>
-      <c r="B11" s="60" t="n"/>
+      <c r="B11" s="105" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n"/>
-      <c r="B12" s="60" t="n"/>
+      <c r="B12" s="105" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n"/>
-      <c r="B13" s="60" t="n"/>
+      <c r="B13" s="105" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
-      <c r="B14" s="60" t="n"/>
+      <c r="B14" s="105" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
-      <c r="B15" s="60" t="n"/>
+      <c r="B15" s="105" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n"/>
-      <c r="B16" s="60" t="n"/>
+      <c r="B16" s="105" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n"/>
-      <c r="B17" s="60" t="n"/>
+      <c r="B17" s="105" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n"/>
-      <c r="B18" s="60" t="n"/>
+      <c r="B18" s="105" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n"/>
-      <c r="B19" s="60" t="n"/>
+      <c r="B19" s="105" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n"/>
-      <c r="B20" s="60" t="n"/>
+      <c r="B20" s="105" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2959,7 +3781,7 @@
       <c r="B4" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="61" t="n"/>
+      <c r="C4" s="106" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -2970,7 +3792,7 @@
       <c r="B5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="61" t="n"/>
+      <c r="C5" s="106" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -2979,7 +3801,7 @@
         </is>
       </c>
       <c r="B6" s="18" t="n"/>
-      <c r="C6" s="61" t="n"/>
+      <c r="C6" s="106" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
@@ -2988,7 +3810,7 @@
         </is>
       </c>
       <c r="B7" s="18" t="n"/>
-      <c r="C7" s="60" t="n"/>
+      <c r="C7" s="105" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -2997,267 +3819,267 @@
         </is>
       </c>
       <c r="B8" s="18" t="n"/>
-      <c r="C8" s="60" t="n"/>
+      <c r="C8" s="105" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
       <c r="B9" s="18" t="n"/>
-      <c r="C9" s="60" t="n"/>
+      <c r="C9" s="105" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="60" t="n"/>
+      <c r="C10" s="105" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n"/>
       <c r="B11" s="18" t="n"/>
-      <c r="C11" s="60" t="n"/>
+      <c r="C11" s="105" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n"/>
       <c r="B12" s="18" t="n"/>
-      <c r="C12" s="60" t="n"/>
+      <c r="C12" s="105" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n"/>
       <c r="B13" s="18" t="n"/>
-      <c r="C13" s="60" t="n"/>
+      <c r="C13" s="105" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
       <c r="B14" s="18" t="n"/>
-      <c r="C14" s="60" t="n"/>
+      <c r="C14" s="105" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
       <c r="B15" s="18" t="n"/>
-      <c r="C15" s="60" t="n"/>
+      <c r="C15" s="105" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n"/>
       <c r="B16" s="18" t="n"/>
-      <c r="C16" s="60" t="n"/>
+      <c r="C16" s="105" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n"/>
       <c r="B17" s="18" t="n"/>
-      <c r="C17" s="60" t="n"/>
+      <c r="C17" s="105" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n"/>
       <c r="B18" s="18" t="n"/>
-      <c r="C18" s="60" t="n"/>
+      <c r="C18" s="105" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n"/>
       <c r="B19" s="18" t="n"/>
-      <c r="C19" s="60" t="n"/>
+      <c r="C19" s="105" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n"/>
       <c r="B20" s="18" t="n"/>
-      <c r="C20" s="60" t="n"/>
+      <c r="C20" s="105" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n"/>
       <c r="B21" s="18" t="n"/>
-      <c r="C21" s="60" t="n"/>
+      <c r="C21" s="105" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="n"/>
       <c r="B22" s="18" t="n"/>
-      <c r="C22" s="60" t="n"/>
+      <c r="C22" s="105" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n"/>
       <c r="B23" s="18" t="n"/>
-      <c r="C23" s="60" t="n"/>
+      <c r="C23" s="105" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="18" t="n"/>
       <c r="B24" s="18" t="n"/>
-      <c r="C24" s="60" t="n"/>
+      <c r="C24" s="105" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="n"/>
       <c r="B25" s="18" t="n"/>
-      <c r="C25" s="60" t="n"/>
+      <c r="C25" s="105" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="n"/>
       <c r="B26" s="18" t="n"/>
-      <c r="C26" s="60" t="n"/>
+      <c r="C26" s="105" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="18" t="n"/>
       <c r="B27" s="18" t="n"/>
-      <c r="C27" s="60" t="n"/>
+      <c r="C27" s="105" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="18" t="n"/>
       <c r="B28" s="18" t="n"/>
-      <c r="C28" s="60" t="n"/>
+      <c r="C28" s="105" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n"/>
       <c r="B29" s="18" t="n"/>
-      <c r="C29" s="60" t="n"/>
+      <c r="C29" s="105" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n"/>
       <c r="B30" s="18" t="n"/>
-      <c r="C30" s="60" t="n"/>
+      <c r="C30" s="105" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n"/>
       <c r="B31" s="18" t="n"/>
-      <c r="C31" s="60" t="n"/>
+      <c r="C31" s="105" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n"/>
       <c r="B32" s="18" t="n"/>
-      <c r="C32" s="60" t="n"/>
+      <c r="C32" s="105" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n"/>
       <c r="B33" s="18" t="n"/>
-      <c r="C33" s="60" t="n"/>
+      <c r="C33" s="105" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n"/>
       <c r="B34" s="18" t="n"/>
-      <c r="C34" s="60" t="n"/>
+      <c r="C34" s="105" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n"/>
       <c r="B35" s="18" t="n"/>
-      <c r="C35" s="60" t="n"/>
+      <c r="C35" s="105" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n"/>
       <c r="B36" s="18" t="n"/>
-      <c r="C36" s="60" t="n"/>
+      <c r="C36" s="105" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n"/>
       <c r="B37" s="18" t="n"/>
-      <c r="C37" s="60" t="n"/>
+      <c r="C37" s="105" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="18" t="n"/>
       <c r="B38" s="18" t="n"/>
-      <c r="C38" s="60" t="n"/>
+      <c r="C38" s="105" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="n"/>
       <c r="B39" s="18" t="n"/>
-      <c r="C39" s="60" t="n"/>
+      <c r="C39" s="105" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="18" t="n"/>
       <c r="B40" s="18" t="n"/>
-      <c r="C40" s="60" t="n"/>
+      <c r="C40" s="105" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="18" t="n"/>
       <c r="B41" s="18" t="n"/>
-      <c r="C41" s="60" t="n"/>
+      <c r="C41" s="105" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="n"/>
       <c r="B42" s="18" t="n"/>
-      <c r="C42" s="60" t="n"/>
+      <c r="C42" s="105" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n"/>
       <c r="B43" s="18" t="n"/>
-      <c r="C43" s="60" t="n"/>
+      <c r="C43" s="105" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n"/>
       <c r="B44" s="18" t="n"/>
-      <c r="C44" s="60" t="n"/>
+      <c r="C44" s="105" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n"/>
       <c r="B45" s="18" t="n"/>
-      <c r="C45" s="60" t="n"/>
+      <c r="C45" s="105" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="n"/>
       <c r="B46" s="18" t="n"/>
-      <c r="C46" s="60" t="n"/>
+      <c r="C46" s="105" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="18" t="n"/>
       <c r="B47" s="18" t="n"/>
-      <c r="C47" s="60" t="n"/>
+      <c r="C47" s="105" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="18" t="n"/>
       <c r="B48" s="18" t="n"/>
-      <c r="C48" s="60" t="n"/>
+      <c r="C48" s="105" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="18" t="n"/>
       <c r="B49" s="18" t="n"/>
-      <c r="C49" s="60" t="n"/>
+      <c r="C49" s="105" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="n"/>
       <c r="B50" s="18" t="n"/>
-      <c r="C50" s="60" t="n"/>
+      <c r="C50" s="105" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="18" t="n"/>
       <c r="B51" s="18" t="n"/>
-      <c r="C51" s="60" t="n"/>
+      <c r="C51" s="105" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="18" t="n"/>
       <c r="B52" s="18" t="n"/>
-      <c r="C52" s="60" t="n"/>
+      <c r="C52" s="105" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="18" t="n"/>
       <c r="B53" s="18" t="n"/>
-      <c r="C53" s="60" t="n"/>
+      <c r="C53" s="105" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="18" t="n"/>
       <c r="B54" s="18" t="n"/>
-      <c r="C54" s="60" t="n"/>
+      <c r="C54" s="105" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="18" t="n"/>
       <c r="B55" s="18" t="n"/>
-      <c r="C55" s="60" t="n"/>
+      <c r="C55" s="105" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="18" t="n"/>
       <c r="B56" s="18" t="n"/>
-      <c r="C56" s="60" t="n"/>
+      <c r="C56" s="105" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="18" t="n"/>
       <c r="B57" s="18" t="n"/>
-      <c r="C57" s="60" t="n"/>
+      <c r="C57" s="105" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="18" t="n"/>
       <c r="B58" s="18" t="n"/>
-      <c r="C58" s="60" t="n"/>
+      <c r="C58" s="105" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="18" t="n"/>
       <c r="B59" s="18" t="n"/>
-      <c r="C59" s="60" t="n"/>
+      <c r="C59" s="105" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="18" t="n"/>
       <c r="B60" s="18" t="n"/>
-      <c r="C60" s="60" t="n"/>
+      <c r="C60" s="105" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3327,12 +4149,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="107" t="inlineStr">
         <is>
           <t>青</t>
         </is>
       </c>
-      <c r="D4" s="60" t="n"/>
+      <c r="D4" s="105" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -3345,12 +4167,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="C5" s="108" t="inlineStr">
         <is>
           <t>緑</t>
         </is>
       </c>
-      <c r="D5" s="60" t="n"/>
+      <c r="D5" s="105" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -3363,28 +4185,28 @@
           <t>○</t>
         </is>
       </c>
-      <c r="C6" s="64" t="inlineStr">
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>紫</t>
         </is>
       </c>
-      <c r="D6" s="60" t="n"/>
+      <c r="D6" s="105" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n"/>
       <c r="B7" s="18" t="n"/>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="110" t="inlineStr">
         <is>
           <t>橙</t>
         </is>
       </c>
-      <c r="D7" s="60" t="n"/>
+      <c r="D7" s="105" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n"/>
       <c r="B8" s="18" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="C8" s="105" t="n"/>
+      <c r="D8" s="106" t="inlineStr">
         <is>
           <t>5つめ以降の区分は色が付きません（白のまま）</t>
         </is>
@@ -3393,74 +4215,74 @@
     <row r="9">
       <c r="A9" s="18" t="n"/>
       <c r="B9" s="18" t="n"/>
-      <c r="C9" s="60" t="n"/>
-      <c r="D9" s="60" t="n"/>
+      <c r="C9" s="105" t="n"/>
+      <c r="D9" s="105" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="60" t="n"/>
-      <c r="D10" s="60" t="n"/>
+      <c r="C10" s="105" t="n"/>
+      <c r="D10" s="105" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n"/>
       <c r="B11" s="18" t="n"/>
-      <c r="C11" s="60" t="n"/>
-      <c r="D11" s="60" t="n"/>
+      <c r="C11" s="105" t="n"/>
+      <c r="D11" s="105" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n"/>
       <c r="B12" s="18" t="n"/>
-      <c r="C12" s="60" t="n"/>
-      <c r="D12" s="60" t="n"/>
+      <c r="C12" s="105" t="n"/>
+      <c r="D12" s="105" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n"/>
       <c r="B13" s="18" t="n"/>
-      <c r="C13" s="60" t="n"/>
-      <c r="D13" s="60" t="n"/>
+      <c r="C13" s="105" t="n"/>
+      <c r="D13" s="105" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
       <c r="B14" s="18" t="n"/>
-      <c r="C14" s="60" t="n"/>
-      <c r="D14" s="60" t="n"/>
+      <c r="C14" s="105" t="n"/>
+      <c r="D14" s="105" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
       <c r="B15" s="18" t="n"/>
-      <c r="C15" s="60" t="n"/>
-      <c r="D15" s="60" t="n"/>
+      <c r="C15" s="105" t="n"/>
+      <c r="D15" s="105" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n"/>
       <c r="B16" s="18" t="n"/>
-      <c r="C16" s="60" t="n"/>
-      <c r="D16" s="60" t="n"/>
+      <c r="C16" s="105" t="n"/>
+      <c r="D16" s="105" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n"/>
       <c r="B17" s="18" t="n"/>
-      <c r="C17" s="60" t="n"/>
-      <c r="D17" s="60" t="n"/>
+      <c r="C17" s="105" t="n"/>
+      <c r="D17" s="105" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n"/>
       <c r="B18" s="18" t="n"/>
-      <c r="C18" s="60" t="n"/>
-      <c r="D18" s="60" t="n"/>
+      <c r="C18" s="105" t="n"/>
+      <c r="D18" s="105" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n"/>
       <c r="B19" s="18" t="n"/>
-      <c r="C19" s="60" t="n"/>
-      <c r="D19" s="60" t="n"/>
+      <c r="C19" s="105" t="n"/>
+      <c r="D19" s="105" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n"/>
       <c r="B20" s="18" t="n"/>
-      <c r="C20" s="60" t="n"/>
-      <c r="D20" s="60" t="n"/>
+      <c r="C20" s="105" t="n"/>
+      <c r="D20" s="105" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3505,7 +4327,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n"/>
+      <c r="B4" s="105" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -3513,7 +4335,7 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="B5" s="60" t="n"/>
+      <c r="B5" s="105" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -3521,43 +4343,43 @@
           <t>調整中</t>
         </is>
       </c>
-      <c r="B6" s="60" t="n"/>
+      <c r="B6" s="105" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n"/>
-      <c r="B7" s="60" t="n"/>
+      <c r="B7" s="105" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n"/>
-      <c r="B8" s="60" t="n"/>
+      <c r="B8" s="105" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
-      <c r="B9" s="60" t="n"/>
+      <c r="B9" s="105" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
-      <c r="B10" s="60" t="n"/>
+      <c r="B10" s="105" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n"/>
-      <c r="B11" s="60" t="n"/>
+      <c r="B11" s="105" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n"/>
-      <c r="B12" s="60" t="n"/>
+      <c r="B12" s="105" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n"/>
-      <c r="B13" s="60" t="n"/>
+      <c r="B13" s="105" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
-      <c r="B14" s="60" t="n"/>
+      <c r="B14" s="105" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
-      <c r="B15" s="60" t="n"/>
+      <c r="B15" s="105" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3604,60 +4426,60 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="106" t="inlineStr">
         <is>
           <t>集計・稼働に入り、カレンダーでは区分の色で表示します</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>仮予約</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="106" t="inlineStr">
         <is>
           <t>集計には入りますが、カレンダーではグレーの斜体、帯表では白抜き、FAX表では「仮」</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>調整中</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="106" t="inlineStr">
         <is>
           <t>仮予約と同じ扱いです</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>利用済み</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="106" t="inlineStr">
         <is>
           <t>実績。確定と同じ扱いです</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>キャンセル</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="106" t="inlineStr">
         <is>
           <t>記録として残しますが、全ての集計・表示・重複判定から外れます</t>
         </is>
@@ -19936,31 +20758,31 @@
           <t>第1週</t>
         </is>
       </c>
-      <c r="B9" s="66">
+      <c r="B9" s="111">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+0)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+0)</f>
         <v/>
       </c>
-      <c r="C9" s="67">
+      <c r="C9" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+1)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+1)</f>
         <v/>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+2)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+2)</f>
         <v/>
       </c>
-      <c r="E9" s="67">
+      <c r="E9" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+3)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+3)</f>
         <v/>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+4)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+4)</f>
         <v/>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+5)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+5)</f>
         <v/>
       </c>
-      <c r="H9" s="68">
+      <c r="H9" s="113">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+6)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+6)</f>
         <v/>
       </c>
@@ -20289,31 +21111,31 @@
           <t>第2週</t>
         </is>
       </c>
-      <c r="B17" s="66">
+      <c r="B17" s="111">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+7)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+7)</f>
         <v/>
       </c>
-      <c r="C17" s="67">
+      <c r="C17" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+8)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+8)</f>
         <v/>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+9)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+9)</f>
         <v/>
       </c>
-      <c r="E17" s="67">
+      <c r="E17" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+10)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+10)</f>
         <v/>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+11)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+11)</f>
         <v/>
       </c>
-      <c r="G17" s="67">
+      <c r="G17" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+12)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+12)</f>
         <v/>
       </c>
-      <c r="H17" s="68">
+      <c r="H17" s="113">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+13)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+13)</f>
         <v/>
       </c>
@@ -20642,31 +21464,31 @@
           <t>第3週</t>
         </is>
       </c>
-      <c r="B25" s="66">
+      <c r="B25" s="111">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+14)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+14)</f>
         <v/>
       </c>
-      <c r="C25" s="67">
+      <c r="C25" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+15)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+15)</f>
         <v/>
       </c>
-      <c r="D25" s="67">
+      <c r="D25" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+16)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+16)</f>
         <v/>
       </c>
-      <c r="E25" s="67">
+      <c r="E25" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+17)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+17)</f>
         <v/>
       </c>
-      <c r="F25" s="67">
+      <c r="F25" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+18)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+18)</f>
         <v/>
       </c>
-      <c r="G25" s="67">
+      <c r="G25" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+19)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+19)</f>
         <v/>
       </c>
-      <c r="H25" s="68">
+      <c r="H25" s="113">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+20)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+20)</f>
         <v/>
       </c>
@@ -20995,31 +21817,31 @@
           <t>第4週</t>
         </is>
       </c>
-      <c r="B33" s="66">
+      <c r="B33" s="111">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+21)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+21)</f>
         <v/>
       </c>
-      <c r="C33" s="67">
+      <c r="C33" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+22)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+22)</f>
         <v/>
       </c>
-      <c r="D33" s="67">
+      <c r="D33" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+23)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+23)</f>
         <v/>
       </c>
-      <c r="E33" s="67">
+      <c r="E33" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+24)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+24)</f>
         <v/>
       </c>
-      <c r="F33" s="67">
+      <c r="F33" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+25)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+25)</f>
         <v/>
       </c>
-      <c r="G33" s="67">
+      <c r="G33" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+26)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+26)</f>
         <v/>
       </c>
-      <c r="H33" s="68">
+      <c r="H33" s="113">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+27)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+27)</f>
         <v/>
       </c>
@@ -21348,31 +22170,31 @@
           <t>第5週</t>
         </is>
       </c>
-      <c r="B41" s="66">
+      <c r="B41" s="111">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+28)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+28)</f>
         <v/>
       </c>
-      <c r="C41" s="67">
+      <c r="C41" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+29)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+29)</f>
         <v/>
       </c>
-      <c r="D41" s="67">
+      <c r="D41" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+30)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+30)</f>
         <v/>
       </c>
-      <c r="E41" s="67">
+      <c r="E41" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+31)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+31)</f>
         <v/>
       </c>
-      <c r="F41" s="67">
+      <c r="F41" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+32)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+32)</f>
         <v/>
       </c>
-      <c r="G41" s="67">
+      <c r="G41" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+33)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+33)</f>
         <v/>
       </c>
-      <c r="H41" s="68">
+      <c r="H41" s="113">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+34)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+34)</f>
         <v/>
       </c>
@@ -21701,31 +22523,31 @@
           <t>第6週</t>
         </is>
       </c>
-      <c r="B49" s="66">
+      <c r="B49" s="111">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+35)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+35)</f>
         <v/>
       </c>
-      <c r="C49" s="67">
+      <c r="C49" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+36)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+36)</f>
         <v/>
       </c>
-      <c r="D49" s="67">
+      <c r="D49" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+37)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+37)</f>
         <v/>
       </c>
-      <c r="E49" s="67">
+      <c r="E49" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+38)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+38)</f>
         <v/>
       </c>
-      <c r="F49" s="67">
+      <c r="F49" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+39)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+39)</f>
         <v/>
       </c>
-      <c r="G49" s="67">
+      <c r="G49" s="112">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+40)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+40)</f>
         <v/>
       </c>
-      <c r="H49" s="68">
+      <c r="H49" s="113">
         <f>IF(MONTH($B$4-WEEKDAY($B$4)+1+41)&lt;&gt;MONTH($B$4),"",$B$4-WEEKDAY($B$4)+1+41)</f>
         <v/>
       </c>
@@ -22546,10 +23368,10 @@
         <f>'02_カレンダー'!$B$4</f>
         <v/>
       </c>
-      <c r="C3" s="69" t="n"/>
-      <c r="D3" s="69" t="n"/>
-      <c r="E3" s="69" t="n"/>
-      <c r="F3" s="70" t="n"/>
+      <c r="C3" s="114" t="n"/>
+      <c r="D3" s="114" t="n"/>
+      <c r="E3" s="114" t="n"/>
+      <c r="F3" s="115" t="n"/>
       <c r="G3" s="40" t="inlineStr">
         <is>
           <t>02_カレンダー の対象月に連動します</t>
@@ -28158,65 +28980,65 @@
           <t>部屋</t>
         </is>
       </c>
-      <c r="C32" s="69" t="n"/>
-      <c r="D32" s="69" t="n"/>
-      <c r="E32" s="70" t="n"/>
+      <c r="C32" s="114" t="n"/>
+      <c r="D32" s="114" t="n"/>
+      <c r="E32" s="115" t="n"/>
       <c r="F32" s="33" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="70" t="n"/>
+      <c r="G32" s="114" t="n"/>
+      <c r="H32" s="115" t="n"/>
       <c r="I32" s="33" t="inlineStr">
         <is>
           <t>入所</t>
         </is>
       </c>
-      <c r="J32" s="69" t="n"/>
-      <c r="K32" s="69" t="n"/>
-      <c r="L32" s="69" t="n"/>
-      <c r="M32" s="69" t="n"/>
-      <c r="N32" s="70" t="n"/>
+      <c r="J32" s="114" t="n"/>
+      <c r="K32" s="114" t="n"/>
+      <c r="L32" s="114" t="n"/>
+      <c r="M32" s="114" t="n"/>
+      <c r="N32" s="115" t="n"/>
       <c r="O32" s="33" t="inlineStr">
         <is>
           <t>退所</t>
         </is>
       </c>
-      <c r="P32" s="69" t="n"/>
-      <c r="Q32" s="69" t="n"/>
-      <c r="R32" s="69" t="n"/>
-      <c r="S32" s="69" t="n"/>
-      <c r="T32" s="70" t="n"/>
+      <c r="P32" s="114" t="n"/>
+      <c r="Q32" s="114" t="n"/>
+      <c r="R32" s="114" t="n"/>
+      <c r="S32" s="114" t="n"/>
+      <c r="T32" s="115" t="n"/>
       <c r="U32" s="33" t="inlineStr">
         <is>
           <t>泊数</t>
         </is>
       </c>
-      <c r="V32" s="69" t="n"/>
-      <c r="W32" s="70" t="n"/>
+      <c r="V32" s="114" t="n"/>
+      <c r="W32" s="115" t="n"/>
       <c r="X32" s="33" t="inlineStr">
         <is>
           <t>食事</t>
         </is>
       </c>
-      <c r="Y32" s="69" t="n"/>
-      <c r="Z32" s="69" t="n"/>
-      <c r="AA32" s="70" t="n"/>
+      <c r="Y32" s="114" t="n"/>
+      <c r="Z32" s="114" t="n"/>
+      <c r="AA32" s="115" t="n"/>
       <c r="AB32" s="33" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="AC32" s="69" t="n"/>
-      <c r="AD32" s="70" t="n"/>
+      <c r="AC32" s="114" t="n"/>
+      <c r="AD32" s="115" t="n"/>
       <c r="AE32" s="33" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AF32" s="69" t="n"/>
-      <c r="AG32" s="70" t="n"/>
+      <c r="AF32" s="114" t="n"/>
+      <c r="AG32" s="115" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="46">
@@ -28227,58 +29049,58 @@
         <f>IF($AQ33=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ33)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ33)))</f>
         <v/>
       </c>
-      <c r="C33" s="69" t="n"/>
-      <c r="D33" s="69" t="n"/>
-      <c r="E33" s="70" t="n"/>
+      <c r="C33" s="114" t="n"/>
+      <c r="D33" s="114" t="n"/>
+      <c r="E33" s="115" t="n"/>
       <c r="F33" s="47">
         <f>IF($AQ33=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ33))</f>
         <v/>
       </c>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="70" t="n"/>
+      <c r="G33" s="114" t="n"/>
+      <c r="H33" s="115" t="n"/>
       <c r="I33" s="46">
         <f>IF($AQ33=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ33))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ33))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ33)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ33))</f>
         <v/>
       </c>
-      <c r="J33" s="69" t="n"/>
-      <c r="K33" s="69" t="n"/>
-      <c r="L33" s="69" t="n"/>
-      <c r="M33" s="69" t="n"/>
-      <c r="N33" s="70" t="n"/>
+      <c r="J33" s="114" t="n"/>
+      <c r="K33" s="114" t="n"/>
+      <c r="L33" s="114" t="n"/>
+      <c r="M33" s="114" t="n"/>
+      <c r="N33" s="115" t="n"/>
       <c r="O33" s="46">
         <f>IF($AQ33=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ33))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ33))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ33)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ33))</f>
         <v/>
       </c>
-      <c r="P33" s="69" t="n"/>
-      <c r="Q33" s="69" t="n"/>
-      <c r="R33" s="69" t="n"/>
-      <c r="S33" s="69" t="n"/>
-      <c r="T33" s="70" t="n"/>
+      <c r="P33" s="114" t="n"/>
+      <c r="Q33" s="114" t="n"/>
+      <c r="R33" s="114" t="n"/>
+      <c r="S33" s="114" t="n"/>
+      <c r="T33" s="115" t="n"/>
       <c r="U33" s="47">
         <f>IF($AQ33=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ33)=INDEX('01_予約入力'!$G$5:$G$204,$AQ33),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ33)-INDEX('01_予約入力'!$G$5:$G$204,$AQ33)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V33" s="69" t="n"/>
-      <c r="W33" s="70" t="n"/>
+      <c r="V33" s="114" t="n"/>
+      <c r="W33" s="115" t="n"/>
       <c r="X33" s="47">
         <f>IF($AQ33=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ33)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ33)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ33)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ33)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ33))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ33)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ33))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ33)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ33))))</f>
         <v/>
       </c>
-      <c r="Y33" s="69" t="n"/>
-      <c r="Z33" s="69" t="n"/>
-      <c r="AA33" s="70" t="n"/>
+      <c r="Y33" s="114" t="n"/>
+      <c r="Z33" s="114" t="n"/>
+      <c r="AA33" s="115" t="n"/>
       <c r="AB33" s="47">
         <f>IF($AQ33=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ33)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ33)))</f>
         <v/>
       </c>
-      <c r="AC33" s="69" t="n"/>
-      <c r="AD33" s="70" t="n"/>
+      <c r="AC33" s="114" t="n"/>
+      <c r="AD33" s="115" t="n"/>
       <c r="AE33" s="46">
         <f>IF($AQ33=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ33))</f>
         <v/>
       </c>
-      <c r="AF33" s="69" t="n"/>
-      <c r="AG33" s="70" t="n"/>
+      <c r="AF33" s="114" t="n"/>
+      <c r="AG33" s="115" t="n"/>
       <c r="AP33">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,1),"")</f>
         <v/>
@@ -28297,58 +29119,58 @@
         <f>IF($AQ34=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ34)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ34)))</f>
         <v/>
       </c>
-      <c r="C34" s="69" t="n"/>
-      <c r="D34" s="69" t="n"/>
-      <c r="E34" s="70" t="n"/>
+      <c r="C34" s="114" t="n"/>
+      <c r="D34" s="114" t="n"/>
+      <c r="E34" s="115" t="n"/>
       <c r="F34" s="47">
         <f>IF($AQ34=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ34))</f>
         <v/>
       </c>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="70" t="n"/>
+      <c r="G34" s="114" t="n"/>
+      <c r="H34" s="115" t="n"/>
       <c r="I34" s="46">
         <f>IF($AQ34=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ34))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ34))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ34)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ34))</f>
         <v/>
       </c>
-      <c r="J34" s="69" t="n"/>
-      <c r="K34" s="69" t="n"/>
-      <c r="L34" s="69" t="n"/>
-      <c r="M34" s="69" t="n"/>
-      <c r="N34" s="70" t="n"/>
+      <c r="J34" s="114" t="n"/>
+      <c r="K34" s="114" t="n"/>
+      <c r="L34" s="114" t="n"/>
+      <c r="M34" s="114" t="n"/>
+      <c r="N34" s="115" t="n"/>
       <c r="O34" s="46">
         <f>IF($AQ34=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ34))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ34))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ34)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ34))</f>
         <v/>
       </c>
-      <c r="P34" s="69" t="n"/>
-      <c r="Q34" s="69" t="n"/>
-      <c r="R34" s="69" t="n"/>
-      <c r="S34" s="69" t="n"/>
-      <c r="T34" s="70" t="n"/>
+      <c r="P34" s="114" t="n"/>
+      <c r="Q34" s="114" t="n"/>
+      <c r="R34" s="114" t="n"/>
+      <c r="S34" s="114" t="n"/>
+      <c r="T34" s="115" t="n"/>
       <c r="U34" s="47">
         <f>IF($AQ34=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ34)=INDEX('01_予約入力'!$G$5:$G$204,$AQ34),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ34)-INDEX('01_予約入力'!$G$5:$G$204,$AQ34)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V34" s="69" t="n"/>
-      <c r="W34" s="70" t="n"/>
+      <c r="V34" s="114" t="n"/>
+      <c r="W34" s="115" t="n"/>
       <c r="X34" s="47">
         <f>IF($AQ34=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ34)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ34)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ34)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ34)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ34))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ34)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ34))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ34)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ34))))</f>
         <v/>
       </c>
-      <c r="Y34" s="69" t="n"/>
-      <c r="Z34" s="69" t="n"/>
-      <c r="AA34" s="70" t="n"/>
+      <c r="Y34" s="114" t="n"/>
+      <c r="Z34" s="114" t="n"/>
+      <c r="AA34" s="115" t="n"/>
       <c r="AB34" s="47">
         <f>IF($AQ34=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ34)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ34)))</f>
         <v/>
       </c>
-      <c r="AC34" s="69" t="n"/>
-      <c r="AD34" s="70" t="n"/>
+      <c r="AC34" s="114" t="n"/>
+      <c r="AD34" s="115" t="n"/>
       <c r="AE34" s="46">
         <f>IF($AQ34=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ34))</f>
         <v/>
       </c>
-      <c r="AF34" s="69" t="n"/>
-      <c r="AG34" s="70" t="n"/>
+      <c r="AF34" s="114" t="n"/>
+      <c r="AG34" s="115" t="n"/>
       <c r="AP34">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,2),"")</f>
         <v/>
@@ -28367,58 +29189,58 @@
         <f>IF($AQ35=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ35)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ35)))</f>
         <v/>
       </c>
-      <c r="C35" s="69" t="n"/>
-      <c r="D35" s="69" t="n"/>
-      <c r="E35" s="70" t="n"/>
+      <c r="C35" s="114" t="n"/>
+      <c r="D35" s="114" t="n"/>
+      <c r="E35" s="115" t="n"/>
       <c r="F35" s="47">
         <f>IF($AQ35=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ35))</f>
         <v/>
       </c>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="70" t="n"/>
+      <c r="G35" s="114" t="n"/>
+      <c r="H35" s="115" t="n"/>
       <c r="I35" s="46">
         <f>IF($AQ35=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ35))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ35))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ35)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ35))</f>
         <v/>
       </c>
-      <c r="J35" s="69" t="n"/>
-      <c r="K35" s="69" t="n"/>
-      <c r="L35" s="69" t="n"/>
-      <c r="M35" s="69" t="n"/>
-      <c r="N35" s="70" t="n"/>
+      <c r="J35" s="114" t="n"/>
+      <c r="K35" s="114" t="n"/>
+      <c r="L35" s="114" t="n"/>
+      <c r="M35" s="114" t="n"/>
+      <c r="N35" s="115" t="n"/>
       <c r="O35" s="46">
         <f>IF($AQ35=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ35))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ35))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ35)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ35))</f>
         <v/>
       </c>
-      <c r="P35" s="69" t="n"/>
-      <c r="Q35" s="69" t="n"/>
-      <c r="R35" s="69" t="n"/>
-      <c r="S35" s="69" t="n"/>
-      <c r="T35" s="70" t="n"/>
+      <c r="P35" s="114" t="n"/>
+      <c r="Q35" s="114" t="n"/>
+      <c r="R35" s="114" t="n"/>
+      <c r="S35" s="114" t="n"/>
+      <c r="T35" s="115" t="n"/>
       <c r="U35" s="47">
         <f>IF($AQ35=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ35)=INDEX('01_予約入力'!$G$5:$G$204,$AQ35),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ35)-INDEX('01_予約入力'!$G$5:$G$204,$AQ35)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V35" s="69" t="n"/>
-      <c r="W35" s="70" t="n"/>
+      <c r="V35" s="114" t="n"/>
+      <c r="W35" s="115" t="n"/>
       <c r="X35" s="47">
         <f>IF($AQ35=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ35)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ35)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ35)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ35)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ35))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ35)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ35))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ35)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ35))))</f>
         <v/>
       </c>
-      <c r="Y35" s="69" t="n"/>
-      <c r="Z35" s="69" t="n"/>
-      <c r="AA35" s="70" t="n"/>
+      <c r="Y35" s="114" t="n"/>
+      <c r="Z35" s="114" t="n"/>
+      <c r="AA35" s="115" t="n"/>
       <c r="AB35" s="47">
         <f>IF($AQ35=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ35)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ35)))</f>
         <v/>
       </c>
-      <c r="AC35" s="69" t="n"/>
-      <c r="AD35" s="70" t="n"/>
+      <c r="AC35" s="114" t="n"/>
+      <c r="AD35" s="115" t="n"/>
       <c r="AE35" s="46">
         <f>IF($AQ35=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ35))</f>
         <v/>
       </c>
-      <c r="AF35" s="69" t="n"/>
-      <c r="AG35" s="70" t="n"/>
+      <c r="AF35" s="114" t="n"/>
+      <c r="AG35" s="115" t="n"/>
       <c r="AP35">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,3),"")</f>
         <v/>
@@ -28437,58 +29259,58 @@
         <f>IF($AQ36=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ36)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ36)))</f>
         <v/>
       </c>
-      <c r="C36" s="69" t="n"/>
-      <c r="D36" s="69" t="n"/>
-      <c r="E36" s="70" t="n"/>
+      <c r="C36" s="114" t="n"/>
+      <c r="D36" s="114" t="n"/>
+      <c r="E36" s="115" t="n"/>
       <c r="F36" s="47">
         <f>IF($AQ36=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ36))</f>
         <v/>
       </c>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="70" t="n"/>
+      <c r="G36" s="114" t="n"/>
+      <c r="H36" s="115" t="n"/>
       <c r="I36" s="46">
         <f>IF($AQ36=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ36))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ36))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ36)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ36))</f>
         <v/>
       </c>
-      <c r="J36" s="69" t="n"/>
-      <c r="K36" s="69" t="n"/>
-      <c r="L36" s="69" t="n"/>
-      <c r="M36" s="69" t="n"/>
-      <c r="N36" s="70" t="n"/>
+      <c r="J36" s="114" t="n"/>
+      <c r="K36" s="114" t="n"/>
+      <c r="L36" s="114" t="n"/>
+      <c r="M36" s="114" t="n"/>
+      <c r="N36" s="115" t="n"/>
       <c r="O36" s="46">
         <f>IF($AQ36=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ36))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ36))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ36)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ36))</f>
         <v/>
       </c>
-      <c r="P36" s="69" t="n"/>
-      <c r="Q36" s="69" t="n"/>
-      <c r="R36" s="69" t="n"/>
-      <c r="S36" s="69" t="n"/>
-      <c r="T36" s="70" t="n"/>
+      <c r="P36" s="114" t="n"/>
+      <c r="Q36" s="114" t="n"/>
+      <c r="R36" s="114" t="n"/>
+      <c r="S36" s="114" t="n"/>
+      <c r="T36" s="115" t="n"/>
       <c r="U36" s="47">
         <f>IF($AQ36=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ36)=INDEX('01_予約入力'!$G$5:$G$204,$AQ36),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ36)-INDEX('01_予約入力'!$G$5:$G$204,$AQ36)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V36" s="69" t="n"/>
-      <c r="W36" s="70" t="n"/>
+      <c r="V36" s="114" t="n"/>
+      <c r="W36" s="115" t="n"/>
       <c r="X36" s="47">
         <f>IF($AQ36=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ36)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ36)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ36)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ36)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ36))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ36)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ36))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ36)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ36))))</f>
         <v/>
       </c>
-      <c r="Y36" s="69" t="n"/>
-      <c r="Z36" s="69" t="n"/>
-      <c r="AA36" s="70" t="n"/>
+      <c r="Y36" s="114" t="n"/>
+      <c r="Z36" s="114" t="n"/>
+      <c r="AA36" s="115" t="n"/>
       <c r="AB36" s="47">
         <f>IF($AQ36=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ36)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ36)))</f>
         <v/>
       </c>
-      <c r="AC36" s="69" t="n"/>
-      <c r="AD36" s="70" t="n"/>
+      <c r="AC36" s="114" t="n"/>
+      <c r="AD36" s="115" t="n"/>
       <c r="AE36" s="46">
         <f>IF($AQ36=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ36))</f>
         <v/>
       </c>
-      <c r="AF36" s="69" t="n"/>
-      <c r="AG36" s="70" t="n"/>
+      <c r="AF36" s="114" t="n"/>
+      <c r="AG36" s="115" t="n"/>
       <c r="AP36">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,4),"")</f>
         <v/>
@@ -28507,58 +29329,58 @@
         <f>IF($AQ37=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ37)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ37)))</f>
         <v/>
       </c>
-      <c r="C37" s="69" t="n"/>
-      <c r="D37" s="69" t="n"/>
-      <c r="E37" s="70" t="n"/>
+      <c r="C37" s="114" t="n"/>
+      <c r="D37" s="114" t="n"/>
+      <c r="E37" s="115" t="n"/>
       <c r="F37" s="47">
         <f>IF($AQ37=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ37))</f>
         <v/>
       </c>
-      <c r="G37" s="69" t="n"/>
-      <c r="H37" s="70" t="n"/>
+      <c r="G37" s="114" t="n"/>
+      <c r="H37" s="115" t="n"/>
       <c r="I37" s="46">
         <f>IF($AQ37=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ37))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ37))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ37)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ37))</f>
         <v/>
       </c>
-      <c r="J37" s="69" t="n"/>
-      <c r="K37" s="69" t="n"/>
-      <c r="L37" s="69" t="n"/>
-      <c r="M37" s="69" t="n"/>
-      <c r="N37" s="70" t="n"/>
+      <c r="J37" s="114" t="n"/>
+      <c r="K37" s="114" t="n"/>
+      <c r="L37" s="114" t="n"/>
+      <c r="M37" s="114" t="n"/>
+      <c r="N37" s="115" t="n"/>
       <c r="O37" s="46">
         <f>IF($AQ37=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ37))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ37))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ37)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ37))</f>
         <v/>
       </c>
-      <c r="P37" s="69" t="n"/>
-      <c r="Q37" s="69" t="n"/>
-      <c r="R37" s="69" t="n"/>
-      <c r="S37" s="69" t="n"/>
-      <c r="T37" s="70" t="n"/>
+      <c r="P37" s="114" t="n"/>
+      <c r="Q37" s="114" t="n"/>
+      <c r="R37" s="114" t="n"/>
+      <c r="S37" s="114" t="n"/>
+      <c r="T37" s="115" t="n"/>
       <c r="U37" s="47">
         <f>IF($AQ37=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ37)=INDEX('01_予約入力'!$G$5:$G$204,$AQ37),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ37)-INDEX('01_予約入力'!$G$5:$G$204,$AQ37)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V37" s="69" t="n"/>
-      <c r="W37" s="70" t="n"/>
+      <c r="V37" s="114" t="n"/>
+      <c r="W37" s="115" t="n"/>
       <c r="X37" s="47">
         <f>IF($AQ37=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ37)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ37)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ37)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ37)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ37))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ37)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ37))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ37)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ37))))</f>
         <v/>
       </c>
-      <c r="Y37" s="69" t="n"/>
-      <c r="Z37" s="69" t="n"/>
-      <c r="AA37" s="70" t="n"/>
+      <c r="Y37" s="114" t="n"/>
+      <c r="Z37" s="114" t="n"/>
+      <c r="AA37" s="115" t="n"/>
       <c r="AB37" s="47">
         <f>IF($AQ37=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ37)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ37)))</f>
         <v/>
       </c>
-      <c r="AC37" s="69" t="n"/>
-      <c r="AD37" s="70" t="n"/>
+      <c r="AC37" s="114" t="n"/>
+      <c r="AD37" s="115" t="n"/>
       <c r="AE37" s="46">
         <f>IF($AQ37=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ37))</f>
         <v/>
       </c>
-      <c r="AF37" s="69" t="n"/>
-      <c r="AG37" s="70" t="n"/>
+      <c r="AF37" s="114" t="n"/>
+      <c r="AG37" s="115" t="n"/>
       <c r="AP37">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,5),"")</f>
         <v/>
@@ -28577,58 +29399,58 @@
         <f>IF($AQ38=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ38)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ38)))</f>
         <v/>
       </c>
-      <c r="C38" s="69" t="n"/>
-      <c r="D38" s="69" t="n"/>
-      <c r="E38" s="70" t="n"/>
+      <c r="C38" s="114" t="n"/>
+      <c r="D38" s="114" t="n"/>
+      <c r="E38" s="115" t="n"/>
       <c r="F38" s="47">
         <f>IF($AQ38=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ38))</f>
         <v/>
       </c>
-      <c r="G38" s="69" t="n"/>
-      <c r="H38" s="70" t="n"/>
+      <c r="G38" s="114" t="n"/>
+      <c r="H38" s="115" t="n"/>
       <c r="I38" s="46">
         <f>IF($AQ38=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ38))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ38))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ38)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ38))</f>
         <v/>
       </c>
-      <c r="J38" s="69" t="n"/>
-      <c r="K38" s="69" t="n"/>
-      <c r="L38" s="69" t="n"/>
-      <c r="M38" s="69" t="n"/>
-      <c r="N38" s="70" t="n"/>
+      <c r="J38" s="114" t="n"/>
+      <c r="K38" s="114" t="n"/>
+      <c r="L38" s="114" t="n"/>
+      <c r="M38" s="114" t="n"/>
+      <c r="N38" s="115" t="n"/>
       <c r="O38" s="46">
         <f>IF($AQ38=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ38))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ38))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ38)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ38))</f>
         <v/>
       </c>
-      <c r="P38" s="69" t="n"/>
-      <c r="Q38" s="69" t="n"/>
-      <c r="R38" s="69" t="n"/>
-      <c r="S38" s="69" t="n"/>
-      <c r="T38" s="70" t="n"/>
+      <c r="P38" s="114" t="n"/>
+      <c r="Q38" s="114" t="n"/>
+      <c r="R38" s="114" t="n"/>
+      <c r="S38" s="114" t="n"/>
+      <c r="T38" s="115" t="n"/>
       <c r="U38" s="47">
         <f>IF($AQ38=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ38)=INDEX('01_予約入力'!$G$5:$G$204,$AQ38),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ38)-INDEX('01_予約入力'!$G$5:$G$204,$AQ38)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V38" s="69" t="n"/>
-      <c r="W38" s="70" t="n"/>
+      <c r="V38" s="114" t="n"/>
+      <c r="W38" s="115" t="n"/>
       <c r="X38" s="47">
         <f>IF($AQ38=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ38)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ38)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ38)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ38)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ38))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ38)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ38))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ38)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ38))))</f>
         <v/>
       </c>
-      <c r="Y38" s="69" t="n"/>
-      <c r="Z38" s="69" t="n"/>
-      <c r="AA38" s="70" t="n"/>
+      <c r="Y38" s="114" t="n"/>
+      <c r="Z38" s="114" t="n"/>
+      <c r="AA38" s="115" t="n"/>
       <c r="AB38" s="47">
         <f>IF($AQ38=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ38)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ38)))</f>
         <v/>
       </c>
-      <c r="AC38" s="69" t="n"/>
-      <c r="AD38" s="70" t="n"/>
+      <c r="AC38" s="114" t="n"/>
+      <c r="AD38" s="115" t="n"/>
       <c r="AE38" s="46">
         <f>IF($AQ38=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ38))</f>
         <v/>
       </c>
-      <c r="AF38" s="69" t="n"/>
-      <c r="AG38" s="70" t="n"/>
+      <c r="AF38" s="114" t="n"/>
+      <c r="AG38" s="115" t="n"/>
       <c r="AP38">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,6),"")</f>
         <v/>
@@ -28647,58 +29469,58 @@
         <f>IF($AQ39=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ39)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ39)))</f>
         <v/>
       </c>
-      <c r="C39" s="69" t="n"/>
-      <c r="D39" s="69" t="n"/>
-      <c r="E39" s="70" t="n"/>
+      <c r="C39" s="114" t="n"/>
+      <c r="D39" s="114" t="n"/>
+      <c r="E39" s="115" t="n"/>
       <c r="F39" s="47">
         <f>IF($AQ39=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ39))</f>
         <v/>
       </c>
-      <c r="G39" s="69" t="n"/>
-      <c r="H39" s="70" t="n"/>
+      <c r="G39" s="114" t="n"/>
+      <c r="H39" s="115" t="n"/>
       <c r="I39" s="46">
         <f>IF($AQ39=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ39))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ39))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ39)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ39))</f>
         <v/>
       </c>
-      <c r="J39" s="69" t="n"/>
-      <c r="K39" s="69" t="n"/>
-      <c r="L39" s="69" t="n"/>
-      <c r="M39" s="69" t="n"/>
-      <c r="N39" s="70" t="n"/>
+      <c r="J39" s="114" t="n"/>
+      <c r="K39" s="114" t="n"/>
+      <c r="L39" s="114" t="n"/>
+      <c r="M39" s="114" t="n"/>
+      <c r="N39" s="115" t="n"/>
       <c r="O39" s="46">
         <f>IF($AQ39=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ39))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ39))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ39)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ39))</f>
         <v/>
       </c>
-      <c r="P39" s="69" t="n"/>
-      <c r="Q39" s="69" t="n"/>
-      <c r="R39" s="69" t="n"/>
-      <c r="S39" s="69" t="n"/>
-      <c r="T39" s="70" t="n"/>
+      <c r="P39" s="114" t="n"/>
+      <c r="Q39" s="114" t="n"/>
+      <c r="R39" s="114" t="n"/>
+      <c r="S39" s="114" t="n"/>
+      <c r="T39" s="115" t="n"/>
       <c r="U39" s="47">
         <f>IF($AQ39=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ39)=INDEX('01_予約入力'!$G$5:$G$204,$AQ39),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ39)-INDEX('01_予約入力'!$G$5:$G$204,$AQ39)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V39" s="69" t="n"/>
-      <c r="W39" s="70" t="n"/>
+      <c r="V39" s="114" t="n"/>
+      <c r="W39" s="115" t="n"/>
       <c r="X39" s="47">
         <f>IF($AQ39=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ39)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ39)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ39)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ39)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ39))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ39)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ39))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ39)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ39))))</f>
         <v/>
       </c>
-      <c r="Y39" s="69" t="n"/>
-      <c r="Z39" s="69" t="n"/>
-      <c r="AA39" s="70" t="n"/>
+      <c r="Y39" s="114" t="n"/>
+      <c r="Z39" s="114" t="n"/>
+      <c r="AA39" s="115" t="n"/>
       <c r="AB39" s="47">
         <f>IF($AQ39=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ39)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ39)))</f>
         <v/>
       </c>
-      <c r="AC39" s="69" t="n"/>
-      <c r="AD39" s="70" t="n"/>
+      <c r="AC39" s="114" t="n"/>
+      <c r="AD39" s="115" t="n"/>
       <c r="AE39" s="46">
         <f>IF($AQ39=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ39))</f>
         <v/>
       </c>
-      <c r="AF39" s="69" t="n"/>
-      <c r="AG39" s="70" t="n"/>
+      <c r="AF39" s="114" t="n"/>
+      <c r="AG39" s="115" t="n"/>
       <c r="AP39">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,7),"")</f>
         <v/>
@@ -28717,58 +29539,58 @@
         <f>IF($AQ40=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ40)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ40)))</f>
         <v/>
       </c>
-      <c r="C40" s="69" t="n"/>
-      <c r="D40" s="69" t="n"/>
-      <c r="E40" s="70" t="n"/>
+      <c r="C40" s="114" t="n"/>
+      <c r="D40" s="114" t="n"/>
+      <c r="E40" s="115" t="n"/>
       <c r="F40" s="47">
         <f>IF($AQ40=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ40))</f>
         <v/>
       </c>
-      <c r="G40" s="69" t="n"/>
-      <c r="H40" s="70" t="n"/>
+      <c r="G40" s="114" t="n"/>
+      <c r="H40" s="115" t="n"/>
       <c r="I40" s="46">
         <f>IF($AQ40=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ40))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ40))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ40)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ40))</f>
         <v/>
       </c>
-      <c r="J40" s="69" t="n"/>
-      <c r="K40" s="69" t="n"/>
-      <c r="L40" s="69" t="n"/>
-      <c r="M40" s="69" t="n"/>
-      <c r="N40" s="70" t="n"/>
+      <c r="J40" s="114" t="n"/>
+      <c r="K40" s="114" t="n"/>
+      <c r="L40" s="114" t="n"/>
+      <c r="M40" s="114" t="n"/>
+      <c r="N40" s="115" t="n"/>
       <c r="O40" s="46">
         <f>IF($AQ40=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ40))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ40))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ40)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ40))</f>
         <v/>
       </c>
-      <c r="P40" s="69" t="n"/>
-      <c r="Q40" s="69" t="n"/>
-      <c r="R40" s="69" t="n"/>
-      <c r="S40" s="69" t="n"/>
-      <c r="T40" s="70" t="n"/>
+      <c r="P40" s="114" t="n"/>
+      <c r="Q40" s="114" t="n"/>
+      <c r="R40" s="114" t="n"/>
+      <c r="S40" s="114" t="n"/>
+      <c r="T40" s="115" t="n"/>
       <c r="U40" s="47">
         <f>IF($AQ40=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ40)=INDEX('01_予約入力'!$G$5:$G$204,$AQ40),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ40)-INDEX('01_予約入力'!$G$5:$G$204,$AQ40)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V40" s="69" t="n"/>
-      <c r="W40" s="70" t="n"/>
+      <c r="V40" s="114" t="n"/>
+      <c r="W40" s="115" t="n"/>
       <c r="X40" s="47">
         <f>IF($AQ40=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ40)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ40)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ40)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ40)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ40))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ40)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ40))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ40)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ40))))</f>
         <v/>
       </c>
-      <c r="Y40" s="69" t="n"/>
-      <c r="Z40" s="69" t="n"/>
-      <c r="AA40" s="70" t="n"/>
+      <c r="Y40" s="114" t="n"/>
+      <c r="Z40" s="114" t="n"/>
+      <c r="AA40" s="115" t="n"/>
       <c r="AB40" s="47">
         <f>IF($AQ40=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ40)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ40)))</f>
         <v/>
       </c>
-      <c r="AC40" s="69" t="n"/>
-      <c r="AD40" s="70" t="n"/>
+      <c r="AC40" s="114" t="n"/>
+      <c r="AD40" s="115" t="n"/>
       <c r="AE40" s="46">
         <f>IF($AQ40=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ40))</f>
         <v/>
       </c>
-      <c r="AF40" s="69" t="n"/>
-      <c r="AG40" s="70" t="n"/>
+      <c r="AF40" s="114" t="n"/>
+      <c r="AG40" s="115" t="n"/>
       <c r="AP40">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,8),"")</f>
         <v/>
@@ -28787,58 +29609,58 @@
         <f>IF($AQ41=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ41)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ41)))</f>
         <v/>
       </c>
-      <c r="C41" s="69" t="n"/>
-      <c r="D41" s="69" t="n"/>
-      <c r="E41" s="70" t="n"/>
+      <c r="C41" s="114" t="n"/>
+      <c r="D41" s="114" t="n"/>
+      <c r="E41" s="115" t="n"/>
       <c r="F41" s="47">
         <f>IF($AQ41=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ41))</f>
         <v/>
       </c>
-      <c r="G41" s="69" t="n"/>
-      <c r="H41" s="70" t="n"/>
+      <c r="G41" s="114" t="n"/>
+      <c r="H41" s="115" t="n"/>
       <c r="I41" s="46">
         <f>IF($AQ41=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ41))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ41))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ41)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ41))</f>
         <v/>
       </c>
-      <c r="J41" s="69" t="n"/>
-      <c r="K41" s="69" t="n"/>
-      <c r="L41" s="69" t="n"/>
-      <c r="M41" s="69" t="n"/>
-      <c r="N41" s="70" t="n"/>
+      <c r="J41" s="114" t="n"/>
+      <c r="K41" s="114" t="n"/>
+      <c r="L41" s="114" t="n"/>
+      <c r="M41" s="114" t="n"/>
+      <c r="N41" s="115" t="n"/>
       <c r="O41" s="46">
         <f>IF($AQ41=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ41))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ41))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ41)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ41))</f>
         <v/>
       </c>
-      <c r="P41" s="69" t="n"/>
-      <c r="Q41" s="69" t="n"/>
-      <c r="R41" s="69" t="n"/>
-      <c r="S41" s="69" t="n"/>
-      <c r="T41" s="70" t="n"/>
+      <c r="P41" s="114" t="n"/>
+      <c r="Q41" s="114" t="n"/>
+      <c r="R41" s="114" t="n"/>
+      <c r="S41" s="114" t="n"/>
+      <c r="T41" s="115" t="n"/>
       <c r="U41" s="47">
         <f>IF($AQ41=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ41)=INDEX('01_予約入力'!$G$5:$G$204,$AQ41),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ41)-INDEX('01_予約入力'!$G$5:$G$204,$AQ41)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V41" s="69" t="n"/>
-      <c r="W41" s="70" t="n"/>
+      <c r="V41" s="114" t="n"/>
+      <c r="W41" s="115" t="n"/>
       <c r="X41" s="47">
         <f>IF($AQ41=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ41)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ41)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ41)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ41)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ41))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ41)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ41))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ41)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ41))))</f>
         <v/>
       </c>
-      <c r="Y41" s="69" t="n"/>
-      <c r="Z41" s="69" t="n"/>
-      <c r="AA41" s="70" t="n"/>
+      <c r="Y41" s="114" t="n"/>
+      <c r="Z41" s="114" t="n"/>
+      <c r="AA41" s="115" t="n"/>
       <c r="AB41" s="47">
         <f>IF($AQ41=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ41)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ41)))</f>
         <v/>
       </c>
-      <c r="AC41" s="69" t="n"/>
-      <c r="AD41" s="70" t="n"/>
+      <c r="AC41" s="114" t="n"/>
+      <c r="AD41" s="115" t="n"/>
       <c r="AE41" s="46">
         <f>IF($AQ41=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ41))</f>
         <v/>
       </c>
-      <c r="AF41" s="69" t="n"/>
-      <c r="AG41" s="70" t="n"/>
+      <c r="AF41" s="114" t="n"/>
+      <c r="AG41" s="115" t="n"/>
       <c r="AP41">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,9),"")</f>
         <v/>
@@ -28857,58 +29679,58 @@
         <f>IF($AQ42=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ42)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ42)))</f>
         <v/>
       </c>
-      <c r="C42" s="69" t="n"/>
-      <c r="D42" s="69" t="n"/>
-      <c r="E42" s="70" t="n"/>
+      <c r="C42" s="114" t="n"/>
+      <c r="D42" s="114" t="n"/>
+      <c r="E42" s="115" t="n"/>
       <c r="F42" s="47">
         <f>IF($AQ42=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ42))</f>
         <v/>
       </c>
-      <c r="G42" s="69" t="n"/>
-      <c r="H42" s="70" t="n"/>
+      <c r="G42" s="114" t="n"/>
+      <c r="H42" s="115" t="n"/>
       <c r="I42" s="46">
         <f>IF($AQ42=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ42))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ42))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ42)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ42))</f>
         <v/>
       </c>
-      <c r="J42" s="69" t="n"/>
-      <c r="K42" s="69" t="n"/>
-      <c r="L42" s="69" t="n"/>
-      <c r="M42" s="69" t="n"/>
-      <c r="N42" s="70" t="n"/>
+      <c r="J42" s="114" t="n"/>
+      <c r="K42" s="114" t="n"/>
+      <c r="L42" s="114" t="n"/>
+      <c r="M42" s="114" t="n"/>
+      <c r="N42" s="115" t="n"/>
       <c r="O42" s="46">
         <f>IF($AQ42=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ42))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ42))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ42)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ42))</f>
         <v/>
       </c>
-      <c r="P42" s="69" t="n"/>
-      <c r="Q42" s="69" t="n"/>
-      <c r="R42" s="69" t="n"/>
-      <c r="S42" s="69" t="n"/>
-      <c r="T42" s="70" t="n"/>
+      <c r="P42" s="114" t="n"/>
+      <c r="Q42" s="114" t="n"/>
+      <c r="R42" s="114" t="n"/>
+      <c r="S42" s="114" t="n"/>
+      <c r="T42" s="115" t="n"/>
       <c r="U42" s="47">
         <f>IF($AQ42=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ42)=INDEX('01_予約入力'!$G$5:$G$204,$AQ42),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ42)-INDEX('01_予約入力'!$G$5:$G$204,$AQ42)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V42" s="69" t="n"/>
-      <c r="W42" s="70" t="n"/>
+      <c r="V42" s="114" t="n"/>
+      <c r="W42" s="115" t="n"/>
       <c r="X42" s="47">
         <f>IF($AQ42=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ42)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ42)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ42)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ42)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ42))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ42)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ42))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ42)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ42))))</f>
         <v/>
       </c>
-      <c r="Y42" s="69" t="n"/>
-      <c r="Z42" s="69" t="n"/>
-      <c r="AA42" s="70" t="n"/>
+      <c r="Y42" s="114" t="n"/>
+      <c r="Z42" s="114" t="n"/>
+      <c r="AA42" s="115" t="n"/>
       <c r="AB42" s="47">
         <f>IF($AQ42=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ42)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ42)))</f>
         <v/>
       </c>
-      <c r="AC42" s="69" t="n"/>
-      <c r="AD42" s="70" t="n"/>
+      <c r="AC42" s="114" t="n"/>
+      <c r="AD42" s="115" t="n"/>
       <c r="AE42" s="46">
         <f>IF($AQ42=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ42))</f>
         <v/>
       </c>
-      <c r="AF42" s="69" t="n"/>
-      <c r="AG42" s="70" t="n"/>
+      <c r="AF42" s="114" t="n"/>
+      <c r="AG42" s="115" t="n"/>
       <c r="AP42">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,10),"")</f>
         <v/>
@@ -28927,58 +29749,58 @@
         <f>IF($AQ43=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ43)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ43)))</f>
         <v/>
       </c>
-      <c r="C43" s="69" t="n"/>
-      <c r="D43" s="69" t="n"/>
-      <c r="E43" s="70" t="n"/>
+      <c r="C43" s="114" t="n"/>
+      <c r="D43" s="114" t="n"/>
+      <c r="E43" s="115" t="n"/>
       <c r="F43" s="47">
         <f>IF($AQ43=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ43))</f>
         <v/>
       </c>
-      <c r="G43" s="69" t="n"/>
-      <c r="H43" s="70" t="n"/>
+      <c r="G43" s="114" t="n"/>
+      <c r="H43" s="115" t="n"/>
       <c r="I43" s="46">
         <f>IF($AQ43=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ43))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ43))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ43)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ43))</f>
         <v/>
       </c>
-      <c r="J43" s="69" t="n"/>
-      <c r="K43" s="69" t="n"/>
-      <c r="L43" s="69" t="n"/>
-      <c r="M43" s="69" t="n"/>
-      <c r="N43" s="70" t="n"/>
+      <c r="J43" s="114" t="n"/>
+      <c r="K43" s="114" t="n"/>
+      <c r="L43" s="114" t="n"/>
+      <c r="M43" s="114" t="n"/>
+      <c r="N43" s="115" t="n"/>
       <c r="O43" s="46">
         <f>IF($AQ43=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ43))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ43))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ43)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ43))</f>
         <v/>
       </c>
-      <c r="P43" s="69" t="n"/>
-      <c r="Q43" s="69" t="n"/>
-      <c r="R43" s="69" t="n"/>
-      <c r="S43" s="69" t="n"/>
-      <c r="T43" s="70" t="n"/>
+      <c r="P43" s="114" t="n"/>
+      <c r="Q43" s="114" t="n"/>
+      <c r="R43" s="114" t="n"/>
+      <c r="S43" s="114" t="n"/>
+      <c r="T43" s="115" t="n"/>
       <c r="U43" s="47">
         <f>IF($AQ43=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ43)=INDEX('01_予約入力'!$G$5:$G$204,$AQ43),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ43)-INDEX('01_予約入力'!$G$5:$G$204,$AQ43)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V43" s="69" t="n"/>
-      <c r="W43" s="70" t="n"/>
+      <c r="V43" s="114" t="n"/>
+      <c r="W43" s="115" t="n"/>
       <c r="X43" s="47">
         <f>IF($AQ43=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ43)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ43)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ43)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ43)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ43))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ43)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ43))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ43)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ43))))</f>
         <v/>
       </c>
-      <c r="Y43" s="69" t="n"/>
-      <c r="Z43" s="69" t="n"/>
-      <c r="AA43" s="70" t="n"/>
+      <c r="Y43" s="114" t="n"/>
+      <c r="Z43" s="114" t="n"/>
+      <c r="AA43" s="115" t="n"/>
       <c r="AB43" s="47">
         <f>IF($AQ43=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ43)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ43)))</f>
         <v/>
       </c>
-      <c r="AC43" s="69" t="n"/>
-      <c r="AD43" s="70" t="n"/>
+      <c r="AC43" s="114" t="n"/>
+      <c r="AD43" s="115" t="n"/>
       <c r="AE43" s="46">
         <f>IF($AQ43=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ43))</f>
         <v/>
       </c>
-      <c r="AF43" s="69" t="n"/>
-      <c r="AG43" s="70" t="n"/>
+      <c r="AF43" s="114" t="n"/>
+      <c r="AG43" s="115" t="n"/>
       <c r="AP43">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,11),"")</f>
         <v/>
@@ -28997,58 +29819,58 @@
         <f>IF($AQ44=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ44)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ44)))</f>
         <v/>
       </c>
-      <c r="C44" s="69" t="n"/>
-      <c r="D44" s="69" t="n"/>
-      <c r="E44" s="70" t="n"/>
+      <c r="C44" s="114" t="n"/>
+      <c r="D44" s="114" t="n"/>
+      <c r="E44" s="115" t="n"/>
       <c r="F44" s="47">
         <f>IF($AQ44=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ44))</f>
         <v/>
       </c>
-      <c r="G44" s="69" t="n"/>
-      <c r="H44" s="70" t="n"/>
+      <c r="G44" s="114" t="n"/>
+      <c r="H44" s="115" t="n"/>
       <c r="I44" s="46">
         <f>IF($AQ44=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ44))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ44))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ44)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ44))</f>
         <v/>
       </c>
-      <c r="J44" s="69" t="n"/>
-      <c r="K44" s="69" t="n"/>
-      <c r="L44" s="69" t="n"/>
-      <c r="M44" s="69" t="n"/>
-      <c r="N44" s="70" t="n"/>
+      <c r="J44" s="114" t="n"/>
+      <c r="K44" s="114" t="n"/>
+      <c r="L44" s="114" t="n"/>
+      <c r="M44" s="114" t="n"/>
+      <c r="N44" s="115" t="n"/>
       <c r="O44" s="46">
         <f>IF($AQ44=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ44))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ44))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ44)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ44))</f>
         <v/>
       </c>
-      <c r="P44" s="69" t="n"/>
-      <c r="Q44" s="69" t="n"/>
-      <c r="R44" s="69" t="n"/>
-      <c r="S44" s="69" t="n"/>
-      <c r="T44" s="70" t="n"/>
+      <c r="P44" s="114" t="n"/>
+      <c r="Q44" s="114" t="n"/>
+      <c r="R44" s="114" t="n"/>
+      <c r="S44" s="114" t="n"/>
+      <c r="T44" s="115" t="n"/>
       <c r="U44" s="47">
         <f>IF($AQ44=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ44)=INDEX('01_予約入力'!$G$5:$G$204,$AQ44),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ44)-INDEX('01_予約入力'!$G$5:$G$204,$AQ44)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V44" s="69" t="n"/>
-      <c r="W44" s="70" t="n"/>
+      <c r="V44" s="114" t="n"/>
+      <c r="W44" s="115" t="n"/>
       <c r="X44" s="47">
         <f>IF($AQ44=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ44)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ44)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ44)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ44)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ44))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ44)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ44))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ44)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ44))))</f>
         <v/>
       </c>
-      <c r="Y44" s="69" t="n"/>
-      <c r="Z44" s="69" t="n"/>
-      <c r="AA44" s="70" t="n"/>
+      <c r="Y44" s="114" t="n"/>
+      <c r="Z44" s="114" t="n"/>
+      <c r="AA44" s="115" t="n"/>
       <c r="AB44" s="47">
         <f>IF($AQ44=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ44)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ44)))</f>
         <v/>
       </c>
-      <c r="AC44" s="69" t="n"/>
-      <c r="AD44" s="70" t="n"/>
+      <c r="AC44" s="114" t="n"/>
+      <c r="AD44" s="115" t="n"/>
       <c r="AE44" s="46">
         <f>IF($AQ44=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ44))</f>
         <v/>
       </c>
-      <c r="AF44" s="69" t="n"/>
-      <c r="AG44" s="70" t="n"/>
+      <c r="AF44" s="114" t="n"/>
+      <c r="AG44" s="115" t="n"/>
       <c r="AP44">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,12),"")</f>
         <v/>
@@ -29067,58 +29889,58 @@
         <f>IF($AQ45=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ45)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ45)))</f>
         <v/>
       </c>
-      <c r="C45" s="69" t="n"/>
-      <c r="D45" s="69" t="n"/>
-      <c r="E45" s="70" t="n"/>
+      <c r="C45" s="114" t="n"/>
+      <c r="D45" s="114" t="n"/>
+      <c r="E45" s="115" t="n"/>
       <c r="F45" s="47">
         <f>IF($AQ45=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ45))</f>
         <v/>
       </c>
-      <c r="G45" s="69" t="n"/>
-      <c r="H45" s="70" t="n"/>
+      <c r="G45" s="114" t="n"/>
+      <c r="H45" s="115" t="n"/>
       <c r="I45" s="46">
         <f>IF($AQ45=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ45))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ45))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ45)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ45))</f>
         <v/>
       </c>
-      <c r="J45" s="69" t="n"/>
-      <c r="K45" s="69" t="n"/>
-      <c r="L45" s="69" t="n"/>
-      <c r="M45" s="69" t="n"/>
-      <c r="N45" s="70" t="n"/>
+      <c r="J45" s="114" t="n"/>
+      <c r="K45" s="114" t="n"/>
+      <c r="L45" s="114" t="n"/>
+      <c r="M45" s="114" t="n"/>
+      <c r="N45" s="115" t="n"/>
       <c r="O45" s="46">
         <f>IF($AQ45=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ45))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ45))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ45)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ45))</f>
         <v/>
       </c>
-      <c r="P45" s="69" t="n"/>
-      <c r="Q45" s="69" t="n"/>
-      <c r="R45" s="69" t="n"/>
-      <c r="S45" s="69" t="n"/>
-      <c r="T45" s="70" t="n"/>
+      <c r="P45" s="114" t="n"/>
+      <c r="Q45" s="114" t="n"/>
+      <c r="R45" s="114" t="n"/>
+      <c r="S45" s="114" t="n"/>
+      <c r="T45" s="115" t="n"/>
       <c r="U45" s="47">
         <f>IF($AQ45=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ45)=INDEX('01_予約入力'!$G$5:$G$204,$AQ45),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ45)-INDEX('01_予約入力'!$G$5:$G$204,$AQ45)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V45" s="69" t="n"/>
-      <c r="W45" s="70" t="n"/>
+      <c r="V45" s="114" t="n"/>
+      <c r="W45" s="115" t="n"/>
       <c r="X45" s="47">
         <f>IF($AQ45=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ45)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ45)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ45)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ45)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ45))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ45)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ45))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ45)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ45))))</f>
         <v/>
       </c>
-      <c r="Y45" s="69" t="n"/>
-      <c r="Z45" s="69" t="n"/>
-      <c r="AA45" s="70" t="n"/>
+      <c r="Y45" s="114" t="n"/>
+      <c r="Z45" s="114" t="n"/>
+      <c r="AA45" s="115" t="n"/>
       <c r="AB45" s="47">
         <f>IF($AQ45=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ45)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ45)))</f>
         <v/>
       </c>
-      <c r="AC45" s="69" t="n"/>
-      <c r="AD45" s="70" t="n"/>
+      <c r="AC45" s="114" t="n"/>
+      <c r="AD45" s="115" t="n"/>
       <c r="AE45" s="46">
         <f>IF($AQ45=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ45))</f>
         <v/>
       </c>
-      <c r="AF45" s="69" t="n"/>
-      <c r="AG45" s="70" t="n"/>
+      <c r="AF45" s="114" t="n"/>
+      <c r="AG45" s="115" t="n"/>
       <c r="AP45">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,13),"")</f>
         <v/>
@@ -29137,58 +29959,58 @@
         <f>IF($AQ46=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ46)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ46)))</f>
         <v/>
       </c>
-      <c r="C46" s="69" t="n"/>
-      <c r="D46" s="69" t="n"/>
-      <c r="E46" s="70" t="n"/>
+      <c r="C46" s="114" t="n"/>
+      <c r="D46" s="114" t="n"/>
+      <c r="E46" s="115" t="n"/>
       <c r="F46" s="47">
         <f>IF($AQ46=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ46))</f>
         <v/>
       </c>
-      <c r="G46" s="69" t="n"/>
-      <c r="H46" s="70" t="n"/>
+      <c r="G46" s="114" t="n"/>
+      <c r="H46" s="115" t="n"/>
       <c r="I46" s="46">
         <f>IF($AQ46=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ46))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ46))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ46)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ46))</f>
         <v/>
       </c>
-      <c r="J46" s="69" t="n"/>
-      <c r="K46" s="69" t="n"/>
-      <c r="L46" s="69" t="n"/>
-      <c r="M46" s="69" t="n"/>
-      <c r="N46" s="70" t="n"/>
+      <c r="J46" s="114" t="n"/>
+      <c r="K46" s="114" t="n"/>
+      <c r="L46" s="114" t="n"/>
+      <c r="M46" s="114" t="n"/>
+      <c r="N46" s="115" t="n"/>
       <c r="O46" s="46">
         <f>IF($AQ46=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ46))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ46))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ46)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ46))</f>
         <v/>
       </c>
-      <c r="P46" s="69" t="n"/>
-      <c r="Q46" s="69" t="n"/>
-      <c r="R46" s="69" t="n"/>
-      <c r="S46" s="69" t="n"/>
-      <c r="T46" s="70" t="n"/>
+      <c r="P46" s="114" t="n"/>
+      <c r="Q46" s="114" t="n"/>
+      <c r="R46" s="114" t="n"/>
+      <c r="S46" s="114" t="n"/>
+      <c r="T46" s="115" t="n"/>
       <c r="U46" s="47">
         <f>IF($AQ46=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ46)=INDEX('01_予約入力'!$G$5:$G$204,$AQ46),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ46)-INDEX('01_予約入力'!$G$5:$G$204,$AQ46)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V46" s="69" t="n"/>
-      <c r="W46" s="70" t="n"/>
+      <c r="V46" s="114" t="n"/>
+      <c r="W46" s="115" t="n"/>
       <c r="X46" s="47">
         <f>IF($AQ46=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ46)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ46)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ46)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ46)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ46))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ46)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ46))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ46)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ46))))</f>
         <v/>
       </c>
-      <c r="Y46" s="69" t="n"/>
-      <c r="Z46" s="69" t="n"/>
-      <c r="AA46" s="70" t="n"/>
+      <c r="Y46" s="114" t="n"/>
+      <c r="Z46" s="114" t="n"/>
+      <c r="AA46" s="115" t="n"/>
       <c r="AB46" s="47">
         <f>IF($AQ46=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ46)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ46)))</f>
         <v/>
       </c>
-      <c r="AC46" s="69" t="n"/>
-      <c r="AD46" s="70" t="n"/>
+      <c r="AC46" s="114" t="n"/>
+      <c r="AD46" s="115" t="n"/>
       <c r="AE46" s="46">
         <f>IF($AQ46=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ46))</f>
         <v/>
       </c>
-      <c r="AF46" s="69" t="n"/>
-      <c r="AG46" s="70" t="n"/>
+      <c r="AF46" s="114" t="n"/>
+      <c r="AG46" s="115" t="n"/>
       <c r="AP46">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,14),"")</f>
         <v/>
@@ -29207,58 +30029,58 @@
         <f>IF($AQ47=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ47)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ47)))</f>
         <v/>
       </c>
-      <c r="C47" s="69" t="n"/>
-      <c r="D47" s="69" t="n"/>
-      <c r="E47" s="70" t="n"/>
+      <c r="C47" s="114" t="n"/>
+      <c r="D47" s="114" t="n"/>
+      <c r="E47" s="115" t="n"/>
       <c r="F47" s="47">
         <f>IF($AQ47=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ47))</f>
         <v/>
       </c>
-      <c r="G47" s="69" t="n"/>
-      <c r="H47" s="70" t="n"/>
+      <c r="G47" s="114" t="n"/>
+      <c r="H47" s="115" t="n"/>
       <c r="I47" s="46">
         <f>IF($AQ47=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ47))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ47))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ47)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ47))</f>
         <v/>
       </c>
-      <c r="J47" s="69" t="n"/>
-      <c r="K47" s="69" t="n"/>
-      <c r="L47" s="69" t="n"/>
-      <c r="M47" s="69" t="n"/>
-      <c r="N47" s="70" t="n"/>
+      <c r="J47" s="114" t="n"/>
+      <c r="K47" s="114" t="n"/>
+      <c r="L47" s="114" t="n"/>
+      <c r="M47" s="114" t="n"/>
+      <c r="N47" s="115" t="n"/>
       <c r="O47" s="46">
         <f>IF($AQ47=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ47))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ47))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ47)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ47))</f>
         <v/>
       </c>
-      <c r="P47" s="69" t="n"/>
-      <c r="Q47" s="69" t="n"/>
-      <c r="R47" s="69" t="n"/>
-      <c r="S47" s="69" t="n"/>
-      <c r="T47" s="70" t="n"/>
+      <c r="P47" s="114" t="n"/>
+      <c r="Q47" s="114" t="n"/>
+      <c r="R47" s="114" t="n"/>
+      <c r="S47" s="114" t="n"/>
+      <c r="T47" s="115" t="n"/>
       <c r="U47" s="47">
         <f>IF($AQ47=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ47)=INDEX('01_予約入力'!$G$5:$G$204,$AQ47),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ47)-INDEX('01_予約入力'!$G$5:$G$204,$AQ47)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V47" s="69" t="n"/>
-      <c r="W47" s="70" t="n"/>
+      <c r="V47" s="114" t="n"/>
+      <c r="W47" s="115" t="n"/>
       <c r="X47" s="47">
         <f>IF($AQ47=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ47)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ47)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ47)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ47)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ47))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ47)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ47))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ47)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ47))))</f>
         <v/>
       </c>
-      <c r="Y47" s="69" t="n"/>
-      <c r="Z47" s="69" t="n"/>
-      <c r="AA47" s="70" t="n"/>
+      <c r="Y47" s="114" t="n"/>
+      <c r="Z47" s="114" t="n"/>
+      <c r="AA47" s="115" t="n"/>
       <c r="AB47" s="47">
         <f>IF($AQ47=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ47)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ47)))</f>
         <v/>
       </c>
-      <c r="AC47" s="69" t="n"/>
-      <c r="AD47" s="70" t="n"/>
+      <c r="AC47" s="114" t="n"/>
+      <c r="AD47" s="115" t="n"/>
       <c r="AE47" s="46">
         <f>IF($AQ47=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ47))</f>
         <v/>
       </c>
-      <c r="AF47" s="69" t="n"/>
-      <c r="AG47" s="70" t="n"/>
+      <c r="AF47" s="114" t="n"/>
+      <c r="AG47" s="115" t="n"/>
       <c r="AP47">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,15),"")</f>
         <v/>
@@ -29277,58 +30099,58 @@
         <f>IF($AQ48=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ48)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ48)))</f>
         <v/>
       </c>
-      <c r="C48" s="69" t="n"/>
-      <c r="D48" s="69" t="n"/>
-      <c r="E48" s="70" t="n"/>
+      <c r="C48" s="114" t="n"/>
+      <c r="D48" s="114" t="n"/>
+      <c r="E48" s="115" t="n"/>
       <c r="F48" s="47">
         <f>IF($AQ48=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ48))</f>
         <v/>
       </c>
-      <c r="G48" s="69" t="n"/>
-      <c r="H48" s="70" t="n"/>
+      <c r="G48" s="114" t="n"/>
+      <c r="H48" s="115" t="n"/>
       <c r="I48" s="46">
         <f>IF($AQ48=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ48))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ48))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ48)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ48))</f>
         <v/>
       </c>
-      <c r="J48" s="69" t="n"/>
-      <c r="K48" s="69" t="n"/>
-      <c r="L48" s="69" t="n"/>
-      <c r="M48" s="69" t="n"/>
-      <c r="N48" s="70" t="n"/>
+      <c r="J48" s="114" t="n"/>
+      <c r="K48" s="114" t="n"/>
+      <c r="L48" s="114" t="n"/>
+      <c r="M48" s="114" t="n"/>
+      <c r="N48" s="115" t="n"/>
       <c r="O48" s="46">
         <f>IF($AQ48=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ48))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ48))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ48)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ48))</f>
         <v/>
       </c>
-      <c r="P48" s="69" t="n"/>
-      <c r="Q48" s="69" t="n"/>
-      <c r="R48" s="69" t="n"/>
-      <c r="S48" s="69" t="n"/>
-      <c r="T48" s="70" t="n"/>
+      <c r="P48" s="114" t="n"/>
+      <c r="Q48" s="114" t="n"/>
+      <c r="R48" s="114" t="n"/>
+      <c r="S48" s="114" t="n"/>
+      <c r="T48" s="115" t="n"/>
       <c r="U48" s="47">
         <f>IF($AQ48=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ48)=INDEX('01_予約入力'!$G$5:$G$204,$AQ48),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ48)-INDEX('01_予約入力'!$G$5:$G$204,$AQ48)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V48" s="69" t="n"/>
-      <c r="W48" s="70" t="n"/>
+      <c r="V48" s="114" t="n"/>
+      <c r="W48" s="115" t="n"/>
       <c r="X48" s="47">
         <f>IF($AQ48=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ48)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ48)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ48)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ48)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ48))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ48)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ48))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ48)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ48))))</f>
         <v/>
       </c>
-      <c r="Y48" s="69" t="n"/>
-      <c r="Z48" s="69" t="n"/>
-      <c r="AA48" s="70" t="n"/>
+      <c r="Y48" s="114" t="n"/>
+      <c r="Z48" s="114" t="n"/>
+      <c r="AA48" s="115" t="n"/>
       <c r="AB48" s="47">
         <f>IF($AQ48=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ48)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ48)))</f>
         <v/>
       </c>
-      <c r="AC48" s="69" t="n"/>
-      <c r="AD48" s="70" t="n"/>
+      <c r="AC48" s="114" t="n"/>
+      <c r="AD48" s="115" t="n"/>
       <c r="AE48" s="46">
         <f>IF($AQ48=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ48))</f>
         <v/>
       </c>
-      <c r="AF48" s="69" t="n"/>
-      <c r="AG48" s="70" t="n"/>
+      <c r="AF48" s="114" t="n"/>
+      <c r="AG48" s="115" t="n"/>
       <c r="AP48">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,16),"")</f>
         <v/>
@@ -29347,58 +30169,58 @@
         <f>IF($AQ49=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ49)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ49)))</f>
         <v/>
       </c>
-      <c r="C49" s="69" t="n"/>
-      <c r="D49" s="69" t="n"/>
-      <c r="E49" s="70" t="n"/>
+      <c r="C49" s="114" t="n"/>
+      <c r="D49" s="114" t="n"/>
+      <c r="E49" s="115" t="n"/>
       <c r="F49" s="47">
         <f>IF($AQ49=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ49))</f>
         <v/>
       </c>
-      <c r="G49" s="69" t="n"/>
-      <c r="H49" s="70" t="n"/>
+      <c r="G49" s="114" t="n"/>
+      <c r="H49" s="115" t="n"/>
       <c r="I49" s="46">
         <f>IF($AQ49=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ49))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ49))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ49)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ49))</f>
         <v/>
       </c>
-      <c r="J49" s="69" t="n"/>
-      <c r="K49" s="69" t="n"/>
-      <c r="L49" s="69" t="n"/>
-      <c r="M49" s="69" t="n"/>
-      <c r="N49" s="70" t="n"/>
+      <c r="J49" s="114" t="n"/>
+      <c r="K49" s="114" t="n"/>
+      <c r="L49" s="114" t="n"/>
+      <c r="M49" s="114" t="n"/>
+      <c r="N49" s="115" t="n"/>
       <c r="O49" s="46">
         <f>IF($AQ49=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ49))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ49))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ49)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ49))</f>
         <v/>
       </c>
-      <c r="P49" s="69" t="n"/>
-      <c r="Q49" s="69" t="n"/>
-      <c r="R49" s="69" t="n"/>
-      <c r="S49" s="69" t="n"/>
-      <c r="T49" s="70" t="n"/>
+      <c r="P49" s="114" t="n"/>
+      <c r="Q49" s="114" t="n"/>
+      <c r="R49" s="114" t="n"/>
+      <c r="S49" s="114" t="n"/>
+      <c r="T49" s="115" t="n"/>
       <c r="U49" s="47">
         <f>IF($AQ49=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ49)=INDEX('01_予約入力'!$G$5:$G$204,$AQ49),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ49)-INDEX('01_予約入力'!$G$5:$G$204,$AQ49)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V49" s="69" t="n"/>
-      <c r="W49" s="70" t="n"/>
+      <c r="V49" s="114" t="n"/>
+      <c r="W49" s="115" t="n"/>
       <c r="X49" s="47">
         <f>IF($AQ49=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ49)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ49)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ49)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ49)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ49))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ49)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ49))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ49)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ49))))</f>
         <v/>
       </c>
-      <c r="Y49" s="69" t="n"/>
-      <c r="Z49" s="69" t="n"/>
-      <c r="AA49" s="70" t="n"/>
+      <c r="Y49" s="114" t="n"/>
+      <c r="Z49" s="114" t="n"/>
+      <c r="AA49" s="115" t="n"/>
       <c r="AB49" s="47">
         <f>IF($AQ49=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ49)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ49)))</f>
         <v/>
       </c>
-      <c r="AC49" s="69" t="n"/>
-      <c r="AD49" s="70" t="n"/>
+      <c r="AC49" s="114" t="n"/>
+      <c r="AD49" s="115" t="n"/>
       <c r="AE49" s="46">
         <f>IF($AQ49=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ49))</f>
         <v/>
       </c>
-      <c r="AF49" s="69" t="n"/>
-      <c r="AG49" s="70" t="n"/>
+      <c r="AF49" s="114" t="n"/>
+      <c r="AG49" s="115" t="n"/>
       <c r="AP49">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,17),"")</f>
         <v/>
@@ -29417,58 +30239,58 @@
         <f>IF($AQ50=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ50)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ50)))</f>
         <v/>
       </c>
-      <c r="C50" s="69" t="n"/>
-      <c r="D50" s="69" t="n"/>
-      <c r="E50" s="70" t="n"/>
+      <c r="C50" s="114" t="n"/>
+      <c r="D50" s="114" t="n"/>
+      <c r="E50" s="115" t="n"/>
       <c r="F50" s="47">
         <f>IF($AQ50=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ50))</f>
         <v/>
       </c>
-      <c r="G50" s="69" t="n"/>
-      <c r="H50" s="70" t="n"/>
+      <c r="G50" s="114" t="n"/>
+      <c r="H50" s="115" t="n"/>
       <c r="I50" s="46">
         <f>IF($AQ50=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ50))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ50))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ50)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ50))</f>
         <v/>
       </c>
-      <c r="J50" s="69" t="n"/>
-      <c r="K50" s="69" t="n"/>
-      <c r="L50" s="69" t="n"/>
-      <c r="M50" s="69" t="n"/>
-      <c r="N50" s="70" t="n"/>
+      <c r="J50" s="114" t="n"/>
+      <c r="K50" s="114" t="n"/>
+      <c r="L50" s="114" t="n"/>
+      <c r="M50" s="114" t="n"/>
+      <c r="N50" s="115" t="n"/>
       <c r="O50" s="46">
         <f>IF($AQ50=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ50))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ50))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ50)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ50))</f>
         <v/>
       </c>
-      <c r="P50" s="69" t="n"/>
-      <c r="Q50" s="69" t="n"/>
-      <c r="R50" s="69" t="n"/>
-      <c r="S50" s="69" t="n"/>
-      <c r="T50" s="70" t="n"/>
+      <c r="P50" s="114" t="n"/>
+      <c r="Q50" s="114" t="n"/>
+      <c r="R50" s="114" t="n"/>
+      <c r="S50" s="114" t="n"/>
+      <c r="T50" s="115" t="n"/>
       <c r="U50" s="47">
         <f>IF($AQ50=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ50)=INDEX('01_予約入力'!$G$5:$G$204,$AQ50),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ50)-INDEX('01_予約入力'!$G$5:$G$204,$AQ50)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V50" s="69" t="n"/>
-      <c r="W50" s="70" t="n"/>
+      <c r="V50" s="114" t="n"/>
+      <c r="W50" s="115" t="n"/>
       <c r="X50" s="47">
         <f>IF($AQ50=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ50)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ50)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ50)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ50)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ50))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ50)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ50))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ50)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ50))))</f>
         <v/>
       </c>
-      <c r="Y50" s="69" t="n"/>
-      <c r="Z50" s="69" t="n"/>
-      <c r="AA50" s="70" t="n"/>
+      <c r="Y50" s="114" t="n"/>
+      <c r="Z50" s="114" t="n"/>
+      <c r="AA50" s="115" t="n"/>
       <c r="AB50" s="47">
         <f>IF($AQ50=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ50)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ50)))</f>
         <v/>
       </c>
-      <c r="AC50" s="69" t="n"/>
-      <c r="AD50" s="70" t="n"/>
+      <c r="AC50" s="114" t="n"/>
+      <c r="AD50" s="115" t="n"/>
       <c r="AE50" s="46">
         <f>IF($AQ50=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ50))</f>
         <v/>
       </c>
-      <c r="AF50" s="69" t="n"/>
-      <c r="AG50" s="70" t="n"/>
+      <c r="AF50" s="114" t="n"/>
+      <c r="AG50" s="115" t="n"/>
       <c r="AP50">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,18),"")</f>
         <v/>
@@ -29487,58 +30309,58 @@
         <f>IF($AQ51=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ51)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ51)))</f>
         <v/>
       </c>
-      <c r="C51" s="69" t="n"/>
-      <c r="D51" s="69" t="n"/>
-      <c r="E51" s="70" t="n"/>
+      <c r="C51" s="114" t="n"/>
+      <c r="D51" s="114" t="n"/>
+      <c r="E51" s="115" t="n"/>
       <c r="F51" s="47">
         <f>IF($AQ51=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ51))</f>
         <v/>
       </c>
-      <c r="G51" s="69" t="n"/>
-      <c r="H51" s="70" t="n"/>
+      <c r="G51" s="114" t="n"/>
+      <c r="H51" s="115" t="n"/>
       <c r="I51" s="46">
         <f>IF($AQ51=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ51))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ51))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ51)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ51))</f>
         <v/>
       </c>
-      <c r="J51" s="69" t="n"/>
-      <c r="K51" s="69" t="n"/>
-      <c r="L51" s="69" t="n"/>
-      <c r="M51" s="69" t="n"/>
-      <c r="N51" s="70" t="n"/>
+      <c r="J51" s="114" t="n"/>
+      <c r="K51" s="114" t="n"/>
+      <c r="L51" s="114" t="n"/>
+      <c r="M51" s="114" t="n"/>
+      <c r="N51" s="115" t="n"/>
       <c r="O51" s="46">
         <f>IF($AQ51=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ51))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ51))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ51)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ51))</f>
         <v/>
       </c>
-      <c r="P51" s="69" t="n"/>
-      <c r="Q51" s="69" t="n"/>
-      <c r="R51" s="69" t="n"/>
-      <c r="S51" s="69" t="n"/>
-      <c r="T51" s="70" t="n"/>
+      <c r="P51" s="114" t="n"/>
+      <c r="Q51" s="114" t="n"/>
+      <c r="R51" s="114" t="n"/>
+      <c r="S51" s="114" t="n"/>
+      <c r="T51" s="115" t="n"/>
       <c r="U51" s="47">
         <f>IF($AQ51=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ51)=INDEX('01_予約入力'!$G$5:$G$204,$AQ51),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ51)-INDEX('01_予約入力'!$G$5:$G$204,$AQ51)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V51" s="69" t="n"/>
-      <c r="W51" s="70" t="n"/>
+      <c r="V51" s="114" t="n"/>
+      <c r="W51" s="115" t="n"/>
       <c r="X51" s="47">
         <f>IF($AQ51=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ51)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ51)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ51)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ51)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ51))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ51)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ51))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ51)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ51))))</f>
         <v/>
       </c>
-      <c r="Y51" s="69" t="n"/>
-      <c r="Z51" s="69" t="n"/>
-      <c r="AA51" s="70" t="n"/>
+      <c r="Y51" s="114" t="n"/>
+      <c r="Z51" s="114" t="n"/>
+      <c r="AA51" s="115" t="n"/>
       <c r="AB51" s="47">
         <f>IF($AQ51=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ51)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ51)))</f>
         <v/>
       </c>
-      <c r="AC51" s="69" t="n"/>
-      <c r="AD51" s="70" t="n"/>
+      <c r="AC51" s="114" t="n"/>
+      <c r="AD51" s="115" t="n"/>
       <c r="AE51" s="46">
         <f>IF($AQ51=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ51))</f>
         <v/>
       </c>
-      <c r="AF51" s="69" t="n"/>
-      <c r="AG51" s="70" t="n"/>
+      <c r="AF51" s="114" t="n"/>
+      <c r="AG51" s="115" t="n"/>
       <c r="AP51">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,19),"")</f>
         <v/>
@@ -29557,58 +30379,58 @@
         <f>IF($AQ52=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ52)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ52)))</f>
         <v/>
       </c>
-      <c r="C52" s="69" t="n"/>
-      <c r="D52" s="69" t="n"/>
-      <c r="E52" s="70" t="n"/>
+      <c r="C52" s="114" t="n"/>
+      <c r="D52" s="114" t="n"/>
+      <c r="E52" s="115" t="n"/>
       <c r="F52" s="47">
         <f>IF($AQ52=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ52))</f>
         <v/>
       </c>
-      <c r="G52" s="69" t="n"/>
-      <c r="H52" s="70" t="n"/>
+      <c r="G52" s="114" t="n"/>
+      <c r="H52" s="115" t="n"/>
       <c r="I52" s="46">
         <f>IF($AQ52=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ52))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ52))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ52)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ52))</f>
         <v/>
       </c>
-      <c r="J52" s="69" t="n"/>
-      <c r="K52" s="69" t="n"/>
-      <c r="L52" s="69" t="n"/>
-      <c r="M52" s="69" t="n"/>
-      <c r="N52" s="70" t="n"/>
+      <c r="J52" s="114" t="n"/>
+      <c r="K52" s="114" t="n"/>
+      <c r="L52" s="114" t="n"/>
+      <c r="M52" s="114" t="n"/>
+      <c r="N52" s="115" t="n"/>
       <c r="O52" s="46">
         <f>IF($AQ52=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ52))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ52))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ52)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ52))</f>
         <v/>
       </c>
-      <c r="P52" s="69" t="n"/>
-      <c r="Q52" s="69" t="n"/>
-      <c r="R52" s="69" t="n"/>
-      <c r="S52" s="69" t="n"/>
-      <c r="T52" s="70" t="n"/>
+      <c r="P52" s="114" t="n"/>
+      <c r="Q52" s="114" t="n"/>
+      <c r="R52" s="114" t="n"/>
+      <c r="S52" s="114" t="n"/>
+      <c r="T52" s="115" t="n"/>
       <c r="U52" s="47">
         <f>IF($AQ52=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ52)=INDEX('01_予約入力'!$G$5:$G$204,$AQ52),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ52)-INDEX('01_予約入力'!$G$5:$G$204,$AQ52)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V52" s="69" t="n"/>
-      <c r="W52" s="70" t="n"/>
+      <c r="V52" s="114" t="n"/>
+      <c r="W52" s="115" t="n"/>
       <c r="X52" s="47">
         <f>IF($AQ52=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ52)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ52)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ52)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ52)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ52))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ52)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ52))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ52)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ52))))</f>
         <v/>
       </c>
-      <c r="Y52" s="69" t="n"/>
-      <c r="Z52" s="69" t="n"/>
-      <c r="AA52" s="70" t="n"/>
+      <c r="Y52" s="114" t="n"/>
+      <c r="Z52" s="114" t="n"/>
+      <c r="AA52" s="115" t="n"/>
       <c r="AB52" s="47">
         <f>IF($AQ52=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ52)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ52)))</f>
         <v/>
       </c>
-      <c r="AC52" s="69" t="n"/>
-      <c r="AD52" s="70" t="n"/>
+      <c r="AC52" s="114" t="n"/>
+      <c r="AD52" s="115" t="n"/>
       <c r="AE52" s="46">
         <f>IF($AQ52=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ52))</f>
         <v/>
       </c>
-      <c r="AF52" s="69" t="n"/>
-      <c r="AG52" s="70" t="n"/>
+      <c r="AF52" s="114" t="n"/>
+      <c r="AG52" s="115" t="n"/>
       <c r="AP52">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,20),"")</f>
         <v/>
@@ -29627,58 +30449,58 @@
         <f>IF($AQ53=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ53)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ53)))</f>
         <v/>
       </c>
-      <c r="C53" s="69" t="n"/>
-      <c r="D53" s="69" t="n"/>
-      <c r="E53" s="70" t="n"/>
+      <c r="C53" s="114" t="n"/>
+      <c r="D53" s="114" t="n"/>
+      <c r="E53" s="115" t="n"/>
       <c r="F53" s="47">
         <f>IF($AQ53=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ53))</f>
         <v/>
       </c>
-      <c r="G53" s="69" t="n"/>
-      <c r="H53" s="70" t="n"/>
+      <c r="G53" s="114" t="n"/>
+      <c r="H53" s="115" t="n"/>
       <c r="I53" s="46">
         <f>IF($AQ53=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ53))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ53))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ53)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ53))</f>
         <v/>
       </c>
-      <c r="J53" s="69" t="n"/>
-      <c r="K53" s="69" t="n"/>
-      <c r="L53" s="69" t="n"/>
-      <c r="M53" s="69" t="n"/>
-      <c r="N53" s="70" t="n"/>
+      <c r="J53" s="114" t="n"/>
+      <c r="K53" s="114" t="n"/>
+      <c r="L53" s="114" t="n"/>
+      <c r="M53" s="114" t="n"/>
+      <c r="N53" s="115" t="n"/>
       <c r="O53" s="46">
         <f>IF($AQ53=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ53))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ53))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ53)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ53))</f>
         <v/>
       </c>
-      <c r="P53" s="69" t="n"/>
-      <c r="Q53" s="69" t="n"/>
-      <c r="R53" s="69" t="n"/>
-      <c r="S53" s="69" t="n"/>
-      <c r="T53" s="70" t="n"/>
+      <c r="P53" s="114" t="n"/>
+      <c r="Q53" s="114" t="n"/>
+      <c r="R53" s="114" t="n"/>
+      <c r="S53" s="114" t="n"/>
+      <c r="T53" s="115" t="n"/>
       <c r="U53" s="47">
         <f>IF($AQ53=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ53)=INDEX('01_予約入力'!$G$5:$G$204,$AQ53),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ53)-INDEX('01_予約入力'!$G$5:$G$204,$AQ53)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V53" s="69" t="n"/>
-      <c r="W53" s="70" t="n"/>
+      <c r="V53" s="114" t="n"/>
+      <c r="W53" s="115" t="n"/>
       <c r="X53" s="47">
         <f>IF($AQ53=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ53)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ53)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ53)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ53)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ53))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ53)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ53))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ53)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ53))))</f>
         <v/>
       </c>
-      <c r="Y53" s="69" t="n"/>
-      <c r="Z53" s="69" t="n"/>
-      <c r="AA53" s="70" t="n"/>
+      <c r="Y53" s="114" t="n"/>
+      <c r="Z53" s="114" t="n"/>
+      <c r="AA53" s="115" t="n"/>
       <c r="AB53" s="47">
         <f>IF($AQ53=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ53)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ53)))</f>
         <v/>
       </c>
-      <c r="AC53" s="69" t="n"/>
-      <c r="AD53" s="70" t="n"/>
+      <c r="AC53" s="114" t="n"/>
+      <c r="AD53" s="115" t="n"/>
       <c r="AE53" s="46">
         <f>IF($AQ53=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ53))</f>
         <v/>
       </c>
-      <c r="AF53" s="69" t="n"/>
-      <c r="AG53" s="70" t="n"/>
+      <c r="AF53" s="114" t="n"/>
+      <c r="AG53" s="115" t="n"/>
       <c r="AP53">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,21),"")</f>
         <v/>
@@ -29697,58 +30519,58 @@
         <f>IF($AQ54=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ54)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ54)))</f>
         <v/>
       </c>
-      <c r="C54" s="69" t="n"/>
-      <c r="D54" s="69" t="n"/>
-      <c r="E54" s="70" t="n"/>
+      <c r="C54" s="114" t="n"/>
+      <c r="D54" s="114" t="n"/>
+      <c r="E54" s="115" t="n"/>
       <c r="F54" s="47">
         <f>IF($AQ54=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ54))</f>
         <v/>
       </c>
-      <c r="G54" s="69" t="n"/>
-      <c r="H54" s="70" t="n"/>
+      <c r="G54" s="114" t="n"/>
+      <c r="H54" s="115" t="n"/>
       <c r="I54" s="46">
         <f>IF($AQ54=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ54))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ54))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ54)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ54))</f>
         <v/>
       </c>
-      <c r="J54" s="69" t="n"/>
-      <c r="K54" s="69" t="n"/>
-      <c r="L54" s="69" t="n"/>
-      <c r="M54" s="69" t="n"/>
-      <c r="N54" s="70" t="n"/>
+      <c r="J54" s="114" t="n"/>
+      <c r="K54" s="114" t="n"/>
+      <c r="L54" s="114" t="n"/>
+      <c r="M54" s="114" t="n"/>
+      <c r="N54" s="115" t="n"/>
       <c r="O54" s="46">
         <f>IF($AQ54=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ54))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ54))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ54)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ54))</f>
         <v/>
       </c>
-      <c r="P54" s="69" t="n"/>
-      <c r="Q54" s="69" t="n"/>
-      <c r="R54" s="69" t="n"/>
-      <c r="S54" s="69" t="n"/>
-      <c r="T54" s="70" t="n"/>
+      <c r="P54" s="114" t="n"/>
+      <c r="Q54" s="114" t="n"/>
+      <c r="R54" s="114" t="n"/>
+      <c r="S54" s="114" t="n"/>
+      <c r="T54" s="115" t="n"/>
       <c r="U54" s="47">
         <f>IF($AQ54=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ54)=INDEX('01_予約入力'!$G$5:$G$204,$AQ54),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ54)-INDEX('01_予約入力'!$G$5:$G$204,$AQ54)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V54" s="69" t="n"/>
-      <c r="W54" s="70" t="n"/>
+      <c r="V54" s="114" t="n"/>
+      <c r="W54" s="115" t="n"/>
       <c r="X54" s="47">
         <f>IF($AQ54=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ54)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ54)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ54)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ54)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ54))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ54)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ54))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ54)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ54))))</f>
         <v/>
       </c>
-      <c r="Y54" s="69" t="n"/>
-      <c r="Z54" s="69" t="n"/>
-      <c r="AA54" s="70" t="n"/>
+      <c r="Y54" s="114" t="n"/>
+      <c r="Z54" s="114" t="n"/>
+      <c r="AA54" s="115" t="n"/>
       <c r="AB54" s="47">
         <f>IF($AQ54=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ54)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ54)))</f>
         <v/>
       </c>
-      <c r="AC54" s="69" t="n"/>
-      <c r="AD54" s="70" t="n"/>
+      <c r="AC54" s="114" t="n"/>
+      <c r="AD54" s="115" t="n"/>
       <c r="AE54" s="46">
         <f>IF($AQ54=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ54))</f>
         <v/>
       </c>
-      <c r="AF54" s="69" t="n"/>
-      <c r="AG54" s="70" t="n"/>
+      <c r="AF54" s="114" t="n"/>
+      <c r="AG54" s="115" t="n"/>
       <c r="AP54">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,22),"")</f>
         <v/>
@@ -29767,58 +30589,58 @@
         <f>IF($AQ55=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ55)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ55)))</f>
         <v/>
       </c>
-      <c r="C55" s="69" t="n"/>
-      <c r="D55" s="69" t="n"/>
-      <c r="E55" s="70" t="n"/>
+      <c r="C55" s="114" t="n"/>
+      <c r="D55" s="114" t="n"/>
+      <c r="E55" s="115" t="n"/>
       <c r="F55" s="47">
         <f>IF($AQ55=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ55))</f>
         <v/>
       </c>
-      <c r="G55" s="69" t="n"/>
-      <c r="H55" s="70" t="n"/>
+      <c r="G55" s="114" t="n"/>
+      <c r="H55" s="115" t="n"/>
       <c r="I55" s="46">
         <f>IF($AQ55=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ55))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ55))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ55)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ55))</f>
         <v/>
       </c>
-      <c r="J55" s="69" t="n"/>
-      <c r="K55" s="69" t="n"/>
-      <c r="L55" s="69" t="n"/>
-      <c r="M55" s="69" t="n"/>
-      <c r="N55" s="70" t="n"/>
+      <c r="J55" s="114" t="n"/>
+      <c r="K55" s="114" t="n"/>
+      <c r="L55" s="114" t="n"/>
+      <c r="M55" s="114" t="n"/>
+      <c r="N55" s="115" t="n"/>
       <c r="O55" s="46">
         <f>IF($AQ55=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ55))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ55))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ55)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ55))</f>
         <v/>
       </c>
-      <c r="P55" s="69" t="n"/>
-      <c r="Q55" s="69" t="n"/>
-      <c r="R55" s="69" t="n"/>
-      <c r="S55" s="69" t="n"/>
-      <c r="T55" s="70" t="n"/>
+      <c r="P55" s="114" t="n"/>
+      <c r="Q55" s="114" t="n"/>
+      <c r="R55" s="114" t="n"/>
+      <c r="S55" s="114" t="n"/>
+      <c r="T55" s="115" t="n"/>
       <c r="U55" s="47">
         <f>IF($AQ55=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ55)=INDEX('01_予約入力'!$G$5:$G$204,$AQ55),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ55)-INDEX('01_予約入力'!$G$5:$G$204,$AQ55)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V55" s="69" t="n"/>
-      <c r="W55" s="70" t="n"/>
+      <c r="V55" s="114" t="n"/>
+      <c r="W55" s="115" t="n"/>
       <c r="X55" s="47">
         <f>IF($AQ55=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ55)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ55)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ55)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ55)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ55))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ55)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ55))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ55)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ55))))</f>
         <v/>
       </c>
-      <c r="Y55" s="69" t="n"/>
-      <c r="Z55" s="69" t="n"/>
-      <c r="AA55" s="70" t="n"/>
+      <c r="Y55" s="114" t="n"/>
+      <c r="Z55" s="114" t="n"/>
+      <c r="AA55" s="115" t="n"/>
       <c r="AB55" s="47">
         <f>IF($AQ55=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ55)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ55)))</f>
         <v/>
       </c>
-      <c r="AC55" s="69" t="n"/>
-      <c r="AD55" s="70" t="n"/>
+      <c r="AC55" s="114" t="n"/>
+      <c r="AD55" s="115" t="n"/>
       <c r="AE55" s="46">
         <f>IF($AQ55=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ55))</f>
         <v/>
       </c>
-      <c r="AF55" s="69" t="n"/>
-      <c r="AG55" s="70" t="n"/>
+      <c r="AF55" s="114" t="n"/>
+      <c r="AG55" s="115" t="n"/>
       <c r="AP55">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,23),"")</f>
         <v/>
@@ -29837,58 +30659,58 @@
         <f>IF($AQ56=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ56)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ56)))</f>
         <v/>
       </c>
-      <c r="C56" s="69" t="n"/>
-      <c r="D56" s="69" t="n"/>
-      <c r="E56" s="70" t="n"/>
+      <c r="C56" s="114" t="n"/>
+      <c r="D56" s="114" t="n"/>
+      <c r="E56" s="115" t="n"/>
       <c r="F56" s="47">
         <f>IF($AQ56=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ56))</f>
         <v/>
       </c>
-      <c r="G56" s="69" t="n"/>
-      <c r="H56" s="70" t="n"/>
+      <c r="G56" s="114" t="n"/>
+      <c r="H56" s="115" t="n"/>
       <c r="I56" s="46">
         <f>IF($AQ56=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ56))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ56))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ56)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ56))</f>
         <v/>
       </c>
-      <c r="J56" s="69" t="n"/>
-      <c r="K56" s="69" t="n"/>
-      <c r="L56" s="69" t="n"/>
-      <c r="M56" s="69" t="n"/>
-      <c r="N56" s="70" t="n"/>
+      <c r="J56" s="114" t="n"/>
+      <c r="K56" s="114" t="n"/>
+      <c r="L56" s="114" t="n"/>
+      <c r="M56" s="114" t="n"/>
+      <c r="N56" s="115" t="n"/>
       <c r="O56" s="46">
         <f>IF($AQ56=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ56))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ56))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ56)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ56))</f>
         <v/>
       </c>
-      <c r="P56" s="69" t="n"/>
-      <c r="Q56" s="69" t="n"/>
-      <c r="R56" s="69" t="n"/>
-      <c r="S56" s="69" t="n"/>
-      <c r="T56" s="70" t="n"/>
+      <c r="P56" s="114" t="n"/>
+      <c r="Q56" s="114" t="n"/>
+      <c r="R56" s="114" t="n"/>
+      <c r="S56" s="114" t="n"/>
+      <c r="T56" s="115" t="n"/>
       <c r="U56" s="47">
         <f>IF($AQ56=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ56)=INDEX('01_予約入力'!$G$5:$G$204,$AQ56),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ56)-INDEX('01_予約入力'!$G$5:$G$204,$AQ56)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V56" s="69" t="n"/>
-      <c r="W56" s="70" t="n"/>
+      <c r="V56" s="114" t="n"/>
+      <c r="W56" s="115" t="n"/>
       <c r="X56" s="47">
         <f>IF($AQ56=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ56)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ56)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ56)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ56)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ56))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ56)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ56))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ56)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ56))))</f>
         <v/>
       </c>
-      <c r="Y56" s="69" t="n"/>
-      <c r="Z56" s="69" t="n"/>
-      <c r="AA56" s="70" t="n"/>
+      <c r="Y56" s="114" t="n"/>
+      <c r="Z56" s="114" t="n"/>
+      <c r="AA56" s="115" t="n"/>
       <c r="AB56" s="47">
         <f>IF($AQ56=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ56)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ56)))</f>
         <v/>
       </c>
-      <c r="AC56" s="69" t="n"/>
-      <c r="AD56" s="70" t="n"/>
+      <c r="AC56" s="114" t="n"/>
+      <c r="AD56" s="115" t="n"/>
       <c r="AE56" s="46">
         <f>IF($AQ56=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ56))</f>
         <v/>
       </c>
-      <c r="AF56" s="69" t="n"/>
-      <c r="AG56" s="70" t="n"/>
+      <c r="AF56" s="114" t="n"/>
+      <c r="AG56" s="115" t="n"/>
       <c r="AP56">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,24),"")</f>
         <v/>
@@ -29907,58 +30729,58 @@
         <f>IF($AQ57=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ57)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ57)))</f>
         <v/>
       </c>
-      <c r="C57" s="69" t="n"/>
-      <c r="D57" s="69" t="n"/>
-      <c r="E57" s="70" t="n"/>
+      <c r="C57" s="114" t="n"/>
+      <c r="D57" s="114" t="n"/>
+      <c r="E57" s="115" t="n"/>
       <c r="F57" s="47">
         <f>IF($AQ57=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ57))</f>
         <v/>
       </c>
-      <c r="G57" s="69" t="n"/>
-      <c r="H57" s="70" t="n"/>
+      <c r="G57" s="114" t="n"/>
+      <c r="H57" s="115" t="n"/>
       <c r="I57" s="46">
         <f>IF($AQ57=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ57))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ57))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ57)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ57))</f>
         <v/>
       </c>
-      <c r="J57" s="69" t="n"/>
-      <c r="K57" s="69" t="n"/>
-      <c r="L57" s="69" t="n"/>
-      <c r="M57" s="69" t="n"/>
-      <c r="N57" s="70" t="n"/>
+      <c r="J57" s="114" t="n"/>
+      <c r="K57" s="114" t="n"/>
+      <c r="L57" s="114" t="n"/>
+      <c r="M57" s="114" t="n"/>
+      <c r="N57" s="115" t="n"/>
       <c r="O57" s="46">
         <f>IF($AQ57=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ57))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ57))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ57)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ57))</f>
         <v/>
       </c>
-      <c r="P57" s="69" t="n"/>
-      <c r="Q57" s="69" t="n"/>
-      <c r="R57" s="69" t="n"/>
-      <c r="S57" s="69" t="n"/>
-      <c r="T57" s="70" t="n"/>
+      <c r="P57" s="114" t="n"/>
+      <c r="Q57" s="114" t="n"/>
+      <c r="R57" s="114" t="n"/>
+      <c r="S57" s="114" t="n"/>
+      <c r="T57" s="115" t="n"/>
       <c r="U57" s="47">
         <f>IF($AQ57=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ57)=INDEX('01_予約入力'!$G$5:$G$204,$AQ57),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ57)-INDEX('01_予約入力'!$G$5:$G$204,$AQ57)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V57" s="69" t="n"/>
-      <c r="W57" s="70" t="n"/>
+      <c r="V57" s="114" t="n"/>
+      <c r="W57" s="115" t="n"/>
       <c r="X57" s="47">
         <f>IF($AQ57=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ57)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ57)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ57)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ57)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ57))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ57)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ57))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ57)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ57))))</f>
         <v/>
       </c>
-      <c r="Y57" s="69" t="n"/>
-      <c r="Z57" s="69" t="n"/>
-      <c r="AA57" s="70" t="n"/>
+      <c r="Y57" s="114" t="n"/>
+      <c r="Z57" s="114" t="n"/>
+      <c r="AA57" s="115" t="n"/>
       <c r="AB57" s="47">
         <f>IF($AQ57=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ57)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ57)))</f>
         <v/>
       </c>
-      <c r="AC57" s="69" t="n"/>
-      <c r="AD57" s="70" t="n"/>
+      <c r="AC57" s="114" t="n"/>
+      <c r="AD57" s="115" t="n"/>
       <c r="AE57" s="46">
         <f>IF($AQ57=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ57))</f>
         <v/>
       </c>
-      <c r="AF57" s="69" t="n"/>
-      <c r="AG57" s="70" t="n"/>
+      <c r="AF57" s="114" t="n"/>
+      <c r="AG57" s="115" t="n"/>
       <c r="AP57">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,25),"")</f>
         <v/>
@@ -29977,58 +30799,58 @@
         <f>IF($AQ58=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ58)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ58)))</f>
         <v/>
       </c>
-      <c r="C58" s="69" t="n"/>
-      <c r="D58" s="69" t="n"/>
-      <c r="E58" s="70" t="n"/>
+      <c r="C58" s="114" t="n"/>
+      <c r="D58" s="114" t="n"/>
+      <c r="E58" s="115" t="n"/>
       <c r="F58" s="47">
         <f>IF($AQ58=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ58))</f>
         <v/>
       </c>
-      <c r="G58" s="69" t="n"/>
-      <c r="H58" s="70" t="n"/>
+      <c r="G58" s="114" t="n"/>
+      <c r="H58" s="115" t="n"/>
       <c r="I58" s="46">
         <f>IF($AQ58=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ58))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ58))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ58)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ58))</f>
         <v/>
       </c>
-      <c r="J58" s="69" t="n"/>
-      <c r="K58" s="69" t="n"/>
-      <c r="L58" s="69" t="n"/>
-      <c r="M58" s="69" t="n"/>
-      <c r="N58" s="70" t="n"/>
+      <c r="J58" s="114" t="n"/>
+      <c r="K58" s="114" t="n"/>
+      <c r="L58" s="114" t="n"/>
+      <c r="M58" s="114" t="n"/>
+      <c r="N58" s="115" t="n"/>
       <c r="O58" s="46">
         <f>IF($AQ58=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ58))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ58))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ58)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ58))</f>
         <v/>
       </c>
-      <c r="P58" s="69" t="n"/>
-      <c r="Q58" s="69" t="n"/>
-      <c r="R58" s="69" t="n"/>
-      <c r="S58" s="69" t="n"/>
-      <c r="T58" s="70" t="n"/>
+      <c r="P58" s="114" t="n"/>
+      <c r="Q58" s="114" t="n"/>
+      <c r="R58" s="114" t="n"/>
+      <c r="S58" s="114" t="n"/>
+      <c r="T58" s="115" t="n"/>
       <c r="U58" s="47">
         <f>IF($AQ58=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ58)=INDEX('01_予約入力'!$G$5:$G$204,$AQ58),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ58)-INDEX('01_予約入力'!$G$5:$G$204,$AQ58)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V58" s="69" t="n"/>
-      <c r="W58" s="70" t="n"/>
+      <c r="V58" s="114" t="n"/>
+      <c r="W58" s="115" t="n"/>
       <c r="X58" s="47">
         <f>IF($AQ58=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ58)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ58)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ58)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ58)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ58))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ58)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ58))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ58)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ58))))</f>
         <v/>
       </c>
-      <c r="Y58" s="69" t="n"/>
-      <c r="Z58" s="69" t="n"/>
-      <c r="AA58" s="70" t="n"/>
+      <c r="Y58" s="114" t="n"/>
+      <c r="Z58" s="114" t="n"/>
+      <c r="AA58" s="115" t="n"/>
       <c r="AB58" s="47">
         <f>IF($AQ58=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ58)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ58)))</f>
         <v/>
       </c>
-      <c r="AC58" s="69" t="n"/>
-      <c r="AD58" s="70" t="n"/>
+      <c r="AC58" s="114" t="n"/>
+      <c r="AD58" s="115" t="n"/>
       <c r="AE58" s="46">
         <f>IF($AQ58=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ58))</f>
         <v/>
       </c>
-      <c r="AF58" s="69" t="n"/>
-      <c r="AG58" s="70" t="n"/>
+      <c r="AF58" s="114" t="n"/>
+      <c r="AG58" s="115" t="n"/>
       <c r="AP58">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,26),"")</f>
         <v/>
@@ -30047,58 +30869,58 @@
         <f>IF($AQ59=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ59)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ59)))</f>
         <v/>
       </c>
-      <c r="C59" s="69" t="n"/>
-      <c r="D59" s="69" t="n"/>
-      <c r="E59" s="70" t="n"/>
+      <c r="C59" s="114" t="n"/>
+      <c r="D59" s="114" t="n"/>
+      <c r="E59" s="115" t="n"/>
       <c r="F59" s="47">
         <f>IF($AQ59=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ59))</f>
         <v/>
       </c>
-      <c r="G59" s="69" t="n"/>
-      <c r="H59" s="70" t="n"/>
+      <c r="G59" s="114" t="n"/>
+      <c r="H59" s="115" t="n"/>
       <c r="I59" s="46">
         <f>IF($AQ59=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ59))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ59))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ59)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ59))</f>
         <v/>
       </c>
-      <c r="J59" s="69" t="n"/>
-      <c r="K59" s="69" t="n"/>
-      <c r="L59" s="69" t="n"/>
-      <c r="M59" s="69" t="n"/>
-      <c r="N59" s="70" t="n"/>
+      <c r="J59" s="114" t="n"/>
+      <c r="K59" s="114" t="n"/>
+      <c r="L59" s="114" t="n"/>
+      <c r="M59" s="114" t="n"/>
+      <c r="N59" s="115" t="n"/>
       <c r="O59" s="46">
         <f>IF($AQ59=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ59))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ59))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ59)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ59))</f>
         <v/>
       </c>
-      <c r="P59" s="69" t="n"/>
-      <c r="Q59" s="69" t="n"/>
-      <c r="R59" s="69" t="n"/>
-      <c r="S59" s="69" t="n"/>
-      <c r="T59" s="70" t="n"/>
+      <c r="P59" s="114" t="n"/>
+      <c r="Q59" s="114" t="n"/>
+      <c r="R59" s="114" t="n"/>
+      <c r="S59" s="114" t="n"/>
+      <c r="T59" s="115" t="n"/>
       <c r="U59" s="47">
         <f>IF($AQ59=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ59)=INDEX('01_予約入力'!$G$5:$G$204,$AQ59),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ59)-INDEX('01_予約入力'!$G$5:$G$204,$AQ59)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V59" s="69" t="n"/>
-      <c r="W59" s="70" t="n"/>
+      <c r="V59" s="114" t="n"/>
+      <c r="W59" s="115" t="n"/>
       <c r="X59" s="47">
         <f>IF($AQ59=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ59)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ59)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ59)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ59)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ59))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ59)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ59))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ59)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ59))))</f>
         <v/>
       </c>
-      <c r="Y59" s="69" t="n"/>
-      <c r="Z59" s="69" t="n"/>
-      <c r="AA59" s="70" t="n"/>
+      <c r="Y59" s="114" t="n"/>
+      <c r="Z59" s="114" t="n"/>
+      <c r="AA59" s="115" t="n"/>
       <c r="AB59" s="47">
         <f>IF($AQ59=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ59)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ59)))</f>
         <v/>
       </c>
-      <c r="AC59" s="69" t="n"/>
-      <c r="AD59" s="70" t="n"/>
+      <c r="AC59" s="114" t="n"/>
+      <c r="AD59" s="115" t="n"/>
       <c r="AE59" s="46">
         <f>IF($AQ59=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ59))</f>
         <v/>
       </c>
-      <c r="AF59" s="69" t="n"/>
-      <c r="AG59" s="70" t="n"/>
+      <c r="AF59" s="114" t="n"/>
+      <c r="AG59" s="115" t="n"/>
       <c r="AP59">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,27),"")</f>
         <v/>
@@ -30117,58 +30939,58 @@
         <f>IF($AQ60=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ60)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ60)))</f>
         <v/>
       </c>
-      <c r="C60" s="69" t="n"/>
-      <c r="D60" s="69" t="n"/>
-      <c r="E60" s="70" t="n"/>
+      <c r="C60" s="114" t="n"/>
+      <c r="D60" s="114" t="n"/>
+      <c r="E60" s="115" t="n"/>
       <c r="F60" s="47">
         <f>IF($AQ60=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ60))</f>
         <v/>
       </c>
-      <c r="G60" s="69" t="n"/>
-      <c r="H60" s="70" t="n"/>
+      <c r="G60" s="114" t="n"/>
+      <c r="H60" s="115" t="n"/>
       <c r="I60" s="46">
         <f>IF($AQ60=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ60))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ60))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ60)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ60))</f>
         <v/>
       </c>
-      <c r="J60" s="69" t="n"/>
-      <c r="K60" s="69" t="n"/>
-      <c r="L60" s="69" t="n"/>
-      <c r="M60" s="69" t="n"/>
-      <c r="N60" s="70" t="n"/>
+      <c r="J60" s="114" t="n"/>
+      <c r="K60" s="114" t="n"/>
+      <c r="L60" s="114" t="n"/>
+      <c r="M60" s="114" t="n"/>
+      <c r="N60" s="115" t="n"/>
       <c r="O60" s="46">
         <f>IF($AQ60=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ60))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ60))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ60)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ60))</f>
         <v/>
       </c>
-      <c r="P60" s="69" t="n"/>
-      <c r="Q60" s="69" t="n"/>
-      <c r="R60" s="69" t="n"/>
-      <c r="S60" s="69" t="n"/>
-      <c r="T60" s="70" t="n"/>
+      <c r="P60" s="114" t="n"/>
+      <c r="Q60" s="114" t="n"/>
+      <c r="R60" s="114" t="n"/>
+      <c r="S60" s="114" t="n"/>
+      <c r="T60" s="115" t="n"/>
       <c r="U60" s="47">
         <f>IF($AQ60=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ60)=INDEX('01_予約入力'!$G$5:$G$204,$AQ60),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ60)-INDEX('01_予約入力'!$G$5:$G$204,$AQ60)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V60" s="69" t="n"/>
-      <c r="W60" s="70" t="n"/>
+      <c r="V60" s="114" t="n"/>
+      <c r="W60" s="115" t="n"/>
       <c r="X60" s="47">
         <f>IF($AQ60=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ60)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ60)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ60)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ60)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ60))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ60)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ60))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ60)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ60))))</f>
         <v/>
       </c>
-      <c r="Y60" s="69" t="n"/>
-      <c r="Z60" s="69" t="n"/>
-      <c r="AA60" s="70" t="n"/>
+      <c r="Y60" s="114" t="n"/>
+      <c r="Z60" s="114" t="n"/>
+      <c r="AA60" s="115" t="n"/>
       <c r="AB60" s="47">
         <f>IF($AQ60=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ60)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ60)))</f>
         <v/>
       </c>
-      <c r="AC60" s="69" t="n"/>
-      <c r="AD60" s="70" t="n"/>
+      <c r="AC60" s="114" t="n"/>
+      <c r="AD60" s="115" t="n"/>
       <c r="AE60" s="46">
         <f>IF($AQ60=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ60))</f>
         <v/>
       </c>
-      <c r="AF60" s="69" t="n"/>
-      <c r="AG60" s="70" t="n"/>
+      <c r="AF60" s="114" t="n"/>
+      <c r="AG60" s="115" t="n"/>
       <c r="AP60">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,28),"")</f>
         <v/>
@@ -30187,58 +31009,58 @@
         <f>IF($AQ61=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ61)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ61)))</f>
         <v/>
       </c>
-      <c r="C61" s="69" t="n"/>
-      <c r="D61" s="69" t="n"/>
-      <c r="E61" s="70" t="n"/>
+      <c r="C61" s="114" t="n"/>
+      <c r="D61" s="114" t="n"/>
+      <c r="E61" s="115" t="n"/>
       <c r="F61" s="47">
         <f>IF($AQ61=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ61))</f>
         <v/>
       </c>
-      <c r="G61" s="69" t="n"/>
-      <c r="H61" s="70" t="n"/>
+      <c r="G61" s="114" t="n"/>
+      <c r="H61" s="115" t="n"/>
       <c r="I61" s="46">
         <f>IF($AQ61=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ61))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ61))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ61)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ61))</f>
         <v/>
       </c>
-      <c r="J61" s="69" t="n"/>
-      <c r="K61" s="69" t="n"/>
-      <c r="L61" s="69" t="n"/>
-      <c r="M61" s="69" t="n"/>
-      <c r="N61" s="70" t="n"/>
+      <c r="J61" s="114" t="n"/>
+      <c r="K61" s="114" t="n"/>
+      <c r="L61" s="114" t="n"/>
+      <c r="M61" s="114" t="n"/>
+      <c r="N61" s="115" t="n"/>
       <c r="O61" s="46">
         <f>IF($AQ61=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ61))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ61))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ61)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ61))</f>
         <v/>
       </c>
-      <c r="P61" s="69" t="n"/>
-      <c r="Q61" s="69" t="n"/>
-      <c r="R61" s="69" t="n"/>
-      <c r="S61" s="69" t="n"/>
-      <c r="T61" s="70" t="n"/>
+      <c r="P61" s="114" t="n"/>
+      <c r="Q61" s="114" t="n"/>
+      <c r="R61" s="114" t="n"/>
+      <c r="S61" s="114" t="n"/>
+      <c r="T61" s="115" t="n"/>
       <c r="U61" s="47">
         <f>IF($AQ61=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ61)=INDEX('01_予約入力'!$G$5:$G$204,$AQ61),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ61)-INDEX('01_予約入力'!$G$5:$G$204,$AQ61)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V61" s="69" t="n"/>
-      <c r="W61" s="70" t="n"/>
+      <c r="V61" s="114" t="n"/>
+      <c r="W61" s="115" t="n"/>
       <c r="X61" s="47">
         <f>IF($AQ61=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ61)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ61)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ61)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ61)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ61))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ61)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ61))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ61)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ61))))</f>
         <v/>
       </c>
-      <c r="Y61" s="69" t="n"/>
-      <c r="Z61" s="69" t="n"/>
-      <c r="AA61" s="70" t="n"/>
+      <c r="Y61" s="114" t="n"/>
+      <c r="Z61" s="114" t="n"/>
+      <c r="AA61" s="115" t="n"/>
       <c r="AB61" s="47">
         <f>IF($AQ61=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ61)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ61)))</f>
         <v/>
       </c>
-      <c r="AC61" s="69" t="n"/>
-      <c r="AD61" s="70" t="n"/>
+      <c r="AC61" s="114" t="n"/>
+      <c r="AD61" s="115" t="n"/>
       <c r="AE61" s="46">
         <f>IF($AQ61=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ61))</f>
         <v/>
       </c>
-      <c r="AF61" s="69" t="n"/>
-      <c r="AG61" s="70" t="n"/>
+      <c r="AF61" s="114" t="n"/>
+      <c r="AG61" s="115" t="n"/>
       <c r="AP61">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,29),"")</f>
         <v/>
@@ -30257,58 +31079,58 @@
         <f>IF($AQ62=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ62)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ62)))</f>
         <v/>
       </c>
-      <c r="C62" s="69" t="n"/>
-      <c r="D62" s="69" t="n"/>
-      <c r="E62" s="70" t="n"/>
+      <c r="C62" s="114" t="n"/>
+      <c r="D62" s="114" t="n"/>
+      <c r="E62" s="115" t="n"/>
       <c r="F62" s="47">
         <f>IF($AQ62=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ62))</f>
         <v/>
       </c>
-      <c r="G62" s="69" t="n"/>
-      <c r="H62" s="70" t="n"/>
+      <c r="G62" s="114" t="n"/>
+      <c r="H62" s="115" t="n"/>
       <c r="I62" s="46">
         <f>IF($AQ62=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ62))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ62))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ62)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ62))</f>
         <v/>
       </c>
-      <c r="J62" s="69" t="n"/>
-      <c r="K62" s="69" t="n"/>
-      <c r="L62" s="69" t="n"/>
-      <c r="M62" s="69" t="n"/>
-      <c r="N62" s="70" t="n"/>
+      <c r="J62" s="114" t="n"/>
+      <c r="K62" s="114" t="n"/>
+      <c r="L62" s="114" t="n"/>
+      <c r="M62" s="114" t="n"/>
+      <c r="N62" s="115" t="n"/>
       <c r="O62" s="46">
         <f>IF($AQ62=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ62))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ62))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ62)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ62))</f>
         <v/>
       </c>
-      <c r="P62" s="69" t="n"/>
-      <c r="Q62" s="69" t="n"/>
-      <c r="R62" s="69" t="n"/>
-      <c r="S62" s="69" t="n"/>
-      <c r="T62" s="70" t="n"/>
+      <c r="P62" s="114" t="n"/>
+      <c r="Q62" s="114" t="n"/>
+      <c r="R62" s="114" t="n"/>
+      <c r="S62" s="114" t="n"/>
+      <c r="T62" s="115" t="n"/>
       <c r="U62" s="47">
         <f>IF($AQ62=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ62)=INDEX('01_予約入力'!$G$5:$G$204,$AQ62),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ62)-INDEX('01_予約入力'!$G$5:$G$204,$AQ62)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V62" s="69" t="n"/>
-      <c r="W62" s="70" t="n"/>
+      <c r="V62" s="114" t="n"/>
+      <c r="W62" s="115" t="n"/>
       <c r="X62" s="47">
         <f>IF($AQ62=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ62)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ62)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ62)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ62)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ62))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ62)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ62))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ62)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ62))))</f>
         <v/>
       </c>
-      <c r="Y62" s="69" t="n"/>
-      <c r="Z62" s="69" t="n"/>
-      <c r="AA62" s="70" t="n"/>
+      <c r="Y62" s="114" t="n"/>
+      <c r="Z62" s="114" t="n"/>
+      <c r="AA62" s="115" t="n"/>
       <c r="AB62" s="47">
         <f>IF($AQ62=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ62)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ62)))</f>
         <v/>
       </c>
-      <c r="AC62" s="69" t="n"/>
-      <c r="AD62" s="70" t="n"/>
+      <c r="AC62" s="114" t="n"/>
+      <c r="AD62" s="115" t="n"/>
       <c r="AE62" s="46">
         <f>IF($AQ62=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ62))</f>
         <v/>
       </c>
-      <c r="AF62" s="69" t="n"/>
-      <c r="AG62" s="70" t="n"/>
+      <c r="AF62" s="114" t="n"/>
+      <c r="AG62" s="115" t="n"/>
       <c r="AP62">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,30),"")</f>
         <v/>
@@ -30327,58 +31149,58 @@
         <f>IF($AQ63=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ63)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ63)))</f>
         <v/>
       </c>
-      <c r="C63" s="69" t="n"/>
-      <c r="D63" s="69" t="n"/>
-      <c r="E63" s="70" t="n"/>
+      <c r="C63" s="114" t="n"/>
+      <c r="D63" s="114" t="n"/>
+      <c r="E63" s="115" t="n"/>
       <c r="F63" s="47">
         <f>IF($AQ63=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ63))</f>
         <v/>
       </c>
-      <c r="G63" s="69" t="n"/>
-      <c r="H63" s="70" t="n"/>
+      <c r="G63" s="114" t="n"/>
+      <c r="H63" s="115" t="n"/>
       <c r="I63" s="46">
         <f>IF($AQ63=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ63))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ63))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ63)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ63))</f>
         <v/>
       </c>
-      <c r="J63" s="69" t="n"/>
-      <c r="K63" s="69" t="n"/>
-      <c r="L63" s="69" t="n"/>
-      <c r="M63" s="69" t="n"/>
-      <c r="N63" s="70" t="n"/>
+      <c r="J63" s="114" t="n"/>
+      <c r="K63" s="114" t="n"/>
+      <c r="L63" s="114" t="n"/>
+      <c r="M63" s="114" t="n"/>
+      <c r="N63" s="115" t="n"/>
       <c r="O63" s="46">
         <f>IF($AQ63=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ63))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ63))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ63)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ63))</f>
         <v/>
       </c>
-      <c r="P63" s="69" t="n"/>
-      <c r="Q63" s="69" t="n"/>
-      <c r="R63" s="69" t="n"/>
-      <c r="S63" s="69" t="n"/>
-      <c r="T63" s="70" t="n"/>
+      <c r="P63" s="114" t="n"/>
+      <c r="Q63" s="114" t="n"/>
+      <c r="R63" s="114" t="n"/>
+      <c r="S63" s="114" t="n"/>
+      <c r="T63" s="115" t="n"/>
       <c r="U63" s="47">
         <f>IF($AQ63=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ63)=INDEX('01_予約入力'!$G$5:$G$204,$AQ63),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ63)-INDEX('01_予約入力'!$G$5:$G$204,$AQ63)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V63" s="69" t="n"/>
-      <c r="W63" s="70" t="n"/>
+      <c r="V63" s="114" t="n"/>
+      <c r="W63" s="115" t="n"/>
       <c r="X63" s="47">
         <f>IF($AQ63=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ63)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ63)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ63)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ63)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ63))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ63)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ63))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ63)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ63))))</f>
         <v/>
       </c>
-      <c r="Y63" s="69" t="n"/>
-      <c r="Z63" s="69" t="n"/>
-      <c r="AA63" s="70" t="n"/>
+      <c r="Y63" s="114" t="n"/>
+      <c r="Z63" s="114" t="n"/>
+      <c r="AA63" s="115" t="n"/>
       <c r="AB63" s="47">
         <f>IF($AQ63=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ63)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ63)))</f>
         <v/>
       </c>
-      <c r="AC63" s="69" t="n"/>
-      <c r="AD63" s="70" t="n"/>
+      <c r="AC63" s="114" t="n"/>
+      <c r="AD63" s="115" t="n"/>
       <c r="AE63" s="46">
         <f>IF($AQ63=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ63))</f>
         <v/>
       </c>
-      <c r="AF63" s="69" t="n"/>
-      <c r="AG63" s="70" t="n"/>
+      <c r="AF63" s="114" t="n"/>
+      <c r="AG63" s="115" t="n"/>
       <c r="AP63">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,31),"")</f>
         <v/>
@@ -30397,58 +31219,58 @@
         <f>IF($AQ64=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ64)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ64)))</f>
         <v/>
       </c>
-      <c r="C64" s="69" t="n"/>
-      <c r="D64" s="69" t="n"/>
-      <c r="E64" s="70" t="n"/>
+      <c r="C64" s="114" t="n"/>
+      <c r="D64" s="114" t="n"/>
+      <c r="E64" s="115" t="n"/>
       <c r="F64" s="47">
         <f>IF($AQ64=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ64))</f>
         <v/>
       </c>
-      <c r="G64" s="69" t="n"/>
-      <c r="H64" s="70" t="n"/>
+      <c r="G64" s="114" t="n"/>
+      <c r="H64" s="115" t="n"/>
       <c r="I64" s="46">
         <f>IF($AQ64=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ64))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ64))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ64)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ64))</f>
         <v/>
       </c>
-      <c r="J64" s="69" t="n"/>
-      <c r="K64" s="69" t="n"/>
-      <c r="L64" s="69" t="n"/>
-      <c r="M64" s="69" t="n"/>
-      <c r="N64" s="70" t="n"/>
+      <c r="J64" s="114" t="n"/>
+      <c r="K64" s="114" t="n"/>
+      <c r="L64" s="114" t="n"/>
+      <c r="M64" s="114" t="n"/>
+      <c r="N64" s="115" t="n"/>
       <c r="O64" s="46">
         <f>IF($AQ64=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ64))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ64))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ64)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ64))</f>
         <v/>
       </c>
-      <c r="P64" s="69" t="n"/>
-      <c r="Q64" s="69" t="n"/>
-      <c r="R64" s="69" t="n"/>
-      <c r="S64" s="69" t="n"/>
-      <c r="T64" s="70" t="n"/>
+      <c r="P64" s="114" t="n"/>
+      <c r="Q64" s="114" t="n"/>
+      <c r="R64" s="114" t="n"/>
+      <c r="S64" s="114" t="n"/>
+      <c r="T64" s="115" t="n"/>
       <c r="U64" s="47">
         <f>IF($AQ64=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ64)=INDEX('01_予約入力'!$G$5:$G$204,$AQ64),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ64)-INDEX('01_予約入力'!$G$5:$G$204,$AQ64)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V64" s="69" t="n"/>
-      <c r="W64" s="70" t="n"/>
+      <c r="V64" s="114" t="n"/>
+      <c r="W64" s="115" t="n"/>
       <c r="X64" s="47">
         <f>IF($AQ64=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ64)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ64)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ64)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ64)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ64))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ64)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ64))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ64)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ64))))</f>
         <v/>
       </c>
-      <c r="Y64" s="69" t="n"/>
-      <c r="Z64" s="69" t="n"/>
-      <c r="AA64" s="70" t="n"/>
+      <c r="Y64" s="114" t="n"/>
+      <c r="Z64" s="114" t="n"/>
+      <c r="AA64" s="115" t="n"/>
       <c r="AB64" s="47">
         <f>IF($AQ64=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ64)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ64)))</f>
         <v/>
       </c>
-      <c r="AC64" s="69" t="n"/>
-      <c r="AD64" s="70" t="n"/>
+      <c r="AC64" s="114" t="n"/>
+      <c r="AD64" s="115" t="n"/>
       <c r="AE64" s="46">
         <f>IF($AQ64=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ64))</f>
         <v/>
       </c>
-      <c r="AF64" s="69" t="n"/>
-      <c r="AG64" s="70" t="n"/>
+      <c r="AF64" s="114" t="n"/>
+      <c r="AG64" s="115" t="n"/>
       <c r="AP64">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,32),"")</f>
         <v/>
@@ -30467,58 +31289,58 @@
         <f>IF($AQ65=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ65)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ65)))</f>
         <v/>
       </c>
-      <c r="C65" s="69" t="n"/>
-      <c r="D65" s="69" t="n"/>
-      <c r="E65" s="70" t="n"/>
+      <c r="C65" s="114" t="n"/>
+      <c r="D65" s="114" t="n"/>
+      <c r="E65" s="115" t="n"/>
       <c r="F65" s="47">
         <f>IF($AQ65=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ65))</f>
         <v/>
       </c>
-      <c r="G65" s="69" t="n"/>
-      <c r="H65" s="70" t="n"/>
+      <c r="G65" s="114" t="n"/>
+      <c r="H65" s="115" t="n"/>
       <c r="I65" s="46">
         <f>IF($AQ65=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ65))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ65))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ65)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ65))</f>
         <v/>
       </c>
-      <c r="J65" s="69" t="n"/>
-      <c r="K65" s="69" t="n"/>
-      <c r="L65" s="69" t="n"/>
-      <c r="M65" s="69" t="n"/>
-      <c r="N65" s="70" t="n"/>
+      <c r="J65" s="114" t="n"/>
+      <c r="K65" s="114" t="n"/>
+      <c r="L65" s="114" t="n"/>
+      <c r="M65" s="114" t="n"/>
+      <c r="N65" s="115" t="n"/>
       <c r="O65" s="46">
         <f>IF($AQ65=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ65))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ65))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ65)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ65))</f>
         <v/>
       </c>
-      <c r="P65" s="69" t="n"/>
-      <c r="Q65" s="69" t="n"/>
-      <c r="R65" s="69" t="n"/>
-      <c r="S65" s="69" t="n"/>
-      <c r="T65" s="70" t="n"/>
+      <c r="P65" s="114" t="n"/>
+      <c r="Q65" s="114" t="n"/>
+      <c r="R65" s="114" t="n"/>
+      <c r="S65" s="114" t="n"/>
+      <c r="T65" s="115" t="n"/>
       <c r="U65" s="47">
         <f>IF($AQ65=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ65)=INDEX('01_予約入力'!$G$5:$G$204,$AQ65),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ65)-INDEX('01_予約入力'!$G$5:$G$204,$AQ65)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V65" s="69" t="n"/>
-      <c r="W65" s="70" t="n"/>
+      <c r="V65" s="114" t="n"/>
+      <c r="W65" s="115" t="n"/>
       <c r="X65" s="47">
         <f>IF($AQ65=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ65)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ65)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ65)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ65)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ65))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ65)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ65))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ65)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ65))))</f>
         <v/>
       </c>
-      <c r="Y65" s="69" t="n"/>
-      <c r="Z65" s="69" t="n"/>
-      <c r="AA65" s="70" t="n"/>
+      <c r="Y65" s="114" t="n"/>
+      <c r="Z65" s="114" t="n"/>
+      <c r="AA65" s="115" t="n"/>
       <c r="AB65" s="47">
         <f>IF($AQ65=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ65)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ65)))</f>
         <v/>
       </c>
-      <c r="AC65" s="69" t="n"/>
-      <c r="AD65" s="70" t="n"/>
+      <c r="AC65" s="114" t="n"/>
+      <c r="AD65" s="115" t="n"/>
       <c r="AE65" s="46">
         <f>IF($AQ65=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ65))</f>
         <v/>
       </c>
-      <c r="AF65" s="69" t="n"/>
-      <c r="AG65" s="70" t="n"/>
+      <c r="AF65" s="114" t="n"/>
+      <c r="AG65" s="115" t="n"/>
       <c r="AP65">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,33),"")</f>
         <v/>
@@ -30537,58 +31359,58 @@
         <f>IF($AQ66=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ66)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ66)))</f>
         <v/>
       </c>
-      <c r="C66" s="69" t="n"/>
-      <c r="D66" s="69" t="n"/>
-      <c r="E66" s="70" t="n"/>
+      <c r="C66" s="114" t="n"/>
+      <c r="D66" s="114" t="n"/>
+      <c r="E66" s="115" t="n"/>
       <c r="F66" s="47">
         <f>IF($AQ66=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ66))</f>
         <v/>
       </c>
-      <c r="G66" s="69" t="n"/>
-      <c r="H66" s="70" t="n"/>
+      <c r="G66" s="114" t="n"/>
+      <c r="H66" s="115" t="n"/>
       <c r="I66" s="46">
         <f>IF($AQ66=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ66))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ66))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ66)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ66))</f>
         <v/>
       </c>
-      <c r="J66" s="69" t="n"/>
-      <c r="K66" s="69" t="n"/>
-      <c r="L66" s="69" t="n"/>
-      <c r="M66" s="69" t="n"/>
-      <c r="N66" s="70" t="n"/>
+      <c r="J66" s="114" t="n"/>
+      <c r="K66" s="114" t="n"/>
+      <c r="L66" s="114" t="n"/>
+      <c r="M66" s="114" t="n"/>
+      <c r="N66" s="115" t="n"/>
       <c r="O66" s="46">
         <f>IF($AQ66=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ66))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ66))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ66)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ66))</f>
         <v/>
       </c>
-      <c r="P66" s="69" t="n"/>
-      <c r="Q66" s="69" t="n"/>
-      <c r="R66" s="69" t="n"/>
-      <c r="S66" s="69" t="n"/>
-      <c r="T66" s="70" t="n"/>
+      <c r="P66" s="114" t="n"/>
+      <c r="Q66" s="114" t="n"/>
+      <c r="R66" s="114" t="n"/>
+      <c r="S66" s="114" t="n"/>
+      <c r="T66" s="115" t="n"/>
       <c r="U66" s="47">
         <f>IF($AQ66=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ66)=INDEX('01_予約入力'!$G$5:$G$204,$AQ66),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ66)-INDEX('01_予約入力'!$G$5:$G$204,$AQ66)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V66" s="69" t="n"/>
-      <c r="W66" s="70" t="n"/>
+      <c r="V66" s="114" t="n"/>
+      <c r="W66" s="115" t="n"/>
       <c r="X66" s="47">
         <f>IF($AQ66=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ66)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ66)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ66)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ66)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ66))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ66)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ66))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ66)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ66))))</f>
         <v/>
       </c>
-      <c r="Y66" s="69" t="n"/>
-      <c r="Z66" s="69" t="n"/>
-      <c r="AA66" s="70" t="n"/>
+      <c r="Y66" s="114" t="n"/>
+      <c r="Z66" s="114" t="n"/>
+      <c r="AA66" s="115" t="n"/>
       <c r="AB66" s="47">
         <f>IF($AQ66=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ66)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ66)))</f>
         <v/>
       </c>
-      <c r="AC66" s="69" t="n"/>
-      <c r="AD66" s="70" t="n"/>
+      <c r="AC66" s="114" t="n"/>
+      <c r="AD66" s="115" t="n"/>
       <c r="AE66" s="46">
         <f>IF($AQ66=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ66))</f>
         <v/>
       </c>
-      <c r="AF66" s="69" t="n"/>
-      <c r="AG66" s="70" t="n"/>
+      <c r="AF66" s="114" t="n"/>
+      <c r="AG66" s="115" t="n"/>
       <c r="AP66">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,34),"")</f>
         <v/>
@@ -30607,58 +31429,58 @@
         <f>IF($AQ67=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ67)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ67)))</f>
         <v/>
       </c>
-      <c r="C67" s="69" t="n"/>
-      <c r="D67" s="69" t="n"/>
-      <c r="E67" s="70" t="n"/>
+      <c r="C67" s="114" t="n"/>
+      <c r="D67" s="114" t="n"/>
+      <c r="E67" s="115" t="n"/>
       <c r="F67" s="47">
         <f>IF($AQ67=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ67))</f>
         <v/>
       </c>
-      <c r="G67" s="69" t="n"/>
-      <c r="H67" s="70" t="n"/>
+      <c r="G67" s="114" t="n"/>
+      <c r="H67" s="115" t="n"/>
       <c r="I67" s="46">
         <f>IF($AQ67=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ67))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ67))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ67)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ67))</f>
         <v/>
       </c>
-      <c r="J67" s="69" t="n"/>
-      <c r="K67" s="69" t="n"/>
-      <c r="L67" s="69" t="n"/>
-      <c r="M67" s="69" t="n"/>
-      <c r="N67" s="70" t="n"/>
+      <c r="J67" s="114" t="n"/>
+      <c r="K67" s="114" t="n"/>
+      <c r="L67" s="114" t="n"/>
+      <c r="M67" s="114" t="n"/>
+      <c r="N67" s="115" t="n"/>
       <c r="O67" s="46">
         <f>IF($AQ67=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ67))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ67))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ67)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ67))</f>
         <v/>
       </c>
-      <c r="P67" s="69" t="n"/>
-      <c r="Q67" s="69" t="n"/>
-      <c r="R67" s="69" t="n"/>
-      <c r="S67" s="69" t="n"/>
-      <c r="T67" s="70" t="n"/>
+      <c r="P67" s="114" t="n"/>
+      <c r="Q67" s="114" t="n"/>
+      <c r="R67" s="114" t="n"/>
+      <c r="S67" s="114" t="n"/>
+      <c r="T67" s="115" t="n"/>
       <c r="U67" s="47">
         <f>IF($AQ67=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ67)=INDEX('01_予約入力'!$G$5:$G$204,$AQ67),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ67)-INDEX('01_予約入力'!$G$5:$G$204,$AQ67)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V67" s="69" t="n"/>
-      <c r="W67" s="70" t="n"/>
+      <c r="V67" s="114" t="n"/>
+      <c r="W67" s="115" t="n"/>
       <c r="X67" s="47">
         <f>IF($AQ67=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ67)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ67)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ67)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ67)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ67))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ67)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ67))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ67)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ67))))</f>
         <v/>
       </c>
-      <c r="Y67" s="69" t="n"/>
-      <c r="Z67" s="69" t="n"/>
-      <c r="AA67" s="70" t="n"/>
+      <c r="Y67" s="114" t="n"/>
+      <c r="Z67" s="114" t="n"/>
+      <c r="AA67" s="115" t="n"/>
       <c r="AB67" s="47">
         <f>IF($AQ67=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ67)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ67)))</f>
         <v/>
       </c>
-      <c r="AC67" s="69" t="n"/>
-      <c r="AD67" s="70" t="n"/>
+      <c r="AC67" s="114" t="n"/>
+      <c r="AD67" s="115" t="n"/>
       <c r="AE67" s="46">
         <f>IF($AQ67=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ67))</f>
         <v/>
       </c>
-      <c r="AF67" s="69" t="n"/>
-      <c r="AG67" s="70" t="n"/>
+      <c r="AF67" s="114" t="n"/>
+      <c r="AG67" s="115" t="n"/>
       <c r="AP67">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,35),"")</f>
         <v/>
@@ -30677,58 +31499,58 @@
         <f>IF($AQ68=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ68)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ68)))</f>
         <v/>
       </c>
-      <c r="C68" s="69" t="n"/>
-      <c r="D68" s="69" t="n"/>
-      <c r="E68" s="70" t="n"/>
+      <c r="C68" s="114" t="n"/>
+      <c r="D68" s="114" t="n"/>
+      <c r="E68" s="115" t="n"/>
       <c r="F68" s="47">
         <f>IF($AQ68=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ68))</f>
         <v/>
       </c>
-      <c r="G68" s="69" t="n"/>
-      <c r="H68" s="70" t="n"/>
+      <c r="G68" s="114" t="n"/>
+      <c r="H68" s="115" t="n"/>
       <c r="I68" s="46">
         <f>IF($AQ68=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ68))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ68))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ68)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ68))</f>
         <v/>
       </c>
-      <c r="J68" s="69" t="n"/>
-      <c r="K68" s="69" t="n"/>
-      <c r="L68" s="69" t="n"/>
-      <c r="M68" s="69" t="n"/>
-      <c r="N68" s="70" t="n"/>
+      <c r="J68" s="114" t="n"/>
+      <c r="K68" s="114" t="n"/>
+      <c r="L68" s="114" t="n"/>
+      <c r="M68" s="114" t="n"/>
+      <c r="N68" s="115" t="n"/>
       <c r="O68" s="46">
         <f>IF($AQ68=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ68))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ68))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ68)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ68))</f>
         <v/>
       </c>
-      <c r="P68" s="69" t="n"/>
-      <c r="Q68" s="69" t="n"/>
-      <c r="R68" s="69" t="n"/>
-      <c r="S68" s="69" t="n"/>
-      <c r="T68" s="70" t="n"/>
+      <c r="P68" s="114" t="n"/>
+      <c r="Q68" s="114" t="n"/>
+      <c r="R68" s="114" t="n"/>
+      <c r="S68" s="114" t="n"/>
+      <c r="T68" s="115" t="n"/>
       <c r="U68" s="47">
         <f>IF($AQ68=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ68)=INDEX('01_予約入力'!$G$5:$G$204,$AQ68),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ68)-INDEX('01_予約入力'!$G$5:$G$204,$AQ68)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V68" s="69" t="n"/>
-      <c r="W68" s="70" t="n"/>
+      <c r="V68" s="114" t="n"/>
+      <c r="W68" s="115" t="n"/>
       <c r="X68" s="47">
         <f>IF($AQ68=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ68)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ68)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ68)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ68)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ68))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ68)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ68))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ68)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ68))))</f>
         <v/>
       </c>
-      <c r="Y68" s="69" t="n"/>
-      <c r="Z68" s="69" t="n"/>
-      <c r="AA68" s="70" t="n"/>
+      <c r="Y68" s="114" t="n"/>
+      <c r="Z68" s="114" t="n"/>
+      <c r="AA68" s="115" t="n"/>
       <c r="AB68" s="47">
         <f>IF($AQ68=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ68)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ68)))</f>
         <v/>
       </c>
-      <c r="AC68" s="69" t="n"/>
-      <c r="AD68" s="70" t="n"/>
+      <c r="AC68" s="114" t="n"/>
+      <c r="AD68" s="115" t="n"/>
       <c r="AE68" s="46">
         <f>IF($AQ68=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ68))</f>
         <v/>
       </c>
-      <c r="AF68" s="69" t="n"/>
-      <c r="AG68" s="70" t="n"/>
+      <c r="AF68" s="114" t="n"/>
+      <c r="AG68" s="115" t="n"/>
       <c r="AP68">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,36),"")</f>
         <v/>
@@ -30747,58 +31569,58 @@
         <f>IF($AQ69=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ69)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ69)))</f>
         <v/>
       </c>
-      <c r="C69" s="69" t="n"/>
-      <c r="D69" s="69" t="n"/>
-      <c r="E69" s="70" t="n"/>
+      <c r="C69" s="114" t="n"/>
+      <c r="D69" s="114" t="n"/>
+      <c r="E69" s="115" t="n"/>
       <c r="F69" s="47">
         <f>IF($AQ69=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ69))</f>
         <v/>
       </c>
-      <c r="G69" s="69" t="n"/>
-      <c r="H69" s="70" t="n"/>
+      <c r="G69" s="114" t="n"/>
+      <c r="H69" s="115" t="n"/>
       <c r="I69" s="46">
         <f>IF($AQ69=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ69))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ69))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ69)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ69))</f>
         <v/>
       </c>
-      <c r="J69" s="69" t="n"/>
-      <c r="K69" s="69" t="n"/>
-      <c r="L69" s="69" t="n"/>
-      <c r="M69" s="69" t="n"/>
-      <c r="N69" s="70" t="n"/>
+      <c r="J69" s="114" t="n"/>
+      <c r="K69" s="114" t="n"/>
+      <c r="L69" s="114" t="n"/>
+      <c r="M69" s="114" t="n"/>
+      <c r="N69" s="115" t="n"/>
       <c r="O69" s="46">
         <f>IF($AQ69=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ69))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ69))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ69)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ69))</f>
         <v/>
       </c>
-      <c r="P69" s="69" t="n"/>
-      <c r="Q69" s="69" t="n"/>
-      <c r="R69" s="69" t="n"/>
-      <c r="S69" s="69" t="n"/>
-      <c r="T69" s="70" t="n"/>
+      <c r="P69" s="114" t="n"/>
+      <c r="Q69" s="114" t="n"/>
+      <c r="R69" s="114" t="n"/>
+      <c r="S69" s="114" t="n"/>
+      <c r="T69" s="115" t="n"/>
       <c r="U69" s="47">
         <f>IF($AQ69=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ69)=INDEX('01_予約入力'!$G$5:$G$204,$AQ69),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ69)-INDEX('01_予約入力'!$G$5:$G$204,$AQ69)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V69" s="69" t="n"/>
-      <c r="W69" s="70" t="n"/>
+      <c r="V69" s="114" t="n"/>
+      <c r="W69" s="115" t="n"/>
       <c r="X69" s="47">
         <f>IF($AQ69=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ69)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ69)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ69)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ69)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ69))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ69)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ69))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ69)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ69))))</f>
         <v/>
       </c>
-      <c r="Y69" s="69" t="n"/>
-      <c r="Z69" s="69" t="n"/>
-      <c r="AA69" s="70" t="n"/>
+      <c r="Y69" s="114" t="n"/>
+      <c r="Z69" s="114" t="n"/>
+      <c r="AA69" s="115" t="n"/>
       <c r="AB69" s="47">
         <f>IF($AQ69=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ69)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ69)))</f>
         <v/>
       </c>
-      <c r="AC69" s="69" t="n"/>
-      <c r="AD69" s="70" t="n"/>
+      <c r="AC69" s="114" t="n"/>
+      <c r="AD69" s="115" t="n"/>
       <c r="AE69" s="46">
         <f>IF($AQ69=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ69))</f>
         <v/>
       </c>
-      <c r="AF69" s="69" t="n"/>
-      <c r="AG69" s="70" t="n"/>
+      <c r="AF69" s="114" t="n"/>
+      <c r="AG69" s="115" t="n"/>
       <c r="AP69">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,37),"")</f>
         <v/>
@@ -30817,58 +31639,58 @@
         <f>IF($AQ70=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ70)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ70)))</f>
         <v/>
       </c>
-      <c r="C70" s="69" t="n"/>
-      <c r="D70" s="69" t="n"/>
-      <c r="E70" s="70" t="n"/>
+      <c r="C70" s="114" t="n"/>
+      <c r="D70" s="114" t="n"/>
+      <c r="E70" s="115" t="n"/>
       <c r="F70" s="47">
         <f>IF($AQ70=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ70))</f>
         <v/>
       </c>
-      <c r="G70" s="69" t="n"/>
-      <c r="H70" s="70" t="n"/>
+      <c r="G70" s="114" t="n"/>
+      <c r="H70" s="115" t="n"/>
       <c r="I70" s="46">
         <f>IF($AQ70=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ70))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ70))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ70)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ70))</f>
         <v/>
       </c>
-      <c r="J70" s="69" t="n"/>
-      <c r="K70" s="69" t="n"/>
-      <c r="L70" s="69" t="n"/>
-      <c r="M70" s="69" t="n"/>
-      <c r="N70" s="70" t="n"/>
+      <c r="J70" s="114" t="n"/>
+      <c r="K70" s="114" t="n"/>
+      <c r="L70" s="114" t="n"/>
+      <c r="M70" s="114" t="n"/>
+      <c r="N70" s="115" t="n"/>
       <c r="O70" s="46">
         <f>IF($AQ70=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ70))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ70))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ70)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ70))</f>
         <v/>
       </c>
-      <c r="P70" s="69" t="n"/>
-      <c r="Q70" s="69" t="n"/>
-      <c r="R70" s="69" t="n"/>
-      <c r="S70" s="69" t="n"/>
-      <c r="T70" s="70" t="n"/>
+      <c r="P70" s="114" t="n"/>
+      <c r="Q70" s="114" t="n"/>
+      <c r="R70" s="114" t="n"/>
+      <c r="S70" s="114" t="n"/>
+      <c r="T70" s="115" t="n"/>
       <c r="U70" s="47">
         <f>IF($AQ70=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ70)=INDEX('01_予約入力'!$G$5:$G$204,$AQ70),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ70)-INDEX('01_予約入力'!$G$5:$G$204,$AQ70)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V70" s="69" t="n"/>
-      <c r="W70" s="70" t="n"/>
+      <c r="V70" s="114" t="n"/>
+      <c r="W70" s="115" t="n"/>
       <c r="X70" s="47">
         <f>IF($AQ70=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ70)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ70)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ70)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ70)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ70))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ70)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ70))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ70)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ70))))</f>
         <v/>
       </c>
-      <c r="Y70" s="69" t="n"/>
-      <c r="Z70" s="69" t="n"/>
-      <c r="AA70" s="70" t="n"/>
+      <c r="Y70" s="114" t="n"/>
+      <c r="Z70" s="114" t="n"/>
+      <c r="AA70" s="115" t="n"/>
       <c r="AB70" s="47">
         <f>IF($AQ70=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ70)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ70)))</f>
         <v/>
       </c>
-      <c r="AC70" s="69" t="n"/>
-      <c r="AD70" s="70" t="n"/>
+      <c r="AC70" s="114" t="n"/>
+      <c r="AD70" s="115" t="n"/>
       <c r="AE70" s="46">
         <f>IF($AQ70=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ70))</f>
         <v/>
       </c>
-      <c r="AF70" s="69" t="n"/>
-      <c r="AG70" s="70" t="n"/>
+      <c r="AF70" s="114" t="n"/>
+      <c r="AG70" s="115" t="n"/>
       <c r="AP70">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,38),"")</f>
         <v/>
@@ -30887,58 +31709,58 @@
         <f>IF($AQ71=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ71)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ71)))</f>
         <v/>
       </c>
-      <c r="C71" s="69" t="n"/>
-      <c r="D71" s="69" t="n"/>
-      <c r="E71" s="70" t="n"/>
+      <c r="C71" s="114" t="n"/>
+      <c r="D71" s="114" t="n"/>
+      <c r="E71" s="115" t="n"/>
       <c r="F71" s="47">
         <f>IF($AQ71=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ71))</f>
         <v/>
       </c>
-      <c r="G71" s="69" t="n"/>
-      <c r="H71" s="70" t="n"/>
+      <c r="G71" s="114" t="n"/>
+      <c r="H71" s="115" t="n"/>
       <c r="I71" s="46">
         <f>IF($AQ71=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ71))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ71))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ71)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ71))</f>
         <v/>
       </c>
-      <c r="J71" s="69" t="n"/>
-      <c r="K71" s="69" t="n"/>
-      <c r="L71" s="69" t="n"/>
-      <c r="M71" s="69" t="n"/>
-      <c r="N71" s="70" t="n"/>
+      <c r="J71" s="114" t="n"/>
+      <c r="K71" s="114" t="n"/>
+      <c r="L71" s="114" t="n"/>
+      <c r="M71" s="114" t="n"/>
+      <c r="N71" s="115" t="n"/>
       <c r="O71" s="46">
         <f>IF($AQ71=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ71))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ71))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ71)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ71))</f>
         <v/>
       </c>
-      <c r="P71" s="69" t="n"/>
-      <c r="Q71" s="69" t="n"/>
-      <c r="R71" s="69" t="n"/>
-      <c r="S71" s="69" t="n"/>
-      <c r="T71" s="70" t="n"/>
+      <c r="P71" s="114" t="n"/>
+      <c r="Q71" s="114" t="n"/>
+      <c r="R71" s="114" t="n"/>
+      <c r="S71" s="114" t="n"/>
+      <c r="T71" s="115" t="n"/>
       <c r="U71" s="47">
         <f>IF($AQ71=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ71)=INDEX('01_予約入力'!$G$5:$G$204,$AQ71),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ71)-INDEX('01_予約入力'!$G$5:$G$204,$AQ71)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V71" s="69" t="n"/>
-      <c r="W71" s="70" t="n"/>
+      <c r="V71" s="114" t="n"/>
+      <c r="W71" s="115" t="n"/>
       <c r="X71" s="47">
         <f>IF($AQ71=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ71)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ71)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ71)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ71)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ71))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ71)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ71))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ71)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ71))))</f>
         <v/>
       </c>
-      <c r="Y71" s="69" t="n"/>
-      <c r="Z71" s="69" t="n"/>
-      <c r="AA71" s="70" t="n"/>
+      <c r="Y71" s="114" t="n"/>
+      <c r="Z71" s="114" t="n"/>
+      <c r="AA71" s="115" t="n"/>
       <c r="AB71" s="47">
         <f>IF($AQ71=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ71)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ71)))</f>
         <v/>
       </c>
-      <c r="AC71" s="69" t="n"/>
-      <c r="AD71" s="70" t="n"/>
+      <c r="AC71" s="114" t="n"/>
+      <c r="AD71" s="115" t="n"/>
       <c r="AE71" s="46">
         <f>IF($AQ71=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ71))</f>
         <v/>
       </c>
-      <c r="AF71" s="69" t="n"/>
-      <c r="AG71" s="70" t="n"/>
+      <c r="AF71" s="114" t="n"/>
+      <c r="AG71" s="115" t="n"/>
       <c r="AP71">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,39),"")</f>
         <v/>
@@ -30957,58 +31779,58 @@
         <f>IF($AQ72=0,"",IF(INDEX('01_予約入力'!$D$5:$D$204,$AQ72)="","⚠未選択",INDEX('01_予約入力'!$D$5:$D$204,$AQ72)))</f>
         <v/>
       </c>
-      <c r="C72" s="69" t="n"/>
-      <c r="D72" s="69" t="n"/>
-      <c r="E72" s="70" t="n"/>
+      <c r="C72" s="114" t="n"/>
+      <c r="D72" s="114" t="n"/>
+      <c r="E72" s="115" t="n"/>
       <c r="F72" s="47">
         <f>IF($AQ72=0,"",INDEX('01_予約入力'!$C$5:$C$204,$AQ72))</f>
         <v/>
       </c>
-      <c r="G72" s="69" t="n"/>
-      <c r="H72" s="70" t="n"/>
+      <c r="G72" s="114" t="n"/>
+      <c r="H72" s="115" t="n"/>
       <c r="I72" s="46">
         <f>IF($AQ72=0,"",MONTH(INDEX('01_予約入力'!$G$5:$G$204,$AQ72))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ72))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$G$5:$G$204,$AQ72)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AD$5:$AD$204,$AQ72))</f>
         <v/>
       </c>
-      <c r="J72" s="69" t="n"/>
-      <c r="K72" s="69" t="n"/>
-      <c r="L72" s="69" t="n"/>
-      <c r="M72" s="69" t="n"/>
-      <c r="N72" s="70" t="n"/>
+      <c r="J72" s="114" t="n"/>
+      <c r="K72" s="114" t="n"/>
+      <c r="L72" s="114" t="n"/>
+      <c r="M72" s="114" t="n"/>
+      <c r="N72" s="115" t="n"/>
       <c r="O72" s="46">
         <f>IF($AQ72=0,"",MONTH(INDEX('01_予約入力'!$J$5:$J$204,$AQ72))&amp;"/"&amp;DAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ72))&amp;"("&amp;MID("日月火水木金土",WEEKDAY(INDEX('01_予約入力'!$J$5:$J$204,$AQ72)),1)&amp;")"&amp;" "&amp;INDEX('01_予約入力'!$AE$5:$AE$204,$AQ72))</f>
         <v/>
       </c>
-      <c r="P72" s="69" t="n"/>
-      <c r="Q72" s="69" t="n"/>
-      <c r="R72" s="69" t="n"/>
-      <c r="S72" s="69" t="n"/>
-      <c r="T72" s="70" t="n"/>
+      <c r="P72" s="114" t="n"/>
+      <c r="Q72" s="114" t="n"/>
+      <c r="R72" s="114" t="n"/>
+      <c r="S72" s="114" t="n"/>
+      <c r="T72" s="115" t="n"/>
       <c r="U72" s="47">
         <f>IF($AQ72=0,"",IF(INDEX('01_予約入力'!$J$5:$J$204,$AQ72)=INDEX('01_予約入力'!$G$5:$G$204,$AQ72),"日帰り",INDEX('01_予約入力'!$J$5:$J$204,$AQ72)-INDEX('01_予約入力'!$G$5:$G$204,$AQ72)&amp;"泊"))</f>
         <v/>
       </c>
-      <c r="V72" s="69" t="n"/>
-      <c r="W72" s="70" t="n"/>
+      <c r="V72" s="114" t="n"/>
+      <c r="W72" s="115" t="n"/>
       <c r="X72" s="47">
         <f>IF($AQ72=0,"",IF(AND(INDEX('01_予約入力'!$L$5:$L$204,$AQ72)="",INDEX('01_予約入力'!$M$5:$M$204,$AQ72)="",INDEX('01_予約入力'!$N$5:$N$204,$AQ72)=""),"標準","朝"&amp;IF(INDEX('01_予約入力'!$L$5:$L$204,$AQ72)="","−",INDEX('01_予約入力'!$L$5:$L$204,$AQ72))&amp;" 昼"&amp;IF(INDEX('01_予約入力'!$M$5:$M$204,$AQ72)="","−",INDEX('01_予約入力'!$M$5:$M$204,$AQ72))&amp;" 夕"&amp;IF(INDEX('01_予約入力'!$N$5:$N$204,$AQ72)="","−",INDEX('01_予約入力'!$N$5:$N$204,$AQ72))))</f>
         <v/>
       </c>
-      <c r="Y72" s="69" t="n"/>
-      <c r="Z72" s="69" t="n"/>
-      <c r="AA72" s="70" t="n"/>
+      <c r="Y72" s="114" t="n"/>
+      <c r="Z72" s="114" t="n"/>
+      <c r="AA72" s="115" t="n"/>
       <c r="AB72" s="47">
         <f>IF($AQ72=0,"",IF(INDEX('01_予約入力'!$Q$5:$Q$204,$AQ72)="","確定",INDEX('01_予約入力'!$Q$5:$Q$204,$AQ72)))</f>
         <v/>
       </c>
-      <c r="AC72" s="69" t="n"/>
-      <c r="AD72" s="70" t="n"/>
+      <c r="AC72" s="114" t="n"/>
+      <c r="AD72" s="115" t="n"/>
       <c r="AE72" s="46">
         <f>IF($AQ72=0,"",INDEX('01_予約入力'!$V$5:$V$204,$AQ72))</f>
         <v/>
       </c>
-      <c r="AF72" s="69" t="n"/>
-      <c r="AG72" s="70" t="n"/>
+      <c r="AF72" s="114" t="n"/>
+      <c r="AG72" s="115" t="n"/>
       <c r="AP72">
         <f>IFERROR(SMALL('01_予約入力'!$AC$5:$AC$204,40),"")</f>
         <v/>
